--- a/code/resultados/NWJSSP_OADG_NEH(InsertionUPFirstImprovement).xlsx
+++ b/code/resultados/NWJSSP_OADG_NEH(InsertionUPFirstImprovement).xlsx
@@ -15,6 +15,11 @@
     <sheet name="ft20r" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="tai_j10_m10_1" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="tai_j10_m10_1r" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="tai_j100_m10_1" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="tai_j100_m10_1r" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="tai_j100_m100_1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="tai_j100_m100_1r" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="tai_j1000_m10_1" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,6 +461,5000 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>6492739</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3600499</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>59021</v>
+      </c>
+      <c r="B2" t="n">
+        <v>51356</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47469</v>
+      </c>
+      <c r="D2" t="n">
+        <v>125319</v>
+      </c>
+      <c r="E2" t="n">
+        <v>102038</v>
+      </c>
+      <c r="F2" t="n">
+        <v>93</v>
+      </c>
+      <c r="G2" t="n">
+        <v>103422</v>
+      </c>
+      <c r="H2" t="n">
+        <v>92692</v>
+      </c>
+      <c r="I2" t="n">
+        <v>128743</v>
+      </c>
+      <c r="J2" t="n">
+        <v>60220</v>
+      </c>
+      <c r="K2" t="n">
+        <v>37998</v>
+      </c>
+      <c r="L2" t="n">
+        <v>86274</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2102</v>
+      </c>
+      <c r="N2" t="n">
+        <v>29188</v>
+      </c>
+      <c r="O2" t="n">
+        <v>38430</v>
+      </c>
+      <c r="P2" t="n">
+        <v>49307</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>42244</v>
+      </c>
+      <c r="R2" t="n">
+        <v>84554</v>
+      </c>
+      <c r="S2" t="n">
+        <v>39359</v>
+      </c>
+      <c r="T2" t="n">
+        <v>71349</v>
+      </c>
+      <c r="U2" t="n">
+        <v>121665</v>
+      </c>
+      <c r="V2" t="n">
+        <v>78467</v>
+      </c>
+      <c r="W2" t="n">
+        <v>106557</v>
+      </c>
+      <c r="X2" t="n">
+        <v>84452</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>125529</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>65301</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>45592</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>70103</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>13165</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>67980</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>35773</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>113272</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>110182</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>61355</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>95446</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>64512</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>48294</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>111443</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>78169</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>18591</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>131392</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>120220</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>55544</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>69194</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>15580</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>67300</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>96692</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>37268</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>118643</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>75988</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>79460</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>3690</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6978</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>15561</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>73109</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>106960</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>34282</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>23282</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>30431</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>10913</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>59423</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>73704</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>39448</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>83091</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>34704</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>18988</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>15664</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>27303</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>88727</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>58626</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>46068</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>53826</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>29980</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>7447</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>90700</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>44080</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>104051</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>52314</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>117349</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>27726</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>31891</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>90330</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>24082</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>75465</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>21052</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>12720</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>114760</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>106259</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>93255</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>8927</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>5732</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>56684</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>24489</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>99632</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>10738</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>78958</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>98517</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>21690</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>44385650</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3603120</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>758333</v>
+      </c>
+      <c r="B2" t="n">
+        <v>202263</v>
+      </c>
+      <c r="C2" t="n">
+        <v>257993</v>
+      </c>
+      <c r="D2" t="n">
+        <v>415157</v>
+      </c>
+      <c r="E2" t="n">
+        <v>449325</v>
+      </c>
+      <c r="F2" t="n">
+        <v>776994</v>
+      </c>
+      <c r="G2" t="n">
+        <v>345993</v>
+      </c>
+      <c r="H2" t="n">
+        <v>847028</v>
+      </c>
+      <c r="I2" t="n">
+        <v>680179</v>
+      </c>
+      <c r="J2" t="n">
+        <v>635993</v>
+      </c>
+      <c r="K2" t="n">
+        <v>640712</v>
+      </c>
+      <c r="L2" t="n">
+        <v>190735</v>
+      </c>
+      <c r="M2" t="n">
+        <v>790349</v>
+      </c>
+      <c r="N2" t="n">
+        <v>404327</v>
+      </c>
+      <c r="O2" t="n">
+        <v>115190</v>
+      </c>
+      <c r="P2" t="n">
+        <v>722125</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>837922</v>
+      </c>
+      <c r="R2" t="n">
+        <v>747976</v>
+      </c>
+      <c r="S2" t="n">
+        <v>146099</v>
+      </c>
+      <c r="T2" t="n">
+        <v>271</v>
+      </c>
+      <c r="U2" t="n">
+        <v>746325</v>
+      </c>
+      <c r="V2" t="n">
+        <v>493945</v>
+      </c>
+      <c r="W2" t="n">
+        <v>467770</v>
+      </c>
+      <c r="X2" t="n">
+        <v>580835</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>284048</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>449183</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>828490</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>347270</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>701557</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>558117</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>152626</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>683334</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>344994</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>376698</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>50703</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>527823</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>374636</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>391272</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>178158</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>60533</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>223257</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>157080</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>26812</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>241690</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>257050</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>334557</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>118547</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>459381</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>393816</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>68453</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>171287</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>3755</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>105896</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>612217</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>378220</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>249186</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>63230</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>551309</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>160524</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>668010</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>8061</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>681871</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>277473</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>853700</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>175555</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>328924</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>95939</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>133357</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>105473</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>228479</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>535664</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>641094</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>322842</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>476605</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>544661</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>294491</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>428299</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>703473</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>808696</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>602343</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>504987</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>482803</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>626407</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>60626</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>84774</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>788070</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>52921</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>223834</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>488366</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>425520</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>731532</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>37305</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>206626</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>48888</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>576242</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>605242</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>274740</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>801434</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>312107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>44266602</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3601751</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>96847</v>
+      </c>
+      <c r="B2" t="n">
+        <v>746804</v>
+      </c>
+      <c r="C2" t="n">
+        <v>548294</v>
+      </c>
+      <c r="D2" t="n">
+        <v>181469</v>
+      </c>
+      <c r="E2" t="n">
+        <v>95430</v>
+      </c>
+      <c r="F2" t="n">
+        <v>258323</v>
+      </c>
+      <c r="G2" t="n">
+        <v>738123</v>
+      </c>
+      <c r="H2" t="n">
+        <v>545126</v>
+      </c>
+      <c r="I2" t="n">
+        <v>145243</v>
+      </c>
+      <c r="J2" t="n">
+        <v>128100</v>
+      </c>
+      <c r="K2" t="n">
+        <v>831647</v>
+      </c>
+      <c r="L2" t="n">
+        <v>363435</v>
+      </c>
+      <c r="M2" t="n">
+        <v>302700</v>
+      </c>
+      <c r="N2" t="n">
+        <v>806291</v>
+      </c>
+      <c r="O2" t="n">
+        <v>817029</v>
+      </c>
+      <c r="P2" t="n">
+        <v>554806</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>333233</v>
+      </c>
+      <c r="R2" t="n">
+        <v>61713</v>
+      </c>
+      <c r="S2" t="n">
+        <v>672066</v>
+      </c>
+      <c r="T2" t="n">
+        <v>20762</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>835978</v>
+      </c>
+      <c r="W2" t="n">
+        <v>77440</v>
+      </c>
+      <c r="X2" t="n">
+        <v>290752</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>572370</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>60931</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>469803</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>515456</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>418370</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>776785</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>632748</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>248501</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>410425</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>714649</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>444290</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>611942</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>334070</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>467574</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>377370</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>387916</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>770</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>761709</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>375330</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>309061</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>344176</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>688283</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>20134</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>788790</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>141949</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>162356</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>674253</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>667867</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>292594</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>478699</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>714336</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>224349</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>2885</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>733735</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>57577</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>550960</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>252998</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>172281</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>409978</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>194119</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>124665</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>309657</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>26771</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>185014</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>524865</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>238815</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>106785</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>109418</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>701924</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>240005</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>797547</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>579322</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>49246</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>319077</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>211239</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>512200</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>168047</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>356155</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>591799</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>492685</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>199230</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>37078</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>447713</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>88012</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>621200</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>648070</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>439891</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>647449</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>274124</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>724460</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>216519</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>783830</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>127774</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>386505</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>470017</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>596826</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:ALL2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>581226107</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3678155</v>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr"/>
+      <c r="R1" t="inlineStr"/>
+      <c r="S1" t="inlineStr"/>
+      <c r="T1" t="inlineStr"/>
+      <c r="U1" t="inlineStr"/>
+      <c r="V1" t="inlineStr"/>
+      <c r="W1" t="inlineStr"/>
+      <c r="X1" t="inlineStr"/>
+      <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
+      <c r="AB1" t="inlineStr"/>
+      <c r="AC1" t="inlineStr"/>
+      <c r="AD1" t="inlineStr"/>
+      <c r="AE1" t="inlineStr"/>
+      <c r="AF1" t="inlineStr"/>
+      <c r="AG1" t="inlineStr"/>
+      <c r="AH1" t="inlineStr"/>
+      <c r="AI1" t="inlineStr"/>
+      <c r="AJ1" t="inlineStr"/>
+      <c r="AK1" t="inlineStr"/>
+      <c r="AL1" t="inlineStr"/>
+      <c r="AM1" t="inlineStr"/>
+      <c r="AN1" t="inlineStr"/>
+      <c r="AO1" t="inlineStr"/>
+      <c r="AP1" t="inlineStr"/>
+      <c r="AQ1" t="inlineStr"/>
+      <c r="AR1" t="inlineStr"/>
+      <c r="AS1" t="inlineStr"/>
+      <c r="AT1" t="inlineStr"/>
+      <c r="AU1" t="inlineStr"/>
+      <c r="AV1" t="inlineStr"/>
+      <c r="AW1" t="inlineStr"/>
+      <c r="AX1" t="inlineStr"/>
+      <c r="AY1" t="inlineStr"/>
+      <c r="AZ1" t="inlineStr"/>
+      <c r="BA1" t="inlineStr"/>
+      <c r="BB1" t="inlineStr"/>
+      <c r="BC1" t="inlineStr"/>
+      <c r="BD1" t="inlineStr"/>
+      <c r="BE1" t="inlineStr"/>
+      <c r="BF1" t="inlineStr"/>
+      <c r="BG1" t="inlineStr"/>
+      <c r="BH1" t="inlineStr"/>
+      <c r="BI1" t="inlineStr"/>
+      <c r="BJ1" t="inlineStr"/>
+      <c r="BK1" t="inlineStr"/>
+      <c r="BL1" t="inlineStr"/>
+      <c r="BM1" t="inlineStr"/>
+      <c r="BN1" t="inlineStr"/>
+      <c r="BO1" t="inlineStr"/>
+      <c r="BP1" t="inlineStr"/>
+      <c r="BQ1" t="inlineStr"/>
+      <c r="BR1" t="inlineStr"/>
+      <c r="BS1" t="inlineStr"/>
+      <c r="BT1" t="inlineStr"/>
+      <c r="BU1" t="inlineStr"/>
+      <c r="BV1" t="inlineStr"/>
+      <c r="BW1" t="inlineStr"/>
+      <c r="BX1" t="inlineStr"/>
+      <c r="BY1" t="inlineStr"/>
+      <c r="BZ1" t="inlineStr"/>
+      <c r="CA1" t="inlineStr"/>
+      <c r="CB1" t="inlineStr"/>
+      <c r="CC1" t="inlineStr"/>
+      <c r="CD1" t="inlineStr"/>
+      <c r="CE1" t="inlineStr"/>
+      <c r="CF1" t="inlineStr"/>
+      <c r="CG1" t="inlineStr"/>
+      <c r="CH1" t="inlineStr"/>
+      <c r="CI1" t="inlineStr"/>
+      <c r="CJ1" t="inlineStr"/>
+      <c r="CK1" t="inlineStr"/>
+      <c r="CL1" t="inlineStr"/>
+      <c r="CM1" t="inlineStr"/>
+      <c r="CN1" t="inlineStr"/>
+      <c r="CO1" t="inlineStr"/>
+      <c r="CP1" t="inlineStr"/>
+      <c r="CQ1" t="inlineStr"/>
+      <c r="CR1" t="inlineStr"/>
+      <c r="CS1" t="inlineStr"/>
+      <c r="CT1" t="inlineStr"/>
+      <c r="CU1" t="inlineStr"/>
+      <c r="CV1" t="inlineStr"/>
+      <c r="CW1" t="inlineStr"/>
+      <c r="CX1" t="inlineStr"/>
+      <c r="CY1" t="inlineStr"/>
+      <c r="CZ1" t="inlineStr"/>
+      <c r="DA1" t="inlineStr"/>
+      <c r="DB1" t="inlineStr"/>
+      <c r="DC1" t="inlineStr"/>
+      <c r="DD1" t="inlineStr"/>
+      <c r="DE1" t="inlineStr"/>
+      <c r="DF1" t="inlineStr"/>
+      <c r="DG1" t="inlineStr"/>
+      <c r="DH1" t="inlineStr"/>
+      <c r="DI1" t="inlineStr"/>
+      <c r="DJ1" t="inlineStr"/>
+      <c r="DK1" t="inlineStr"/>
+      <c r="DL1" t="inlineStr"/>
+      <c r="DM1" t="inlineStr"/>
+      <c r="DN1" t="inlineStr"/>
+      <c r="DO1" t="inlineStr"/>
+      <c r="DP1" t="inlineStr"/>
+      <c r="DQ1" t="inlineStr"/>
+      <c r="DR1" t="inlineStr"/>
+      <c r="DS1" t="inlineStr"/>
+      <c r="DT1" t="inlineStr"/>
+      <c r="DU1" t="inlineStr"/>
+      <c r="DV1" t="inlineStr"/>
+      <c r="DW1" t="inlineStr"/>
+      <c r="DX1" t="inlineStr"/>
+      <c r="DY1" t="inlineStr"/>
+      <c r="DZ1" t="inlineStr"/>
+      <c r="EA1" t="inlineStr"/>
+      <c r="EB1" t="inlineStr"/>
+      <c r="EC1" t="inlineStr"/>
+      <c r="ED1" t="inlineStr"/>
+      <c r="EE1" t="inlineStr"/>
+      <c r="EF1" t="inlineStr"/>
+      <c r="EG1" t="inlineStr"/>
+      <c r="EH1" t="inlineStr"/>
+      <c r="EI1" t="inlineStr"/>
+      <c r="EJ1" t="inlineStr"/>
+      <c r="EK1" t="inlineStr"/>
+      <c r="EL1" t="inlineStr"/>
+      <c r="EM1" t="inlineStr"/>
+      <c r="EN1" t="inlineStr"/>
+      <c r="EO1" t="inlineStr"/>
+      <c r="EP1" t="inlineStr"/>
+      <c r="EQ1" t="inlineStr"/>
+      <c r="ER1" t="inlineStr"/>
+      <c r="ES1" t="inlineStr"/>
+      <c r="ET1" t="inlineStr"/>
+      <c r="EU1" t="inlineStr"/>
+      <c r="EV1" t="inlineStr"/>
+      <c r="EW1" t="inlineStr"/>
+      <c r="EX1" t="inlineStr"/>
+      <c r="EY1" t="inlineStr"/>
+      <c r="EZ1" t="inlineStr"/>
+      <c r="FA1" t="inlineStr"/>
+      <c r="FB1" t="inlineStr"/>
+      <c r="FC1" t="inlineStr"/>
+      <c r="FD1" t="inlineStr"/>
+      <c r="FE1" t="inlineStr"/>
+      <c r="FF1" t="inlineStr"/>
+      <c r="FG1" t="inlineStr"/>
+      <c r="FH1" t="inlineStr"/>
+      <c r="FI1" t="inlineStr"/>
+      <c r="FJ1" t="inlineStr"/>
+      <c r="FK1" t="inlineStr"/>
+      <c r="FL1" t="inlineStr"/>
+      <c r="FM1" t="inlineStr"/>
+      <c r="FN1" t="inlineStr"/>
+      <c r="FO1" t="inlineStr"/>
+      <c r="FP1" t="inlineStr"/>
+      <c r="FQ1" t="inlineStr"/>
+      <c r="FR1" t="inlineStr"/>
+      <c r="FS1" t="inlineStr"/>
+      <c r="FT1" t="inlineStr"/>
+      <c r="FU1" t="inlineStr"/>
+      <c r="FV1" t="inlineStr"/>
+      <c r="FW1" t="inlineStr"/>
+      <c r="FX1" t="inlineStr"/>
+      <c r="FY1" t="inlineStr"/>
+      <c r="FZ1" t="inlineStr"/>
+      <c r="GA1" t="inlineStr"/>
+      <c r="GB1" t="inlineStr"/>
+      <c r="GC1" t="inlineStr"/>
+      <c r="GD1" t="inlineStr"/>
+      <c r="GE1" t="inlineStr"/>
+      <c r="GF1" t="inlineStr"/>
+      <c r="GG1" t="inlineStr"/>
+      <c r="GH1" t="inlineStr"/>
+      <c r="GI1" t="inlineStr"/>
+      <c r="GJ1" t="inlineStr"/>
+      <c r="GK1" t="inlineStr"/>
+      <c r="GL1" t="inlineStr"/>
+      <c r="GM1" t="inlineStr"/>
+      <c r="GN1" t="inlineStr"/>
+      <c r="GO1" t="inlineStr"/>
+      <c r="GP1" t="inlineStr"/>
+      <c r="GQ1" t="inlineStr"/>
+      <c r="GR1" t="inlineStr"/>
+      <c r="GS1" t="inlineStr"/>
+      <c r="GT1" t="inlineStr"/>
+      <c r="GU1" t="inlineStr"/>
+      <c r="GV1" t="inlineStr"/>
+      <c r="GW1" t="inlineStr"/>
+      <c r="GX1" t="inlineStr"/>
+      <c r="GY1" t="inlineStr"/>
+      <c r="GZ1" t="inlineStr"/>
+      <c r="HA1" t="inlineStr"/>
+      <c r="HB1" t="inlineStr"/>
+      <c r="HC1" t="inlineStr"/>
+      <c r="HD1" t="inlineStr"/>
+      <c r="HE1" t="inlineStr"/>
+      <c r="HF1" t="inlineStr"/>
+      <c r="HG1" t="inlineStr"/>
+      <c r="HH1" t="inlineStr"/>
+      <c r="HI1" t="inlineStr"/>
+      <c r="HJ1" t="inlineStr"/>
+      <c r="HK1" t="inlineStr"/>
+      <c r="HL1" t="inlineStr"/>
+      <c r="HM1" t="inlineStr"/>
+      <c r="HN1" t="inlineStr"/>
+      <c r="HO1" t="inlineStr"/>
+      <c r="HP1" t="inlineStr"/>
+      <c r="HQ1" t="inlineStr"/>
+      <c r="HR1" t="inlineStr"/>
+      <c r="HS1" t="inlineStr"/>
+      <c r="HT1" t="inlineStr"/>
+      <c r="HU1" t="inlineStr"/>
+      <c r="HV1" t="inlineStr"/>
+      <c r="HW1" t="inlineStr"/>
+      <c r="HX1" t="inlineStr"/>
+      <c r="HY1" t="inlineStr"/>
+      <c r="HZ1" t="inlineStr"/>
+      <c r="IA1" t="inlineStr"/>
+      <c r="IB1" t="inlineStr"/>
+      <c r="IC1" t="inlineStr"/>
+      <c r="ID1" t="inlineStr"/>
+      <c r="IE1" t="inlineStr"/>
+      <c r="IF1" t="inlineStr"/>
+      <c r="IG1" t="inlineStr"/>
+      <c r="IH1" t="inlineStr"/>
+      <c r="II1" t="inlineStr"/>
+      <c r="IJ1" t="inlineStr"/>
+      <c r="IK1" t="inlineStr"/>
+      <c r="IL1" t="inlineStr"/>
+      <c r="IM1" t="inlineStr"/>
+      <c r="IN1" t="inlineStr"/>
+      <c r="IO1" t="inlineStr"/>
+      <c r="IP1" t="inlineStr"/>
+      <c r="IQ1" t="inlineStr"/>
+      <c r="IR1" t="inlineStr"/>
+      <c r="IS1" t="inlineStr"/>
+      <c r="IT1" t="inlineStr"/>
+      <c r="IU1" t="inlineStr"/>
+      <c r="IV1" t="inlineStr"/>
+      <c r="IW1" t="inlineStr"/>
+      <c r="IX1" t="inlineStr"/>
+      <c r="IY1" t="inlineStr"/>
+      <c r="IZ1" t="inlineStr"/>
+      <c r="JA1" t="inlineStr"/>
+      <c r="JB1" t="inlineStr"/>
+      <c r="JC1" t="inlineStr"/>
+      <c r="JD1" t="inlineStr"/>
+      <c r="JE1" t="inlineStr"/>
+      <c r="JF1" t="inlineStr"/>
+      <c r="JG1" t="inlineStr"/>
+      <c r="JH1" t="inlineStr"/>
+      <c r="JI1" t="inlineStr"/>
+      <c r="JJ1" t="inlineStr"/>
+      <c r="JK1" t="inlineStr"/>
+      <c r="JL1" t="inlineStr"/>
+      <c r="JM1" t="inlineStr"/>
+      <c r="JN1" t="inlineStr"/>
+      <c r="JO1" t="inlineStr"/>
+      <c r="JP1" t="inlineStr"/>
+      <c r="JQ1" t="inlineStr"/>
+      <c r="JR1" t="inlineStr"/>
+      <c r="JS1" t="inlineStr"/>
+      <c r="JT1" t="inlineStr"/>
+      <c r="JU1" t="inlineStr"/>
+      <c r="JV1" t="inlineStr"/>
+      <c r="JW1" t="inlineStr"/>
+      <c r="JX1" t="inlineStr"/>
+      <c r="JY1" t="inlineStr"/>
+      <c r="JZ1" t="inlineStr"/>
+      <c r="KA1" t="inlineStr"/>
+      <c r="KB1" t="inlineStr"/>
+      <c r="KC1" t="inlineStr"/>
+      <c r="KD1" t="inlineStr"/>
+      <c r="KE1" t="inlineStr"/>
+      <c r="KF1" t="inlineStr"/>
+      <c r="KG1" t="inlineStr"/>
+      <c r="KH1" t="inlineStr"/>
+      <c r="KI1" t="inlineStr"/>
+      <c r="KJ1" t="inlineStr"/>
+      <c r="KK1" t="inlineStr"/>
+      <c r="KL1" t="inlineStr"/>
+      <c r="KM1" t="inlineStr"/>
+      <c r="KN1" t="inlineStr"/>
+      <c r="KO1" t="inlineStr"/>
+      <c r="KP1" t="inlineStr"/>
+      <c r="KQ1" t="inlineStr"/>
+      <c r="KR1" t="inlineStr"/>
+      <c r="KS1" t="inlineStr"/>
+      <c r="KT1" t="inlineStr"/>
+      <c r="KU1" t="inlineStr"/>
+      <c r="KV1" t="inlineStr"/>
+      <c r="KW1" t="inlineStr"/>
+      <c r="KX1" t="inlineStr"/>
+      <c r="KY1" t="inlineStr"/>
+      <c r="KZ1" t="inlineStr"/>
+      <c r="LA1" t="inlineStr"/>
+      <c r="LB1" t="inlineStr"/>
+      <c r="LC1" t="inlineStr"/>
+      <c r="LD1" t="inlineStr"/>
+      <c r="LE1" t="inlineStr"/>
+      <c r="LF1" t="inlineStr"/>
+      <c r="LG1" t="inlineStr"/>
+      <c r="LH1" t="inlineStr"/>
+      <c r="LI1" t="inlineStr"/>
+      <c r="LJ1" t="inlineStr"/>
+      <c r="LK1" t="inlineStr"/>
+      <c r="LL1" t="inlineStr"/>
+      <c r="LM1" t="inlineStr"/>
+      <c r="LN1" t="inlineStr"/>
+      <c r="LO1" t="inlineStr"/>
+      <c r="LP1" t="inlineStr"/>
+      <c r="LQ1" t="inlineStr"/>
+      <c r="LR1" t="inlineStr"/>
+      <c r="LS1" t="inlineStr"/>
+      <c r="LT1" t="inlineStr"/>
+      <c r="LU1" t="inlineStr"/>
+      <c r="LV1" t="inlineStr"/>
+      <c r="LW1" t="inlineStr"/>
+      <c r="LX1" t="inlineStr"/>
+      <c r="LY1" t="inlineStr"/>
+      <c r="LZ1" t="inlineStr"/>
+      <c r="MA1" t="inlineStr"/>
+      <c r="MB1" t="inlineStr"/>
+      <c r="MC1" t="inlineStr"/>
+      <c r="MD1" t="inlineStr"/>
+      <c r="ME1" t="inlineStr"/>
+      <c r="MF1" t="inlineStr"/>
+      <c r="MG1" t="inlineStr"/>
+      <c r="MH1" t="inlineStr"/>
+      <c r="MI1" t="inlineStr"/>
+      <c r="MJ1" t="inlineStr"/>
+      <c r="MK1" t="inlineStr"/>
+      <c r="ML1" t="inlineStr"/>
+      <c r="MM1" t="inlineStr"/>
+      <c r="MN1" t="inlineStr"/>
+      <c r="MO1" t="inlineStr"/>
+      <c r="MP1" t="inlineStr"/>
+      <c r="MQ1" t="inlineStr"/>
+      <c r="MR1" t="inlineStr"/>
+      <c r="MS1" t="inlineStr"/>
+      <c r="MT1" t="inlineStr"/>
+      <c r="MU1" t="inlineStr"/>
+      <c r="MV1" t="inlineStr"/>
+      <c r="MW1" t="inlineStr"/>
+      <c r="MX1" t="inlineStr"/>
+      <c r="MY1" t="inlineStr"/>
+      <c r="MZ1" t="inlineStr"/>
+      <c r="NA1" t="inlineStr"/>
+      <c r="NB1" t="inlineStr"/>
+      <c r="NC1" t="inlineStr"/>
+      <c r="ND1" t="inlineStr"/>
+      <c r="NE1" t="inlineStr"/>
+      <c r="NF1" t="inlineStr"/>
+      <c r="NG1" t="inlineStr"/>
+      <c r="NH1" t="inlineStr"/>
+      <c r="NI1" t="inlineStr"/>
+      <c r="NJ1" t="inlineStr"/>
+      <c r="NK1" t="inlineStr"/>
+      <c r="NL1" t="inlineStr"/>
+      <c r="NM1" t="inlineStr"/>
+      <c r="NN1" t="inlineStr"/>
+      <c r="NO1" t="inlineStr"/>
+      <c r="NP1" t="inlineStr"/>
+      <c r="NQ1" t="inlineStr"/>
+      <c r="NR1" t="inlineStr"/>
+      <c r="NS1" t="inlineStr"/>
+      <c r="NT1" t="inlineStr"/>
+      <c r="NU1" t="inlineStr"/>
+      <c r="NV1" t="inlineStr"/>
+      <c r="NW1" t="inlineStr"/>
+      <c r="NX1" t="inlineStr"/>
+      <c r="NY1" t="inlineStr"/>
+      <c r="NZ1" t="inlineStr"/>
+      <c r="OA1" t="inlineStr"/>
+      <c r="OB1" t="inlineStr"/>
+      <c r="OC1" t="inlineStr"/>
+      <c r="OD1" t="inlineStr"/>
+      <c r="OE1" t="inlineStr"/>
+      <c r="OF1" t="inlineStr"/>
+      <c r="OG1" t="inlineStr"/>
+      <c r="OH1" t="inlineStr"/>
+      <c r="OI1" t="inlineStr"/>
+      <c r="OJ1" t="inlineStr"/>
+      <c r="OK1" t="inlineStr"/>
+      <c r="OL1" t="inlineStr"/>
+      <c r="OM1" t="inlineStr"/>
+      <c r="ON1" t="inlineStr"/>
+      <c r="OO1" t="inlineStr"/>
+      <c r="OP1" t="inlineStr"/>
+      <c r="OQ1" t="inlineStr"/>
+      <c r="OR1" t="inlineStr"/>
+      <c r="OS1" t="inlineStr"/>
+      <c r="OT1" t="inlineStr"/>
+      <c r="OU1" t="inlineStr"/>
+      <c r="OV1" t="inlineStr"/>
+      <c r="OW1" t="inlineStr"/>
+      <c r="OX1" t="inlineStr"/>
+      <c r="OY1" t="inlineStr"/>
+      <c r="OZ1" t="inlineStr"/>
+      <c r="PA1" t="inlineStr"/>
+      <c r="PB1" t="inlineStr"/>
+      <c r="PC1" t="inlineStr"/>
+      <c r="PD1" t="inlineStr"/>
+      <c r="PE1" t="inlineStr"/>
+      <c r="PF1" t="inlineStr"/>
+      <c r="PG1" t="inlineStr"/>
+      <c r="PH1" t="inlineStr"/>
+      <c r="PI1" t="inlineStr"/>
+      <c r="PJ1" t="inlineStr"/>
+      <c r="PK1" t="inlineStr"/>
+      <c r="PL1" t="inlineStr"/>
+      <c r="PM1" t="inlineStr"/>
+      <c r="PN1" t="inlineStr"/>
+      <c r="PO1" t="inlineStr"/>
+      <c r="PP1" t="inlineStr"/>
+      <c r="PQ1" t="inlineStr"/>
+      <c r="PR1" t="inlineStr"/>
+      <c r="PS1" t="inlineStr"/>
+      <c r="PT1" t="inlineStr"/>
+      <c r="PU1" t="inlineStr"/>
+      <c r="PV1" t="inlineStr"/>
+      <c r="PW1" t="inlineStr"/>
+      <c r="PX1" t="inlineStr"/>
+      <c r="PY1" t="inlineStr"/>
+      <c r="PZ1" t="inlineStr"/>
+      <c r="QA1" t="inlineStr"/>
+      <c r="QB1" t="inlineStr"/>
+      <c r="QC1" t="inlineStr"/>
+      <c r="QD1" t="inlineStr"/>
+      <c r="QE1" t="inlineStr"/>
+      <c r="QF1" t="inlineStr"/>
+      <c r="QG1" t="inlineStr"/>
+      <c r="QH1" t="inlineStr"/>
+      <c r="QI1" t="inlineStr"/>
+      <c r="QJ1" t="inlineStr"/>
+      <c r="QK1" t="inlineStr"/>
+      <c r="QL1" t="inlineStr"/>
+      <c r="QM1" t="inlineStr"/>
+      <c r="QN1" t="inlineStr"/>
+      <c r="QO1" t="inlineStr"/>
+      <c r="QP1" t="inlineStr"/>
+      <c r="QQ1" t="inlineStr"/>
+      <c r="QR1" t="inlineStr"/>
+      <c r="QS1" t="inlineStr"/>
+      <c r="QT1" t="inlineStr"/>
+      <c r="QU1" t="inlineStr"/>
+      <c r="QV1" t="inlineStr"/>
+      <c r="QW1" t="inlineStr"/>
+      <c r="QX1" t="inlineStr"/>
+      <c r="QY1" t="inlineStr"/>
+      <c r="QZ1" t="inlineStr"/>
+      <c r="RA1" t="inlineStr"/>
+      <c r="RB1" t="inlineStr"/>
+      <c r="RC1" t="inlineStr"/>
+      <c r="RD1" t="inlineStr"/>
+      <c r="RE1" t="inlineStr"/>
+      <c r="RF1" t="inlineStr"/>
+      <c r="RG1" t="inlineStr"/>
+      <c r="RH1" t="inlineStr"/>
+      <c r="RI1" t="inlineStr"/>
+      <c r="RJ1" t="inlineStr"/>
+      <c r="RK1" t="inlineStr"/>
+      <c r="RL1" t="inlineStr"/>
+      <c r="RM1" t="inlineStr"/>
+      <c r="RN1" t="inlineStr"/>
+      <c r="RO1" t="inlineStr"/>
+      <c r="RP1" t="inlineStr"/>
+      <c r="RQ1" t="inlineStr"/>
+      <c r="RR1" t="inlineStr"/>
+      <c r="RS1" t="inlineStr"/>
+      <c r="RT1" t="inlineStr"/>
+      <c r="RU1" t="inlineStr"/>
+      <c r="RV1" t="inlineStr"/>
+      <c r="RW1" t="inlineStr"/>
+      <c r="RX1" t="inlineStr"/>
+      <c r="RY1" t="inlineStr"/>
+      <c r="RZ1" t="inlineStr"/>
+      <c r="SA1" t="inlineStr"/>
+      <c r="SB1" t="inlineStr"/>
+      <c r="SC1" t="inlineStr"/>
+      <c r="SD1" t="inlineStr"/>
+      <c r="SE1" t="inlineStr"/>
+      <c r="SF1" t="inlineStr"/>
+      <c r="SG1" t="inlineStr"/>
+      <c r="SH1" t="inlineStr"/>
+      <c r="SI1" t="inlineStr"/>
+      <c r="SJ1" t="inlineStr"/>
+      <c r="SK1" t="inlineStr"/>
+      <c r="SL1" t="inlineStr"/>
+      <c r="SM1" t="inlineStr"/>
+      <c r="SN1" t="inlineStr"/>
+      <c r="SO1" t="inlineStr"/>
+      <c r="SP1" t="inlineStr"/>
+      <c r="SQ1" t="inlineStr"/>
+      <c r="SR1" t="inlineStr"/>
+      <c r="SS1" t="inlineStr"/>
+      <c r="ST1" t="inlineStr"/>
+      <c r="SU1" t="inlineStr"/>
+      <c r="SV1" t="inlineStr"/>
+      <c r="SW1" t="inlineStr"/>
+      <c r="SX1" t="inlineStr"/>
+      <c r="SY1" t="inlineStr"/>
+      <c r="SZ1" t="inlineStr"/>
+      <c r="TA1" t="inlineStr"/>
+      <c r="TB1" t="inlineStr"/>
+      <c r="TC1" t="inlineStr"/>
+      <c r="TD1" t="inlineStr"/>
+      <c r="TE1" t="inlineStr"/>
+      <c r="TF1" t="inlineStr"/>
+      <c r="TG1" t="inlineStr"/>
+      <c r="TH1" t="inlineStr"/>
+      <c r="TI1" t="inlineStr"/>
+      <c r="TJ1" t="inlineStr"/>
+      <c r="TK1" t="inlineStr"/>
+      <c r="TL1" t="inlineStr"/>
+      <c r="TM1" t="inlineStr"/>
+      <c r="TN1" t="inlineStr"/>
+      <c r="TO1" t="inlineStr"/>
+      <c r="TP1" t="inlineStr"/>
+      <c r="TQ1" t="inlineStr"/>
+      <c r="TR1" t="inlineStr"/>
+      <c r="TS1" t="inlineStr"/>
+      <c r="TT1" t="inlineStr"/>
+      <c r="TU1" t="inlineStr"/>
+      <c r="TV1" t="inlineStr"/>
+      <c r="TW1" t="inlineStr"/>
+      <c r="TX1" t="inlineStr"/>
+      <c r="TY1" t="inlineStr"/>
+      <c r="TZ1" t="inlineStr"/>
+      <c r="UA1" t="inlineStr"/>
+      <c r="UB1" t="inlineStr"/>
+      <c r="UC1" t="inlineStr"/>
+      <c r="UD1" t="inlineStr"/>
+      <c r="UE1" t="inlineStr"/>
+      <c r="UF1" t="inlineStr"/>
+      <c r="UG1" t="inlineStr"/>
+      <c r="UH1" t="inlineStr"/>
+      <c r="UI1" t="inlineStr"/>
+      <c r="UJ1" t="inlineStr"/>
+      <c r="UK1" t="inlineStr"/>
+      <c r="UL1" t="inlineStr"/>
+      <c r="UM1" t="inlineStr"/>
+      <c r="UN1" t="inlineStr"/>
+      <c r="UO1" t="inlineStr"/>
+      <c r="UP1" t="inlineStr"/>
+      <c r="UQ1" t="inlineStr"/>
+      <c r="UR1" t="inlineStr"/>
+      <c r="US1" t="inlineStr"/>
+      <c r="UT1" t="inlineStr"/>
+      <c r="UU1" t="inlineStr"/>
+      <c r="UV1" t="inlineStr"/>
+      <c r="UW1" t="inlineStr"/>
+      <c r="UX1" t="inlineStr"/>
+      <c r="UY1" t="inlineStr"/>
+      <c r="UZ1" t="inlineStr"/>
+      <c r="VA1" t="inlineStr"/>
+      <c r="VB1" t="inlineStr"/>
+      <c r="VC1" t="inlineStr"/>
+      <c r="VD1" t="inlineStr"/>
+      <c r="VE1" t="inlineStr"/>
+      <c r="VF1" t="inlineStr"/>
+      <c r="VG1" t="inlineStr"/>
+      <c r="VH1" t="inlineStr"/>
+      <c r="VI1" t="inlineStr"/>
+      <c r="VJ1" t="inlineStr"/>
+      <c r="VK1" t="inlineStr"/>
+      <c r="VL1" t="inlineStr"/>
+      <c r="VM1" t="inlineStr"/>
+      <c r="VN1" t="inlineStr"/>
+      <c r="VO1" t="inlineStr"/>
+      <c r="VP1" t="inlineStr"/>
+      <c r="VQ1" t="inlineStr"/>
+      <c r="VR1" t="inlineStr"/>
+      <c r="VS1" t="inlineStr"/>
+      <c r="VT1" t="inlineStr"/>
+      <c r="VU1" t="inlineStr"/>
+      <c r="VV1" t="inlineStr"/>
+      <c r="VW1" t="inlineStr"/>
+      <c r="VX1" t="inlineStr"/>
+      <c r="VY1" t="inlineStr"/>
+      <c r="VZ1" t="inlineStr"/>
+      <c r="WA1" t="inlineStr"/>
+      <c r="WB1" t="inlineStr"/>
+      <c r="WC1" t="inlineStr"/>
+      <c r="WD1" t="inlineStr"/>
+      <c r="WE1" t="inlineStr"/>
+      <c r="WF1" t="inlineStr"/>
+      <c r="WG1" t="inlineStr"/>
+      <c r="WH1" t="inlineStr"/>
+      <c r="WI1" t="inlineStr"/>
+      <c r="WJ1" t="inlineStr"/>
+      <c r="WK1" t="inlineStr"/>
+      <c r="WL1" t="inlineStr"/>
+      <c r="WM1" t="inlineStr"/>
+      <c r="WN1" t="inlineStr"/>
+      <c r="WO1" t="inlineStr"/>
+      <c r="WP1" t="inlineStr"/>
+      <c r="WQ1" t="inlineStr"/>
+      <c r="WR1" t="inlineStr"/>
+      <c r="WS1" t="inlineStr"/>
+      <c r="WT1" t="inlineStr"/>
+      <c r="WU1" t="inlineStr"/>
+      <c r="WV1" t="inlineStr"/>
+      <c r="WW1" t="inlineStr"/>
+      <c r="WX1" t="inlineStr"/>
+      <c r="WY1" t="inlineStr"/>
+      <c r="WZ1" t="inlineStr"/>
+      <c r="XA1" t="inlineStr"/>
+      <c r="XB1" t="inlineStr"/>
+      <c r="XC1" t="inlineStr"/>
+      <c r="XD1" t="inlineStr"/>
+      <c r="XE1" t="inlineStr"/>
+      <c r="XF1" t="inlineStr"/>
+      <c r="XG1" t="inlineStr"/>
+      <c r="XH1" t="inlineStr"/>
+      <c r="XI1" t="inlineStr"/>
+      <c r="XJ1" t="inlineStr"/>
+      <c r="XK1" t="inlineStr"/>
+      <c r="XL1" t="inlineStr"/>
+      <c r="XM1" t="inlineStr"/>
+      <c r="XN1" t="inlineStr"/>
+      <c r="XO1" t="inlineStr"/>
+      <c r="XP1" t="inlineStr"/>
+      <c r="XQ1" t="inlineStr"/>
+      <c r="XR1" t="inlineStr"/>
+      <c r="XS1" t="inlineStr"/>
+      <c r="XT1" t="inlineStr"/>
+      <c r="XU1" t="inlineStr"/>
+      <c r="XV1" t="inlineStr"/>
+      <c r="XW1" t="inlineStr"/>
+      <c r="XX1" t="inlineStr"/>
+      <c r="XY1" t="inlineStr"/>
+      <c r="XZ1" t="inlineStr"/>
+      <c r="YA1" t="inlineStr"/>
+      <c r="YB1" t="inlineStr"/>
+      <c r="YC1" t="inlineStr"/>
+      <c r="YD1" t="inlineStr"/>
+      <c r="YE1" t="inlineStr"/>
+      <c r="YF1" t="inlineStr"/>
+      <c r="YG1" t="inlineStr"/>
+      <c r="YH1" t="inlineStr"/>
+      <c r="YI1" t="inlineStr"/>
+      <c r="YJ1" t="inlineStr"/>
+      <c r="YK1" t="inlineStr"/>
+      <c r="YL1" t="inlineStr"/>
+      <c r="YM1" t="inlineStr"/>
+      <c r="YN1" t="inlineStr"/>
+      <c r="YO1" t="inlineStr"/>
+      <c r="YP1" t="inlineStr"/>
+      <c r="YQ1" t="inlineStr"/>
+      <c r="YR1" t="inlineStr"/>
+      <c r="YS1" t="inlineStr"/>
+      <c r="YT1" t="inlineStr"/>
+      <c r="YU1" t="inlineStr"/>
+      <c r="YV1" t="inlineStr"/>
+      <c r="YW1" t="inlineStr"/>
+      <c r="YX1" t="inlineStr"/>
+      <c r="YY1" t="inlineStr"/>
+      <c r="YZ1" t="inlineStr"/>
+      <c r="ZA1" t="inlineStr"/>
+      <c r="ZB1" t="inlineStr"/>
+      <c r="ZC1" t="inlineStr"/>
+      <c r="ZD1" t="inlineStr"/>
+      <c r="ZE1" t="inlineStr"/>
+      <c r="ZF1" t="inlineStr"/>
+      <c r="ZG1" t="inlineStr"/>
+      <c r="ZH1" t="inlineStr"/>
+      <c r="ZI1" t="inlineStr"/>
+      <c r="ZJ1" t="inlineStr"/>
+      <c r="ZK1" t="inlineStr"/>
+      <c r="ZL1" t="inlineStr"/>
+      <c r="ZM1" t="inlineStr"/>
+      <c r="ZN1" t="inlineStr"/>
+      <c r="ZO1" t="inlineStr"/>
+      <c r="ZP1" t="inlineStr"/>
+      <c r="ZQ1" t="inlineStr"/>
+      <c r="ZR1" t="inlineStr"/>
+      <c r="ZS1" t="inlineStr"/>
+      <c r="ZT1" t="inlineStr"/>
+      <c r="ZU1" t="inlineStr"/>
+      <c r="ZV1" t="inlineStr"/>
+      <c r="ZW1" t="inlineStr"/>
+      <c r="ZX1" t="inlineStr"/>
+      <c r="ZY1" t="inlineStr"/>
+      <c r="ZZ1" t="inlineStr"/>
+      <c r="AAA1" t="inlineStr"/>
+      <c r="AAB1" t="inlineStr"/>
+      <c r="AAC1" t="inlineStr"/>
+      <c r="AAD1" t="inlineStr"/>
+      <c r="AAE1" t="inlineStr"/>
+      <c r="AAF1" t="inlineStr"/>
+      <c r="AAG1" t="inlineStr"/>
+      <c r="AAH1" t="inlineStr"/>
+      <c r="AAI1" t="inlineStr"/>
+      <c r="AAJ1" t="inlineStr"/>
+      <c r="AAK1" t="inlineStr"/>
+      <c r="AAL1" t="inlineStr"/>
+      <c r="AAM1" t="inlineStr"/>
+      <c r="AAN1" t="inlineStr"/>
+      <c r="AAO1" t="inlineStr"/>
+      <c r="AAP1" t="inlineStr"/>
+      <c r="AAQ1" t="inlineStr"/>
+      <c r="AAR1" t="inlineStr"/>
+      <c r="AAS1" t="inlineStr"/>
+      <c r="AAT1" t="inlineStr"/>
+      <c r="AAU1" t="inlineStr"/>
+      <c r="AAV1" t="inlineStr"/>
+      <c r="AAW1" t="inlineStr"/>
+      <c r="AAX1" t="inlineStr"/>
+      <c r="AAY1" t="inlineStr"/>
+      <c r="AAZ1" t="inlineStr"/>
+      <c r="ABA1" t="inlineStr"/>
+      <c r="ABB1" t="inlineStr"/>
+      <c r="ABC1" t="inlineStr"/>
+      <c r="ABD1" t="inlineStr"/>
+      <c r="ABE1" t="inlineStr"/>
+      <c r="ABF1" t="inlineStr"/>
+      <c r="ABG1" t="inlineStr"/>
+      <c r="ABH1" t="inlineStr"/>
+      <c r="ABI1" t="inlineStr"/>
+      <c r="ABJ1" t="inlineStr"/>
+      <c r="ABK1" t="inlineStr"/>
+      <c r="ABL1" t="inlineStr"/>
+      <c r="ABM1" t="inlineStr"/>
+      <c r="ABN1" t="inlineStr"/>
+      <c r="ABO1" t="inlineStr"/>
+      <c r="ABP1" t="inlineStr"/>
+      <c r="ABQ1" t="inlineStr"/>
+      <c r="ABR1" t="inlineStr"/>
+      <c r="ABS1" t="inlineStr"/>
+      <c r="ABT1" t="inlineStr"/>
+      <c r="ABU1" t="inlineStr"/>
+      <c r="ABV1" t="inlineStr"/>
+      <c r="ABW1" t="inlineStr"/>
+      <c r="ABX1" t="inlineStr"/>
+      <c r="ABY1" t="inlineStr"/>
+      <c r="ABZ1" t="inlineStr"/>
+      <c r="ACA1" t="inlineStr"/>
+      <c r="ACB1" t="inlineStr"/>
+      <c r="ACC1" t="inlineStr"/>
+      <c r="ACD1" t="inlineStr"/>
+      <c r="ACE1" t="inlineStr"/>
+      <c r="ACF1" t="inlineStr"/>
+      <c r="ACG1" t="inlineStr"/>
+      <c r="ACH1" t="inlineStr"/>
+      <c r="ACI1" t="inlineStr"/>
+      <c r="ACJ1" t="inlineStr"/>
+      <c r="ACK1" t="inlineStr"/>
+      <c r="ACL1" t="inlineStr"/>
+      <c r="ACM1" t="inlineStr"/>
+      <c r="ACN1" t="inlineStr"/>
+      <c r="ACO1" t="inlineStr"/>
+      <c r="ACP1" t="inlineStr"/>
+      <c r="ACQ1" t="inlineStr"/>
+      <c r="ACR1" t="inlineStr"/>
+      <c r="ACS1" t="inlineStr"/>
+      <c r="ACT1" t="inlineStr"/>
+      <c r="ACU1" t="inlineStr"/>
+      <c r="ACV1" t="inlineStr"/>
+      <c r="ACW1" t="inlineStr"/>
+      <c r="ACX1" t="inlineStr"/>
+      <c r="ACY1" t="inlineStr"/>
+      <c r="ACZ1" t="inlineStr"/>
+      <c r="ADA1" t="inlineStr"/>
+      <c r="ADB1" t="inlineStr"/>
+      <c r="ADC1" t="inlineStr"/>
+      <c r="ADD1" t="inlineStr"/>
+      <c r="ADE1" t="inlineStr"/>
+      <c r="ADF1" t="inlineStr"/>
+      <c r="ADG1" t="inlineStr"/>
+      <c r="ADH1" t="inlineStr"/>
+      <c r="ADI1" t="inlineStr"/>
+      <c r="ADJ1" t="inlineStr"/>
+      <c r="ADK1" t="inlineStr"/>
+      <c r="ADL1" t="inlineStr"/>
+      <c r="ADM1" t="inlineStr"/>
+      <c r="ADN1" t="inlineStr"/>
+      <c r="ADO1" t="inlineStr"/>
+      <c r="ADP1" t="inlineStr"/>
+      <c r="ADQ1" t="inlineStr"/>
+      <c r="ADR1" t="inlineStr"/>
+      <c r="ADS1" t="inlineStr"/>
+      <c r="ADT1" t="inlineStr"/>
+      <c r="ADU1" t="inlineStr"/>
+      <c r="ADV1" t="inlineStr"/>
+      <c r="ADW1" t="inlineStr"/>
+      <c r="ADX1" t="inlineStr"/>
+      <c r="ADY1" t="inlineStr"/>
+      <c r="ADZ1" t="inlineStr"/>
+      <c r="AEA1" t="inlineStr"/>
+      <c r="AEB1" t="inlineStr"/>
+      <c r="AEC1" t="inlineStr"/>
+      <c r="AED1" t="inlineStr"/>
+      <c r="AEE1" t="inlineStr"/>
+      <c r="AEF1" t="inlineStr"/>
+      <c r="AEG1" t="inlineStr"/>
+      <c r="AEH1" t="inlineStr"/>
+      <c r="AEI1" t="inlineStr"/>
+      <c r="AEJ1" t="inlineStr"/>
+      <c r="AEK1" t="inlineStr"/>
+      <c r="AEL1" t="inlineStr"/>
+      <c r="AEM1" t="inlineStr"/>
+      <c r="AEN1" t="inlineStr"/>
+      <c r="AEO1" t="inlineStr"/>
+      <c r="AEP1" t="inlineStr"/>
+      <c r="AEQ1" t="inlineStr"/>
+      <c r="AER1" t="inlineStr"/>
+      <c r="AES1" t="inlineStr"/>
+      <c r="AET1" t="inlineStr"/>
+      <c r="AEU1" t="inlineStr"/>
+      <c r="AEV1" t="inlineStr"/>
+      <c r="AEW1" t="inlineStr"/>
+      <c r="AEX1" t="inlineStr"/>
+      <c r="AEY1" t="inlineStr"/>
+      <c r="AEZ1" t="inlineStr"/>
+      <c r="AFA1" t="inlineStr"/>
+      <c r="AFB1" t="inlineStr"/>
+      <c r="AFC1" t="inlineStr"/>
+      <c r="AFD1" t="inlineStr"/>
+      <c r="AFE1" t="inlineStr"/>
+      <c r="AFF1" t="inlineStr"/>
+      <c r="AFG1" t="inlineStr"/>
+      <c r="AFH1" t="inlineStr"/>
+      <c r="AFI1" t="inlineStr"/>
+      <c r="AFJ1" t="inlineStr"/>
+      <c r="AFK1" t="inlineStr"/>
+      <c r="AFL1" t="inlineStr"/>
+      <c r="AFM1" t="inlineStr"/>
+      <c r="AFN1" t="inlineStr"/>
+      <c r="AFO1" t="inlineStr"/>
+      <c r="AFP1" t="inlineStr"/>
+      <c r="AFQ1" t="inlineStr"/>
+      <c r="AFR1" t="inlineStr"/>
+      <c r="AFS1" t="inlineStr"/>
+      <c r="AFT1" t="inlineStr"/>
+      <c r="AFU1" t="inlineStr"/>
+      <c r="AFV1" t="inlineStr"/>
+      <c r="AFW1" t="inlineStr"/>
+      <c r="AFX1" t="inlineStr"/>
+      <c r="AFY1" t="inlineStr"/>
+      <c r="AFZ1" t="inlineStr"/>
+      <c r="AGA1" t="inlineStr"/>
+      <c r="AGB1" t="inlineStr"/>
+      <c r="AGC1" t="inlineStr"/>
+      <c r="AGD1" t="inlineStr"/>
+      <c r="AGE1" t="inlineStr"/>
+      <c r="AGF1" t="inlineStr"/>
+      <c r="AGG1" t="inlineStr"/>
+      <c r="AGH1" t="inlineStr"/>
+      <c r="AGI1" t="inlineStr"/>
+      <c r="AGJ1" t="inlineStr"/>
+      <c r="AGK1" t="inlineStr"/>
+      <c r="AGL1" t="inlineStr"/>
+      <c r="AGM1" t="inlineStr"/>
+      <c r="AGN1" t="inlineStr"/>
+      <c r="AGO1" t="inlineStr"/>
+      <c r="AGP1" t="inlineStr"/>
+      <c r="AGQ1" t="inlineStr"/>
+      <c r="AGR1" t="inlineStr"/>
+      <c r="AGS1" t="inlineStr"/>
+      <c r="AGT1" t="inlineStr"/>
+      <c r="AGU1" t="inlineStr"/>
+      <c r="AGV1" t="inlineStr"/>
+      <c r="AGW1" t="inlineStr"/>
+      <c r="AGX1" t="inlineStr"/>
+      <c r="AGY1" t="inlineStr"/>
+      <c r="AGZ1" t="inlineStr"/>
+      <c r="AHA1" t="inlineStr"/>
+      <c r="AHB1" t="inlineStr"/>
+      <c r="AHC1" t="inlineStr"/>
+      <c r="AHD1" t="inlineStr"/>
+      <c r="AHE1" t="inlineStr"/>
+      <c r="AHF1" t="inlineStr"/>
+      <c r="AHG1" t="inlineStr"/>
+      <c r="AHH1" t="inlineStr"/>
+      <c r="AHI1" t="inlineStr"/>
+      <c r="AHJ1" t="inlineStr"/>
+      <c r="AHK1" t="inlineStr"/>
+      <c r="AHL1" t="inlineStr"/>
+      <c r="AHM1" t="inlineStr"/>
+      <c r="AHN1" t="inlineStr"/>
+      <c r="AHO1" t="inlineStr"/>
+      <c r="AHP1" t="inlineStr"/>
+      <c r="AHQ1" t="inlineStr"/>
+      <c r="AHR1" t="inlineStr"/>
+      <c r="AHS1" t="inlineStr"/>
+      <c r="AHT1" t="inlineStr"/>
+      <c r="AHU1" t="inlineStr"/>
+      <c r="AHV1" t="inlineStr"/>
+      <c r="AHW1" t="inlineStr"/>
+      <c r="AHX1" t="inlineStr"/>
+      <c r="AHY1" t="inlineStr"/>
+      <c r="AHZ1" t="inlineStr"/>
+      <c r="AIA1" t="inlineStr"/>
+      <c r="AIB1" t="inlineStr"/>
+      <c r="AIC1" t="inlineStr"/>
+      <c r="AID1" t="inlineStr"/>
+      <c r="AIE1" t="inlineStr"/>
+      <c r="AIF1" t="inlineStr"/>
+      <c r="AIG1" t="inlineStr"/>
+      <c r="AIH1" t="inlineStr"/>
+      <c r="AII1" t="inlineStr"/>
+      <c r="AIJ1" t="inlineStr"/>
+      <c r="AIK1" t="inlineStr"/>
+      <c r="AIL1" t="inlineStr"/>
+      <c r="AIM1" t="inlineStr"/>
+      <c r="AIN1" t="inlineStr"/>
+      <c r="AIO1" t="inlineStr"/>
+      <c r="AIP1" t="inlineStr"/>
+      <c r="AIQ1" t="inlineStr"/>
+      <c r="AIR1" t="inlineStr"/>
+      <c r="AIS1" t="inlineStr"/>
+      <c r="AIT1" t="inlineStr"/>
+      <c r="AIU1" t="inlineStr"/>
+      <c r="AIV1" t="inlineStr"/>
+      <c r="AIW1" t="inlineStr"/>
+      <c r="AIX1" t="inlineStr"/>
+      <c r="AIY1" t="inlineStr"/>
+      <c r="AIZ1" t="inlineStr"/>
+      <c r="AJA1" t="inlineStr"/>
+      <c r="AJB1" t="inlineStr"/>
+      <c r="AJC1" t="inlineStr"/>
+      <c r="AJD1" t="inlineStr"/>
+      <c r="AJE1" t="inlineStr"/>
+      <c r="AJF1" t="inlineStr"/>
+      <c r="AJG1" t="inlineStr"/>
+      <c r="AJH1" t="inlineStr"/>
+      <c r="AJI1" t="inlineStr"/>
+      <c r="AJJ1" t="inlineStr"/>
+      <c r="AJK1" t="inlineStr"/>
+      <c r="AJL1" t="inlineStr"/>
+      <c r="AJM1" t="inlineStr"/>
+      <c r="AJN1" t="inlineStr"/>
+      <c r="AJO1" t="inlineStr"/>
+      <c r="AJP1" t="inlineStr"/>
+      <c r="AJQ1" t="inlineStr"/>
+      <c r="AJR1" t="inlineStr"/>
+      <c r="AJS1" t="inlineStr"/>
+      <c r="AJT1" t="inlineStr"/>
+      <c r="AJU1" t="inlineStr"/>
+      <c r="AJV1" t="inlineStr"/>
+      <c r="AJW1" t="inlineStr"/>
+      <c r="AJX1" t="inlineStr"/>
+      <c r="AJY1" t="inlineStr"/>
+      <c r="AJZ1" t="inlineStr"/>
+      <c r="AKA1" t="inlineStr"/>
+      <c r="AKB1" t="inlineStr"/>
+      <c r="AKC1" t="inlineStr"/>
+      <c r="AKD1" t="inlineStr"/>
+      <c r="AKE1" t="inlineStr"/>
+      <c r="AKF1" t="inlineStr"/>
+      <c r="AKG1" t="inlineStr"/>
+      <c r="AKH1" t="inlineStr"/>
+      <c r="AKI1" t="inlineStr"/>
+      <c r="AKJ1" t="inlineStr"/>
+      <c r="AKK1" t="inlineStr"/>
+      <c r="AKL1" t="inlineStr"/>
+      <c r="AKM1" t="inlineStr"/>
+      <c r="AKN1" t="inlineStr"/>
+      <c r="AKO1" t="inlineStr"/>
+      <c r="AKP1" t="inlineStr"/>
+      <c r="AKQ1" t="inlineStr"/>
+      <c r="AKR1" t="inlineStr"/>
+      <c r="AKS1" t="inlineStr"/>
+      <c r="AKT1" t="inlineStr"/>
+      <c r="AKU1" t="inlineStr"/>
+      <c r="AKV1" t="inlineStr"/>
+      <c r="AKW1" t="inlineStr"/>
+      <c r="AKX1" t="inlineStr"/>
+      <c r="AKY1" t="inlineStr"/>
+      <c r="AKZ1" t="inlineStr"/>
+      <c r="ALA1" t="inlineStr"/>
+      <c r="ALB1" t="inlineStr"/>
+      <c r="ALC1" t="inlineStr"/>
+      <c r="ALD1" t="inlineStr"/>
+      <c r="ALE1" t="inlineStr"/>
+      <c r="ALF1" t="inlineStr"/>
+      <c r="ALG1" t="inlineStr"/>
+      <c r="ALH1" t="inlineStr"/>
+      <c r="ALI1" t="inlineStr"/>
+      <c r="ALJ1" t="inlineStr"/>
+      <c r="ALK1" t="inlineStr"/>
+      <c r="ALL1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1041527</v>
+      </c>
+      <c r="B2" t="n">
+        <v>291193</v>
+      </c>
+      <c r="C2" t="n">
+        <v>623361</v>
+      </c>
+      <c r="D2" t="n">
+        <v>190866</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36981</v>
+      </c>
+      <c r="F2" t="n">
+        <v>178554</v>
+      </c>
+      <c r="G2" t="n">
+        <v>989593</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4391</v>
+      </c>
+      <c r="I2" t="n">
+        <v>281255</v>
+      </c>
+      <c r="J2" t="n">
+        <v>599782</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1112257</v>
+      </c>
+      <c r="L2" t="n">
+        <v>939146</v>
+      </c>
+      <c r="M2" t="n">
+        <v>714150</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1036754</v>
+      </c>
+      <c r="O2" t="n">
+        <v>964178</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1067111</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>650581</v>
+      </c>
+      <c r="R2" t="n">
+        <v>948341</v>
+      </c>
+      <c r="S2" t="n">
+        <v>161530</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1079654</v>
+      </c>
+      <c r="U2" t="n">
+        <v>118832</v>
+      </c>
+      <c r="V2" t="n">
+        <v>963157</v>
+      </c>
+      <c r="W2" t="n">
+        <v>210976</v>
+      </c>
+      <c r="X2" t="n">
+        <v>118353</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>266606</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>338163</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>593392</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>331403</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>83040</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2061</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>174631</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>429774</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>137552</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>870013</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>185526</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>694362</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>582988</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>152827</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>943317</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>595668</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>132079</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>744748</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1041100</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>628175</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1147614</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>943127</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>219837</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1058817</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>177515</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>682122</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>47981</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1176468</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>368133</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>621975</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>737922</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>982354</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>37498</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>15978</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1108346</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>172342</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>157347</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>154978</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1174727</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>620406</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1111703</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1003034</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>219671</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>874049</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>762079</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>8229</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>399346</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>3769</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>13920</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1182657</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>235862</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1066397</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>595399</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>1043318</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>274805</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>770855</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>1004477</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>1071430</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>802799</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>609310</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>949663</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>910344</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>458146</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>58689</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>310854</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>917844</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>258464</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>112013</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>997775</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>69185</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>423857</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>162496</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>39516</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>1051868</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>718292</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>644242</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>773766</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>501498</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>1191740</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>1136935</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>46721</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>787365</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>743397</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>29293</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>503312</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>117092</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>298435</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>717110</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>838692</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>420491</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>373131</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>667018</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>305977</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>144934</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1128655</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>417062</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>614788</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1117295</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>992840</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>999131</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>795538</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>573370</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>171277</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>219894</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>489825</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>507412</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>683544</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>465207</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>77394</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>733185</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>34850</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>1059492</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>25075</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>190126</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>1144767</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>20742</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>535128</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>757621</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>427286</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>683371</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>1822</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>1174341</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>901580</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>972941</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>553975</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>514064</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>702640</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>843861</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>854896</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>845831</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>231488</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>299143</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>818882</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>1135396</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>1120682</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>643587</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>470054</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>247278</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>169624</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>439465</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>133336</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>1093435</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>837896</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>746683</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>464233</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>1030409</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>807036</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>741354</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>862403</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>55479</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>86331</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>500676</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>1024105</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>725844</v>
+      </c>
+      <c r="FX2" t="n">
+        <v>1115110</v>
+      </c>
+      <c r="FY2" t="n">
+        <v>656988</v>
+      </c>
+      <c r="FZ2" t="n">
+        <v>851121</v>
+      </c>
+      <c r="GA2" t="n">
+        <v>800463</v>
+      </c>
+      <c r="GB2" t="n">
+        <v>422036</v>
+      </c>
+      <c r="GC2" t="n">
+        <v>692005</v>
+      </c>
+      <c r="GD2" t="n">
+        <v>181285</v>
+      </c>
+      <c r="GE2" t="n">
+        <v>824298</v>
+      </c>
+      <c r="GF2" t="n">
+        <v>18129</v>
+      </c>
+      <c r="GG2" t="n">
+        <v>718096</v>
+      </c>
+      <c r="GH2" t="n">
+        <v>241259</v>
+      </c>
+      <c r="GI2" t="n">
+        <v>207364</v>
+      </c>
+      <c r="GJ2" t="n">
+        <v>1131133</v>
+      </c>
+      <c r="GK2" t="n">
+        <v>995125</v>
+      </c>
+      <c r="GL2" t="n">
+        <v>279066</v>
+      </c>
+      <c r="GM2" t="n">
+        <v>885285</v>
+      </c>
+      <c r="GN2" t="n">
+        <v>1073149</v>
+      </c>
+      <c r="GO2" t="n">
+        <v>358622</v>
+      </c>
+      <c r="GP2" t="n">
+        <v>234553</v>
+      </c>
+      <c r="GQ2" t="n">
+        <v>198080</v>
+      </c>
+      <c r="GR2" t="n">
+        <v>21157</v>
+      </c>
+      <c r="GS2" t="n">
+        <v>313881</v>
+      </c>
+      <c r="GT2" t="n">
+        <v>386699</v>
+      </c>
+      <c r="GU2" t="n">
+        <v>724237</v>
+      </c>
+      <c r="GV2" t="n">
+        <v>788679</v>
+      </c>
+      <c r="GW2" t="n">
+        <v>912486</v>
+      </c>
+      <c r="GX2" t="n">
+        <v>723284</v>
+      </c>
+      <c r="GY2" t="n">
+        <v>1043389</v>
+      </c>
+      <c r="GZ2" t="n">
+        <v>59061</v>
+      </c>
+      <c r="HA2" t="n">
+        <v>317506</v>
+      </c>
+      <c r="HB2" t="n">
+        <v>114942</v>
+      </c>
+      <c r="HC2" t="n">
+        <v>1117277</v>
+      </c>
+      <c r="HD2" t="n">
+        <v>469125</v>
+      </c>
+      <c r="HE2" t="n">
+        <v>765470</v>
+      </c>
+      <c r="HF2" t="n">
+        <v>273394</v>
+      </c>
+      <c r="HG2" t="n">
+        <v>350815</v>
+      </c>
+      <c r="HH2" t="n">
+        <v>696814</v>
+      </c>
+      <c r="HI2" t="n">
+        <v>319744</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>356337</v>
+      </c>
+      <c r="HK2" t="n">
+        <v>940621</v>
+      </c>
+      <c r="HL2" t="n">
+        <v>266232</v>
+      </c>
+      <c r="HM2" t="n">
+        <v>326241</v>
+      </c>
+      <c r="HN2" t="n">
+        <v>629805</v>
+      </c>
+      <c r="HO2" t="n">
+        <v>563916</v>
+      </c>
+      <c r="HP2" t="n">
+        <v>387655</v>
+      </c>
+      <c r="HQ2" t="n">
+        <v>379267</v>
+      </c>
+      <c r="HR2" t="n">
+        <v>303485</v>
+      </c>
+      <c r="HS2" t="n">
+        <v>126058</v>
+      </c>
+      <c r="HT2" t="n">
+        <v>797386</v>
+      </c>
+      <c r="HU2" t="n">
+        <v>617534</v>
+      </c>
+      <c r="HV2" t="n">
+        <v>775339</v>
+      </c>
+      <c r="HW2" t="n">
+        <v>231319</v>
+      </c>
+      <c r="HX2" t="n">
+        <v>882174</v>
+      </c>
+      <c r="HY2" t="n">
+        <v>962977</v>
+      </c>
+      <c r="HZ2" t="n">
+        <v>23466</v>
+      </c>
+      <c r="IA2" t="n">
+        <v>248911</v>
+      </c>
+      <c r="IB2" t="n">
+        <v>727928</v>
+      </c>
+      <c r="IC2" t="n">
+        <v>1087058</v>
+      </c>
+      <c r="ID2" t="n">
+        <v>856198</v>
+      </c>
+      <c r="IE2" t="n">
+        <v>565348</v>
+      </c>
+      <c r="IF2" t="n">
+        <v>282714</v>
+      </c>
+      <c r="IG2" t="n">
+        <v>45094</v>
+      </c>
+      <c r="IH2" t="n">
+        <v>919106</v>
+      </c>
+      <c r="II2" t="n">
+        <v>194071</v>
+      </c>
+      <c r="IJ2" t="n">
+        <v>663324</v>
+      </c>
+      <c r="IK2" t="n">
+        <v>664327</v>
+      </c>
+      <c r="IL2" t="n">
+        <v>984909</v>
+      </c>
+      <c r="IM2" t="n">
+        <v>910752</v>
+      </c>
+      <c r="IN2" t="n">
+        <v>154146</v>
+      </c>
+      <c r="IO2" t="n">
+        <v>166571</v>
+      </c>
+      <c r="IP2" t="n">
+        <v>719433</v>
+      </c>
+      <c r="IQ2" t="n">
+        <v>233554</v>
+      </c>
+      <c r="IR2" t="n">
+        <v>424704</v>
+      </c>
+      <c r="IS2" t="n">
+        <v>943905</v>
+      </c>
+      <c r="IT2" t="n">
+        <v>251129</v>
+      </c>
+      <c r="IU2" t="n">
+        <v>816168</v>
+      </c>
+      <c r="IV2" t="n">
+        <v>328325</v>
+      </c>
+      <c r="IW2" t="n">
+        <v>815978</v>
+      </c>
+      <c r="IX2" t="n">
+        <v>725602</v>
+      </c>
+      <c r="IY2" t="n">
+        <v>454765</v>
+      </c>
+      <c r="IZ2" t="n">
+        <v>413742</v>
+      </c>
+      <c r="JA2" t="n">
+        <v>1014294</v>
+      </c>
+      <c r="JB2" t="n">
+        <v>493923</v>
+      </c>
+      <c r="JC2" t="n">
+        <v>929103</v>
+      </c>
+      <c r="JD2" t="n">
+        <v>751806</v>
+      </c>
+      <c r="JE2" t="n">
+        <v>487853</v>
+      </c>
+      <c r="JF2" t="n">
+        <v>976636</v>
+      </c>
+      <c r="JG2" t="n">
+        <v>412094</v>
+      </c>
+      <c r="JH2" t="n">
+        <v>1162479</v>
+      </c>
+      <c r="JI2" t="n">
+        <v>639505</v>
+      </c>
+      <c r="JJ2" t="n">
+        <v>1026291</v>
+      </c>
+      <c r="JK2" t="n">
+        <v>1090058</v>
+      </c>
+      <c r="JL2" t="n">
+        <v>559350</v>
+      </c>
+      <c r="JM2" t="n">
+        <v>590426</v>
+      </c>
+      <c r="JN2" t="n">
+        <v>1088854</v>
+      </c>
+      <c r="JO2" t="n">
+        <v>625716</v>
+      </c>
+      <c r="JP2" t="n">
+        <v>975363</v>
+      </c>
+      <c r="JQ2" t="n">
+        <v>1052326</v>
+      </c>
+      <c r="JR2" t="n">
+        <v>301759</v>
+      </c>
+      <c r="JS2" t="n">
+        <v>143361</v>
+      </c>
+      <c r="JT2" t="n">
+        <v>361701</v>
+      </c>
+      <c r="JU2" t="n">
+        <v>1078800</v>
+      </c>
+      <c r="JV2" t="n">
+        <v>107575</v>
+      </c>
+      <c r="JW2" t="n">
+        <v>829075</v>
+      </c>
+      <c r="JX2" t="n">
+        <v>1052663</v>
+      </c>
+      <c r="JY2" t="n">
+        <v>97293</v>
+      </c>
+      <c r="JZ2" t="n">
+        <v>409580</v>
+      </c>
+      <c r="KA2" t="n">
+        <v>987057</v>
+      </c>
+      <c r="KB2" t="n">
+        <v>992014</v>
+      </c>
+      <c r="KC2" t="n">
+        <v>468225</v>
+      </c>
+      <c r="KD2" t="n">
+        <v>380176</v>
+      </c>
+      <c r="KE2" t="n">
+        <v>825642</v>
+      </c>
+      <c r="KF2" t="n">
+        <v>43159</v>
+      </c>
+      <c r="KG2" t="n">
+        <v>530615</v>
+      </c>
+      <c r="KH2" t="n">
+        <v>977464</v>
+      </c>
+      <c r="KI2" t="n">
+        <v>1029764</v>
+      </c>
+      <c r="KJ2" t="n">
+        <v>349159</v>
+      </c>
+      <c r="KK2" t="n">
+        <v>127507</v>
+      </c>
+      <c r="KL2" t="n">
+        <v>482729</v>
+      </c>
+      <c r="KM2" t="n">
+        <v>996079</v>
+      </c>
+      <c r="KN2" t="n">
+        <v>1061436</v>
+      </c>
+      <c r="KO2" t="n">
+        <v>655222</v>
+      </c>
+      <c r="KP2" t="n">
+        <v>383449</v>
+      </c>
+      <c r="KQ2" t="n">
+        <v>1113054</v>
+      </c>
+      <c r="KR2" t="n">
+        <v>654130</v>
+      </c>
+      <c r="KS2" t="n">
+        <v>338436</v>
+      </c>
+      <c r="KT2" t="n">
+        <v>402324</v>
+      </c>
+      <c r="KU2" t="n">
+        <v>384850</v>
+      </c>
+      <c r="KV2" t="n">
+        <v>473891</v>
+      </c>
+      <c r="KW2" t="n">
+        <v>473082</v>
+      </c>
+      <c r="KX2" t="n">
+        <v>360057</v>
+      </c>
+      <c r="KY2" t="n">
+        <v>820946</v>
+      </c>
+      <c r="KZ2" t="n">
+        <v>1061623</v>
+      </c>
+      <c r="LA2" t="n">
+        <v>227138</v>
+      </c>
+      <c r="LB2" t="n">
+        <v>995892</v>
+      </c>
+      <c r="LC2" t="n">
+        <v>1012501</v>
+      </c>
+      <c r="LD2" t="n">
+        <v>166655</v>
+      </c>
+      <c r="LE2" t="n">
+        <v>88186</v>
+      </c>
+      <c r="LF2" t="n">
+        <v>32046</v>
+      </c>
+      <c r="LG2" t="n">
+        <v>202509</v>
+      </c>
+      <c r="LH2" t="n">
+        <v>1108092</v>
+      </c>
+      <c r="LI2" t="n">
+        <v>754950</v>
+      </c>
+      <c r="LJ2" t="n">
+        <v>520109</v>
+      </c>
+      <c r="LK2" t="n">
+        <v>208139</v>
+      </c>
+      <c r="LL2" t="n">
+        <v>684289</v>
+      </c>
+      <c r="LM2" t="n">
+        <v>580600</v>
+      </c>
+      <c r="LN2" t="n">
+        <v>1200796</v>
+      </c>
+      <c r="LO2" t="n">
+        <v>304118</v>
+      </c>
+      <c r="LP2" t="n">
+        <v>374316</v>
+      </c>
+      <c r="LQ2" t="n">
+        <v>1033439</v>
+      </c>
+      <c r="LR2" t="n">
+        <v>405972</v>
+      </c>
+      <c r="LS2" t="n">
+        <v>865614</v>
+      </c>
+      <c r="LT2" t="n">
+        <v>28250</v>
+      </c>
+      <c r="LU2" t="n">
+        <v>687878</v>
+      </c>
+      <c r="LV2" t="n">
+        <v>1036328</v>
+      </c>
+      <c r="LW2" t="n">
+        <v>395070</v>
+      </c>
+      <c r="LX2" t="n">
+        <v>1152385</v>
+      </c>
+      <c r="LY2" t="n">
+        <v>761330</v>
+      </c>
+      <c r="LZ2" t="n">
+        <v>505525</v>
+      </c>
+      <c r="MA2" t="n">
+        <v>1019449</v>
+      </c>
+      <c r="MB2" t="n">
+        <v>184654</v>
+      </c>
+      <c r="MC2" t="n">
+        <v>793212</v>
+      </c>
+      <c r="MD2" t="n">
+        <v>462058</v>
+      </c>
+      <c r="ME2" t="n">
+        <v>345056</v>
+      </c>
+      <c r="MF2" t="n">
+        <v>390020</v>
+      </c>
+      <c r="MG2" t="n">
+        <v>403062</v>
+      </c>
+      <c r="MH2" t="n">
+        <v>878634</v>
+      </c>
+      <c r="MI2" t="n">
+        <v>738989</v>
+      </c>
+      <c r="MJ2" t="n">
+        <v>914006</v>
+      </c>
+      <c r="MK2" t="n">
+        <v>862852</v>
+      </c>
+      <c r="ML2" t="n">
+        <v>159441</v>
+      </c>
+      <c r="MM2" t="n">
+        <v>176643</v>
+      </c>
+      <c r="MN2" t="n">
+        <v>1010319</v>
+      </c>
+      <c r="MO2" t="n">
+        <v>938756</v>
+      </c>
+      <c r="MP2" t="n">
+        <v>354491</v>
+      </c>
+      <c r="MQ2" t="n">
+        <v>907534</v>
+      </c>
+      <c r="MR2" t="n">
+        <v>658106</v>
+      </c>
+      <c r="MS2" t="n">
+        <v>778824</v>
+      </c>
+      <c r="MT2" t="n">
+        <v>714020</v>
+      </c>
+      <c r="MU2" t="n">
+        <v>930451</v>
+      </c>
+      <c r="MV2" t="n">
+        <v>960101</v>
+      </c>
+      <c r="MW2" t="n">
+        <v>857111</v>
+      </c>
+      <c r="MX2" t="n">
+        <v>94454</v>
+      </c>
+      <c r="MY2" t="n">
+        <v>17438</v>
+      </c>
+      <c r="MZ2" t="n">
+        <v>99988</v>
+      </c>
+      <c r="NA2" t="n">
+        <v>271923</v>
+      </c>
+      <c r="NB2" t="n">
+        <v>284233</v>
+      </c>
+      <c r="NC2" t="n">
+        <v>1000880</v>
+      </c>
+      <c r="ND2" t="n">
+        <v>898636</v>
+      </c>
+      <c r="NE2" t="n">
+        <v>954103</v>
+      </c>
+      <c r="NF2" t="n">
+        <v>485859</v>
+      </c>
+      <c r="NG2" t="n">
+        <v>428710</v>
+      </c>
+      <c r="NH2" t="n">
+        <v>229403</v>
+      </c>
+      <c r="NI2" t="n">
+        <v>1099232</v>
+      </c>
+      <c r="NJ2" t="n">
+        <v>76058</v>
+      </c>
+      <c r="NK2" t="n">
+        <v>86430</v>
+      </c>
+      <c r="NL2" t="n">
+        <v>806347</v>
+      </c>
+      <c r="NM2" t="n">
+        <v>23472</v>
+      </c>
+      <c r="NN2" t="n">
+        <v>55276</v>
+      </c>
+      <c r="NO2" t="n">
+        <v>24837</v>
+      </c>
+      <c r="NP2" t="n">
+        <v>967055</v>
+      </c>
+      <c r="NQ2" t="n">
+        <v>478817</v>
+      </c>
+      <c r="NR2" t="n">
+        <v>254538</v>
+      </c>
+      <c r="NS2" t="n">
+        <v>106506</v>
+      </c>
+      <c r="NT2" t="n">
+        <v>66966</v>
+      </c>
+      <c r="NU2" t="n">
+        <v>1183656</v>
+      </c>
+      <c r="NV2" t="n">
+        <v>826369</v>
+      </c>
+      <c r="NW2" t="n">
+        <v>161443</v>
+      </c>
+      <c r="NX2" t="n">
+        <v>259168</v>
+      </c>
+      <c r="NY2" t="n">
+        <v>34151</v>
+      </c>
+      <c r="NZ2" t="n">
+        <v>375013</v>
+      </c>
+      <c r="OA2" t="n">
+        <v>1191368</v>
+      </c>
+      <c r="OB2" t="n">
+        <v>323704</v>
+      </c>
+      <c r="OC2" t="n">
+        <v>1128965</v>
+      </c>
+      <c r="OD2" t="n">
+        <v>1069449</v>
+      </c>
+      <c r="OE2" t="n">
+        <v>1193239</v>
+      </c>
+      <c r="OF2" t="n">
+        <v>652491</v>
+      </c>
+      <c r="OG2" t="n">
+        <v>728631</v>
+      </c>
+      <c r="OH2" t="n">
+        <v>142936</v>
+      </c>
+      <c r="OI2" t="n">
+        <v>852771</v>
+      </c>
+      <c r="OJ2" t="n">
+        <v>15955</v>
+      </c>
+      <c r="OK2" t="n">
+        <v>1139192</v>
+      </c>
+      <c r="OL2" t="n">
+        <v>1197503</v>
+      </c>
+      <c r="OM2" t="n">
+        <v>897190</v>
+      </c>
+      <c r="ON2" t="n">
+        <v>587503</v>
+      </c>
+      <c r="OO2" t="n">
+        <v>1038835</v>
+      </c>
+      <c r="OP2" t="n">
+        <v>1180184</v>
+      </c>
+      <c r="OQ2" t="n">
+        <v>166266</v>
+      </c>
+      <c r="OR2" t="n">
+        <v>182703</v>
+      </c>
+      <c r="OS2" t="n">
+        <v>148493</v>
+      </c>
+      <c r="OT2" t="n">
+        <v>772119</v>
+      </c>
+      <c r="OU2" t="n">
+        <v>678647</v>
+      </c>
+      <c r="OV2" t="n">
+        <v>236740</v>
+      </c>
+      <c r="OW2" t="n">
+        <v>1159297</v>
+      </c>
+      <c r="OX2" t="n">
+        <v>674064</v>
+      </c>
+      <c r="OY2" t="n">
+        <v>78636</v>
+      </c>
+      <c r="OZ2" t="n">
+        <v>665034</v>
+      </c>
+      <c r="PA2" t="n">
+        <v>61084</v>
+      </c>
+      <c r="PB2" t="n">
+        <v>892529</v>
+      </c>
+      <c r="PC2" t="n">
+        <v>915777</v>
+      </c>
+      <c r="PD2" t="n">
+        <v>471626</v>
+      </c>
+      <c r="PE2" t="n">
+        <v>531059</v>
+      </c>
+      <c r="PF2" t="n">
+        <v>609700</v>
+      </c>
+      <c r="PG2" t="n">
+        <v>245218</v>
+      </c>
+      <c r="PH2" t="n">
+        <v>831406</v>
+      </c>
+      <c r="PI2" t="n">
+        <v>551229</v>
+      </c>
+      <c r="PJ2" t="n">
+        <v>424222</v>
+      </c>
+      <c r="PK2" t="n">
+        <v>614046</v>
+      </c>
+      <c r="PL2" t="n">
+        <v>1018265</v>
+      </c>
+      <c r="PM2" t="n">
+        <v>749397</v>
+      </c>
+      <c r="PN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="PO2" t="n">
+        <v>732882</v>
+      </c>
+      <c r="PP2" t="n">
+        <v>916645</v>
+      </c>
+      <c r="PQ2" t="n">
+        <v>178535</v>
+      </c>
+      <c r="PR2" t="n">
+        <v>1027903</v>
+      </c>
+      <c r="PS2" t="n">
+        <v>523606</v>
+      </c>
+      <c r="PT2" t="n">
+        <v>1155311</v>
+      </c>
+      <c r="PU2" t="n">
+        <v>550310</v>
+      </c>
+      <c r="PV2" t="n">
+        <v>84786</v>
+      </c>
+      <c r="PW2" t="n">
+        <v>112108</v>
+      </c>
+      <c r="PX2" t="n">
+        <v>13290</v>
+      </c>
+      <c r="PY2" t="n">
+        <v>1003358</v>
+      </c>
+      <c r="PZ2" t="n">
+        <v>309325</v>
+      </c>
+      <c r="QA2" t="n">
+        <v>172636</v>
+      </c>
+      <c r="QB2" t="n">
+        <v>925738</v>
+      </c>
+      <c r="QC2" t="n">
+        <v>921108</v>
+      </c>
+      <c r="QD2" t="n">
+        <v>669402</v>
+      </c>
+      <c r="QE2" t="n">
+        <v>1162760</v>
+      </c>
+      <c r="QF2" t="n">
+        <v>634948</v>
+      </c>
+      <c r="QG2" t="n">
+        <v>522475</v>
+      </c>
+      <c r="QH2" t="n">
+        <v>213555</v>
+      </c>
+      <c r="QI2" t="n">
+        <v>1023693</v>
+      </c>
+      <c r="QJ2" t="n">
+        <v>579973</v>
+      </c>
+      <c r="QK2" t="n">
+        <v>642958</v>
+      </c>
+      <c r="QL2" t="n">
+        <v>578810</v>
+      </c>
+      <c r="QM2" t="n">
+        <v>769027</v>
+      </c>
+      <c r="QN2" t="n">
+        <v>168203</v>
+      </c>
+      <c r="QO2" t="n">
+        <v>9633</v>
+      </c>
+      <c r="QP2" t="n">
+        <v>83438</v>
+      </c>
+      <c r="QQ2" t="n">
+        <v>860282</v>
+      </c>
+      <c r="QR2" t="n">
+        <v>407894</v>
+      </c>
+      <c r="QS2" t="n">
+        <v>813663</v>
+      </c>
+      <c r="QT2" t="n">
+        <v>194225</v>
+      </c>
+      <c r="QU2" t="n">
+        <v>47833</v>
+      </c>
+      <c r="QV2" t="n">
+        <v>294919</v>
+      </c>
+      <c r="QW2" t="n">
+        <v>747788</v>
+      </c>
+      <c r="QX2" t="n">
+        <v>346589</v>
+      </c>
+      <c r="QY2" t="n">
+        <v>631124</v>
+      </c>
+      <c r="QZ2" t="n">
+        <v>498573</v>
+      </c>
+      <c r="RA2" t="n">
+        <v>112707</v>
+      </c>
+      <c r="RB2" t="n">
+        <v>97163</v>
+      </c>
+      <c r="RC2" t="n">
+        <v>14544</v>
+      </c>
+      <c r="RD2" t="n">
+        <v>103069</v>
+      </c>
+      <c r="RE2" t="n">
+        <v>20141</v>
+      </c>
+      <c r="RF2" t="n">
+        <v>429425</v>
+      </c>
+      <c r="RG2" t="n">
+        <v>340876</v>
+      </c>
+      <c r="RH2" t="n">
+        <v>689363</v>
+      </c>
+      <c r="RI2" t="n">
+        <v>251564</v>
+      </c>
+      <c r="RJ2" t="n">
+        <v>1156864</v>
+      </c>
+      <c r="RK2" t="n">
+        <v>327480</v>
+      </c>
+      <c r="RL2" t="n">
+        <v>204463</v>
+      </c>
+      <c r="RM2" t="n">
+        <v>449243</v>
+      </c>
+      <c r="RN2" t="n">
+        <v>956166</v>
+      </c>
+      <c r="RO2" t="n">
+        <v>85040</v>
+      </c>
+      <c r="RP2" t="n">
+        <v>227210</v>
+      </c>
+      <c r="RQ2" t="n">
+        <v>41301</v>
+      </c>
+      <c r="RR2" t="n">
+        <v>969865</v>
+      </c>
+      <c r="RS2" t="n">
+        <v>393204</v>
+      </c>
+      <c r="RT2" t="n">
+        <v>12031</v>
+      </c>
+      <c r="RU2" t="n">
+        <v>946411</v>
+      </c>
+      <c r="RV2" t="n">
+        <v>935031</v>
+      </c>
+      <c r="RW2" t="n">
+        <v>525956</v>
+      </c>
+      <c r="RX2" t="n">
+        <v>528274</v>
+      </c>
+      <c r="RY2" t="n">
+        <v>493747</v>
+      </c>
+      <c r="RZ2" t="n">
+        <v>164286</v>
+      </c>
+      <c r="SA2" t="n">
+        <v>1098391</v>
+      </c>
+      <c r="SB2" t="n">
+        <v>319075</v>
+      </c>
+      <c r="SC2" t="n">
+        <v>781666</v>
+      </c>
+      <c r="SD2" t="n">
+        <v>406982</v>
+      </c>
+      <c r="SE2" t="n">
+        <v>1006490</v>
+      </c>
+      <c r="SF2" t="n">
+        <v>196512</v>
+      </c>
+      <c r="SG2" t="n">
+        <v>335105</v>
+      </c>
+      <c r="SH2" t="n">
+        <v>584162</v>
+      </c>
+      <c r="SI2" t="n">
+        <v>937692</v>
+      </c>
+      <c r="SJ2" t="n">
+        <v>1101148</v>
+      </c>
+      <c r="SK2" t="n">
+        <v>1032470</v>
+      </c>
+      <c r="SL2" t="n">
+        <v>1125988</v>
+      </c>
+      <c r="SM2" t="n">
+        <v>1011932</v>
+      </c>
+      <c r="SN2" t="n">
+        <v>901972</v>
+      </c>
+      <c r="SO2" t="n">
+        <v>1076451</v>
+      </c>
+      <c r="SP2" t="n">
+        <v>397631</v>
+      </c>
+      <c r="SQ2" t="n">
+        <v>647867</v>
+      </c>
+      <c r="SR2" t="n">
+        <v>8669</v>
+      </c>
+      <c r="SS2" t="n">
+        <v>529492</v>
+      </c>
+      <c r="ST2" t="n">
+        <v>370693</v>
+      </c>
+      <c r="SU2" t="n">
+        <v>787397</v>
+      </c>
+      <c r="SV2" t="n">
+        <v>158323</v>
+      </c>
+      <c r="SW2" t="n">
+        <v>875324</v>
+      </c>
+      <c r="SX2" t="n">
+        <v>436861</v>
+      </c>
+      <c r="SY2" t="n">
+        <v>520888</v>
+      </c>
+      <c r="SZ2" t="n">
+        <v>648874</v>
+      </c>
+      <c r="TA2" t="n">
+        <v>518397</v>
+      </c>
+      <c r="TB2" t="n">
+        <v>141222</v>
+      </c>
+      <c r="TC2" t="n">
+        <v>5196</v>
+      </c>
+      <c r="TD2" t="n">
+        <v>807386</v>
+      </c>
+      <c r="TE2" t="n">
+        <v>752676</v>
+      </c>
+      <c r="TF2" t="n">
+        <v>637200</v>
+      </c>
+      <c r="TG2" t="n">
+        <v>926225</v>
+      </c>
+      <c r="TH2" t="n">
+        <v>251819</v>
+      </c>
+      <c r="TI2" t="n">
+        <v>970363</v>
+      </c>
+      <c r="TJ2" t="n">
+        <v>1194966</v>
+      </c>
+      <c r="TK2" t="n">
+        <v>35384</v>
+      </c>
+      <c r="TL2" t="n">
+        <v>13290</v>
+      </c>
+      <c r="TM2" t="n">
+        <v>873892</v>
+      </c>
+      <c r="TN2" t="n">
+        <v>895393</v>
+      </c>
+      <c r="TO2" t="n">
+        <v>356963</v>
+      </c>
+      <c r="TP2" t="n">
+        <v>869738</v>
+      </c>
+      <c r="TQ2" t="n">
+        <v>836500</v>
+      </c>
+      <c r="TR2" t="n">
+        <v>10450</v>
+      </c>
+      <c r="TS2" t="n">
+        <v>525536</v>
+      </c>
+      <c r="TT2" t="n">
+        <v>921095</v>
+      </c>
+      <c r="TU2" t="n">
+        <v>705895</v>
+      </c>
+      <c r="TV2" t="n">
+        <v>1037452</v>
+      </c>
+      <c r="TW2" t="n">
+        <v>382304</v>
+      </c>
+      <c r="TX2" t="n">
+        <v>222239</v>
+      </c>
+      <c r="TY2" t="n">
+        <v>342342</v>
+      </c>
+      <c r="TZ2" t="n">
+        <v>1105985</v>
+      </c>
+      <c r="UA2" t="n">
+        <v>303122</v>
+      </c>
+      <c r="UB2" t="n">
+        <v>411856</v>
+      </c>
+      <c r="UC2" t="n">
+        <v>566928</v>
+      </c>
+      <c r="UD2" t="n">
+        <v>492252</v>
+      </c>
+      <c r="UE2" t="n">
+        <v>703744</v>
+      </c>
+      <c r="UF2" t="n">
+        <v>74439</v>
+      </c>
+      <c r="UG2" t="n">
+        <v>96081</v>
+      </c>
+      <c r="UH2" t="n">
+        <v>1171667</v>
+      </c>
+      <c r="UI2" t="n">
+        <v>756075</v>
+      </c>
+      <c r="UJ2" t="n">
+        <v>1062643</v>
+      </c>
+      <c r="UK2" t="n">
+        <v>267913</v>
+      </c>
+      <c r="UL2" t="n">
+        <v>65604</v>
+      </c>
+      <c r="UM2" t="n">
+        <v>711134</v>
+      </c>
+      <c r="UN2" t="n">
+        <v>90950</v>
+      </c>
+      <c r="UO2" t="n">
+        <v>561224</v>
+      </c>
+      <c r="UP2" t="n">
+        <v>121398</v>
+      </c>
+      <c r="UQ2" t="n">
+        <v>672363</v>
+      </c>
+      <c r="UR2" t="n">
+        <v>982340</v>
+      </c>
+      <c r="US2" t="n">
+        <v>367261</v>
+      </c>
+      <c r="UT2" t="n">
+        <v>841195</v>
+      </c>
+      <c r="UU2" t="n">
+        <v>345950</v>
+      </c>
+      <c r="UV2" t="n">
+        <v>729455</v>
+      </c>
+      <c r="UW2" t="n">
+        <v>766737</v>
+      </c>
+      <c r="UX2" t="n">
+        <v>109739</v>
+      </c>
+      <c r="UY2" t="n">
+        <v>618258</v>
+      </c>
+      <c r="UZ2" t="n">
+        <v>804052</v>
+      </c>
+      <c r="VA2" t="n">
+        <v>587962</v>
+      </c>
+      <c r="VB2" t="n">
+        <v>604725</v>
+      </c>
+      <c r="VC2" t="n">
+        <v>673088</v>
+      </c>
+      <c r="VD2" t="n">
+        <v>391592</v>
+      </c>
+      <c r="VE2" t="n">
+        <v>611985</v>
+      </c>
+      <c r="VF2" t="n">
+        <v>974893</v>
+      </c>
+      <c r="VG2" t="n">
+        <v>405154</v>
+      </c>
+      <c r="VH2" t="n">
+        <v>454443</v>
+      </c>
+      <c r="VI2" t="n">
+        <v>833341</v>
+      </c>
+      <c r="VJ2" t="n">
+        <v>516221</v>
+      </c>
+      <c r="VK2" t="n">
+        <v>598115</v>
+      </c>
+      <c r="VL2" t="n">
+        <v>1137932</v>
+      </c>
+      <c r="VM2" t="n">
+        <v>1104255</v>
+      </c>
+      <c r="VN2" t="n">
+        <v>105877</v>
+      </c>
+      <c r="VO2" t="n">
+        <v>968003</v>
+      </c>
+      <c r="VP2" t="n">
+        <v>20306</v>
+      </c>
+      <c r="VQ2" t="n">
+        <v>538510</v>
+      </c>
+      <c r="VR2" t="n">
+        <v>571554</v>
+      </c>
+      <c r="VS2" t="n">
+        <v>80843</v>
+      </c>
+      <c r="VT2" t="n">
+        <v>476660</v>
+      </c>
+      <c r="VU2" t="n">
+        <v>81631</v>
+      </c>
+      <c r="VV2" t="n">
+        <v>868030</v>
+      </c>
+      <c r="VW2" t="n">
+        <v>709461</v>
+      </c>
+      <c r="VX2" t="n">
+        <v>293800</v>
+      </c>
+      <c r="VY2" t="n">
+        <v>91110</v>
+      </c>
+      <c r="VZ2" t="n">
+        <v>436841</v>
+      </c>
+      <c r="WA2" t="n">
+        <v>676934</v>
+      </c>
+      <c r="WB2" t="n">
+        <v>731742</v>
+      </c>
+      <c r="WC2" t="n">
+        <v>314663</v>
+      </c>
+      <c r="WD2" t="n">
+        <v>800526</v>
+      </c>
+      <c r="WE2" t="n">
+        <v>298045</v>
+      </c>
+      <c r="WF2" t="n">
+        <v>512713</v>
+      </c>
+      <c r="WG2" t="n">
+        <v>720282</v>
+      </c>
+      <c r="WH2" t="n">
+        <v>150886</v>
+      </c>
+      <c r="WI2" t="n">
+        <v>139523</v>
+      </c>
+      <c r="WJ2" t="n">
+        <v>225863</v>
+      </c>
+      <c r="WK2" t="n">
+        <v>564748</v>
+      </c>
+      <c r="WL2" t="n">
+        <v>288640</v>
+      </c>
+      <c r="WM2" t="n">
+        <v>294618</v>
+      </c>
+      <c r="WN2" t="n">
+        <v>722541</v>
+      </c>
+      <c r="WO2" t="n">
+        <v>561407</v>
+      </c>
+      <c r="WP2" t="n">
+        <v>205268</v>
+      </c>
+      <c r="WQ2" t="n">
+        <v>707820</v>
+      </c>
+      <c r="WR2" t="n">
+        <v>514626</v>
+      </c>
+      <c r="WS2" t="n">
+        <v>376246</v>
+      </c>
+      <c r="WT2" t="n">
+        <v>393280</v>
+      </c>
+      <c r="WU2" t="n">
+        <v>333556</v>
+      </c>
+      <c r="WV2" t="n">
+        <v>40051</v>
+      </c>
+      <c r="WW2" t="n">
+        <v>827547</v>
+      </c>
+      <c r="WX2" t="n">
+        <v>891623</v>
+      </c>
+      <c r="WY2" t="n">
+        <v>41022</v>
+      </c>
+      <c r="WZ2" t="n">
+        <v>202278</v>
+      </c>
+      <c r="XA2" t="n">
+        <v>812493</v>
+      </c>
+      <c r="XB2" t="n">
+        <v>502433</v>
+      </c>
+      <c r="XC2" t="n">
+        <v>731272</v>
+      </c>
+      <c r="XD2" t="n">
+        <v>691211</v>
+      </c>
+      <c r="XE2" t="n">
+        <v>735831</v>
+      </c>
+      <c r="XF2" t="n">
+        <v>481080</v>
+      </c>
+      <c r="XG2" t="n">
+        <v>545902</v>
+      </c>
+      <c r="XH2" t="n">
+        <v>257629</v>
+      </c>
+      <c r="XI2" t="n">
+        <v>552729</v>
+      </c>
+      <c r="XJ2" t="n">
+        <v>435386</v>
+      </c>
+      <c r="XK2" t="n">
+        <v>904589</v>
+      </c>
+      <c r="XL2" t="n">
+        <v>232342</v>
+      </c>
+      <c r="XM2" t="n">
+        <v>575735</v>
+      </c>
+      <c r="XN2" t="n">
+        <v>1139917</v>
+      </c>
+      <c r="XO2" t="n">
+        <v>51196</v>
+      </c>
+      <c r="XP2" t="n">
+        <v>76314</v>
+      </c>
+      <c r="XQ2" t="n">
+        <v>958689</v>
+      </c>
+      <c r="XR2" t="n">
+        <v>314379</v>
+      </c>
+      <c r="XS2" t="n">
+        <v>196824</v>
+      </c>
+      <c r="XT2" t="n">
+        <v>485604</v>
+      </c>
+      <c r="XU2" t="n">
+        <v>508089</v>
+      </c>
+      <c r="XV2" t="n">
+        <v>677470</v>
+      </c>
+      <c r="XW2" t="n">
+        <v>362718</v>
+      </c>
+      <c r="XX2" t="n">
+        <v>118000</v>
+      </c>
+      <c r="XY2" t="n">
+        <v>478093</v>
+      </c>
+      <c r="XZ2" t="n">
+        <v>1069964</v>
+      </c>
+      <c r="YA2" t="n">
+        <v>442047</v>
+      </c>
+      <c r="YB2" t="n">
+        <v>1124824</v>
+      </c>
+      <c r="YC2" t="n">
+        <v>336217</v>
+      </c>
+      <c r="YD2" t="n">
+        <v>1200925</v>
+      </c>
+      <c r="YE2" t="n">
+        <v>67489</v>
+      </c>
+      <c r="YF2" t="n">
+        <v>830578</v>
+      </c>
+      <c r="YG2" t="n">
+        <v>123411</v>
+      </c>
+      <c r="YH2" t="n">
+        <v>625313</v>
+      </c>
+      <c r="YI2" t="n">
+        <v>75606</v>
+      </c>
+      <c r="YJ2" t="n">
+        <v>876462</v>
+      </c>
+      <c r="YK2" t="n">
+        <v>289405</v>
+      </c>
+      <c r="YL2" t="n">
+        <v>1019372</v>
+      </c>
+      <c r="YM2" t="n">
+        <v>932166</v>
+      </c>
+      <c r="YN2" t="n">
+        <v>103375</v>
+      </c>
+      <c r="YO2" t="n">
+        <v>1167629</v>
+      </c>
+      <c r="YP2" t="n">
+        <v>143428</v>
+      </c>
+      <c r="YQ2" t="n">
+        <v>111408</v>
+      </c>
+      <c r="YR2" t="n">
+        <v>819408</v>
+      </c>
+      <c r="YS2" t="n">
+        <v>1150262</v>
+      </c>
+      <c r="YT2" t="n">
+        <v>1047549</v>
+      </c>
+      <c r="YU2" t="n">
+        <v>431910</v>
+      </c>
+      <c r="YV2" t="n">
+        <v>590617</v>
+      </c>
+      <c r="YW2" t="n">
+        <v>1141713</v>
+      </c>
+      <c r="YX2" t="n">
+        <v>958651</v>
+      </c>
+      <c r="YY2" t="n">
+        <v>397336</v>
+      </c>
+      <c r="YZ2" t="n">
+        <v>442792</v>
+      </c>
+      <c r="ZA2" t="n">
+        <v>135040</v>
+      </c>
+      <c r="ZB2" t="n">
+        <v>63756</v>
+      </c>
+      <c r="ZC2" t="n">
+        <v>641525</v>
+      </c>
+      <c r="ZD2" t="n">
+        <v>557617</v>
+      </c>
+      <c r="ZE2" t="n">
+        <v>475297</v>
+      </c>
+      <c r="ZF2" t="n">
+        <v>50309</v>
+      </c>
+      <c r="ZG2" t="n">
+        <v>834094</v>
+      </c>
+      <c r="ZH2" t="n">
+        <v>123576</v>
+      </c>
+      <c r="ZI2" t="n">
+        <v>403568</v>
+      </c>
+      <c r="ZJ2" t="n">
+        <v>381415</v>
+      </c>
+      <c r="ZK2" t="n">
+        <v>585524</v>
+      </c>
+      <c r="ZL2" t="n">
+        <v>1085371</v>
+      </c>
+      <c r="ZM2" t="n">
+        <v>61382</v>
+      </c>
+      <c r="ZN2" t="n">
+        <v>216646</v>
+      </c>
+      <c r="ZO2" t="n">
+        <v>539835</v>
+      </c>
+      <c r="ZP2" t="n">
+        <v>223959</v>
+      </c>
+      <c r="ZQ2" t="n">
+        <v>545959</v>
+      </c>
+      <c r="ZR2" t="n">
+        <v>945187</v>
+      </c>
+      <c r="ZS2" t="n">
+        <v>383793</v>
+      </c>
+      <c r="ZT2" t="n">
+        <v>487235</v>
+      </c>
+      <c r="ZU2" t="n">
+        <v>740108</v>
+      </c>
+      <c r="ZV2" t="n">
+        <v>542082</v>
+      </c>
+      <c r="ZW2" t="n">
+        <v>333460</v>
+      </c>
+      <c r="ZX2" t="n">
+        <v>391325</v>
+      </c>
+      <c r="ZY2" t="n">
+        <v>153297</v>
+      </c>
+      <c r="ZZ2" t="n">
+        <v>208810</v>
+      </c>
+      <c r="AAA2" t="n">
+        <v>923494</v>
+      </c>
+      <c r="AAB2" t="n">
+        <v>555692</v>
+      </c>
+      <c r="AAC2" t="n">
+        <v>667931</v>
+      </c>
+      <c r="AAD2" t="n">
+        <v>1008835</v>
+      </c>
+      <c r="AAE2" t="n">
+        <v>767656</v>
+      </c>
+      <c r="AAF2" t="n">
+        <v>870595</v>
+      </c>
+      <c r="AAG2" t="n">
+        <v>1112719</v>
+      </c>
+      <c r="AAH2" t="n">
+        <v>385315</v>
+      </c>
+      <c r="AAI2" t="n">
+        <v>256252</v>
+      </c>
+      <c r="AAJ2" t="n">
+        <v>1095662</v>
+      </c>
+      <c r="AAK2" t="n">
+        <v>1049219</v>
+      </c>
+      <c r="AAL2" t="n">
+        <v>320810</v>
+      </c>
+      <c r="AAM2" t="n">
+        <v>202892</v>
+      </c>
+      <c r="AAN2" t="n">
+        <v>245755</v>
+      </c>
+      <c r="AAO2" t="n">
+        <v>146453</v>
+      </c>
+      <c r="AAP2" t="n">
+        <v>1115317</v>
+      </c>
+      <c r="AAQ2" t="n">
+        <v>606578</v>
+      </c>
+      <c r="AAR2" t="n">
+        <v>964914</v>
+      </c>
+      <c r="AAS2" t="n">
+        <v>1171225</v>
+      </c>
+      <c r="AAT2" t="n">
+        <v>810987</v>
+      </c>
+      <c r="AAU2" t="n">
+        <v>704857</v>
+      </c>
+      <c r="AAV2" t="n">
+        <v>458621</v>
+      </c>
+      <c r="AAW2" t="n">
+        <v>549035</v>
+      </c>
+      <c r="AAX2" t="n">
+        <v>129731</v>
+      </c>
+      <c r="AAY2" t="n">
+        <v>1054311</v>
+      </c>
+      <c r="AAZ2" t="n">
+        <v>1187215</v>
+      </c>
+      <c r="ABA2" t="n">
+        <v>6862</v>
+      </c>
+      <c r="ABB2" t="n">
+        <v>759162</v>
+      </c>
+      <c r="ABC2" t="n">
+        <v>412149</v>
+      </c>
+      <c r="ABD2" t="n">
+        <v>1188772</v>
+      </c>
+      <c r="ABE2" t="n">
+        <v>770696</v>
+      </c>
+      <c r="ABF2" t="n">
+        <v>783339</v>
+      </c>
+      <c r="ABG2" t="n">
+        <v>686460</v>
+      </c>
+      <c r="ABH2" t="n">
+        <v>848755</v>
+      </c>
+      <c r="ABI2" t="n">
+        <v>272875</v>
+      </c>
+      <c r="ABJ2" t="n">
+        <v>622916</v>
+      </c>
+      <c r="ABK2" t="n">
+        <v>1143399</v>
+      </c>
+      <c r="ABL2" t="n">
+        <v>750463</v>
+      </c>
+      <c r="ABM2" t="n">
+        <v>597642</v>
+      </c>
+      <c r="ABN2" t="n">
+        <v>778062</v>
+      </c>
+      <c r="ABO2" t="n">
+        <v>620242</v>
+      </c>
+      <c r="ABP2" t="n">
+        <v>605572</v>
+      </c>
+      <c r="ABQ2" t="n">
+        <v>741237</v>
+      </c>
+      <c r="ABR2" t="n">
+        <v>239660</v>
+      </c>
+      <c r="ABS2" t="n">
+        <v>784119</v>
+      </c>
+      <c r="ABT2" t="n">
+        <v>305750</v>
+      </c>
+      <c r="ABU2" t="n">
+        <v>1026585</v>
+      </c>
+      <c r="ABV2" t="n">
+        <v>845779</v>
+      </c>
+      <c r="ABW2" t="n">
+        <v>187679</v>
+      </c>
+      <c r="ABX2" t="n">
+        <v>454418</v>
+      </c>
+      <c r="ABY2" t="n">
+        <v>242296</v>
+      </c>
+      <c r="ABZ2" t="n">
+        <v>675088</v>
+      </c>
+      <c r="ACA2" t="n">
+        <v>244169</v>
+      </c>
+      <c r="ACB2" t="n">
+        <v>762196</v>
+      </c>
+      <c r="ACC2" t="n">
+        <v>210920</v>
+      </c>
+      <c r="ACD2" t="n">
+        <v>433773</v>
+      </c>
+      <c r="ACE2" t="n">
+        <v>544386</v>
+      </c>
+      <c r="ACF2" t="n">
+        <v>200733</v>
+      </c>
+      <c r="ACG2" t="n">
+        <v>801686</v>
+      </c>
+      <c r="ACH2" t="n">
+        <v>1020372</v>
+      </c>
+      <c r="ACI2" t="n">
+        <v>1185865</v>
+      </c>
+      <c r="ACJ2" t="n">
+        <v>495552</v>
+      </c>
+      <c r="ACK2" t="n">
+        <v>280279</v>
+      </c>
+      <c r="ACL2" t="n">
+        <v>696762</v>
+      </c>
+      <c r="ACM2" t="n">
+        <v>45503</v>
+      </c>
+      <c r="ACN2" t="n">
+        <v>712106</v>
+      </c>
+      <c r="ACO2" t="n">
+        <v>779408</v>
+      </c>
+      <c r="ACP2" t="n">
+        <v>292866</v>
+      </c>
+      <c r="ACQ2" t="n">
+        <v>798019</v>
+      </c>
+      <c r="ACR2" t="n">
+        <v>847262</v>
+      </c>
+      <c r="ACS2" t="n">
+        <v>793319</v>
+      </c>
+      <c r="ACT2" t="n">
+        <v>185923</v>
+      </c>
+      <c r="ACU2" t="n">
+        <v>1082521</v>
+      </c>
+      <c r="ACV2" t="n">
+        <v>616434</v>
+      </c>
+      <c r="ACW2" t="n">
+        <v>238803</v>
+      </c>
+      <c r="ACX2" t="n">
+        <v>1103864</v>
+      </c>
+      <c r="ACY2" t="n">
+        <v>308813</v>
+      </c>
+      <c r="ACZ2" t="n">
+        <v>147337</v>
+      </c>
+      <c r="ADA2" t="n">
+        <v>910365</v>
+      </c>
+      <c r="ADB2" t="n">
+        <v>1153271</v>
+      </c>
+      <c r="ADC2" t="n">
+        <v>600854</v>
+      </c>
+      <c r="ADD2" t="n">
+        <v>275420</v>
+      </c>
+      <c r="ADE2" t="n">
+        <v>979486</v>
+      </c>
+      <c r="ADF2" t="n">
+        <v>1110104</v>
+      </c>
+      <c r="ADG2" t="n">
+        <v>150149</v>
+      </c>
+      <c r="ADH2" t="n">
+        <v>444860</v>
+      </c>
+      <c r="ADI2" t="n">
+        <v>614672</v>
+      </c>
+      <c r="ADJ2" t="n">
+        <v>93851</v>
+      </c>
+      <c r="ADK2" t="n">
+        <v>662054</v>
+      </c>
+      <c r="ADL2" t="n">
+        <v>1090111</v>
+      </c>
+      <c r="ADM2" t="n">
+        <v>183113</v>
+      </c>
+      <c r="ADN2" t="n">
+        <v>533619</v>
+      </c>
+      <c r="ADO2" t="n">
+        <v>1065879</v>
+      </c>
+      <c r="ADP2" t="n">
+        <v>365429</v>
+      </c>
+      <c r="ADQ2" t="n">
+        <v>287616</v>
+      </c>
+      <c r="ADR2" t="n">
+        <v>794584</v>
+      </c>
+      <c r="ADS2" t="n">
+        <v>414698</v>
+      </c>
+      <c r="ADT2" t="n">
+        <v>536810</v>
+      </c>
+      <c r="ADU2" t="n">
+        <v>191623</v>
+      </c>
+      <c r="ADV2" t="n">
+        <v>890286</v>
+      </c>
+      <c r="ADW2" t="n">
+        <v>463174</v>
+      </c>
+      <c r="ADX2" t="n">
+        <v>1165634</v>
+      </c>
+      <c r="ADY2" t="n">
+        <v>689475</v>
+      </c>
+      <c r="ADZ2" t="n">
+        <v>368759</v>
+      </c>
+      <c r="AEA2" t="n">
+        <v>601860</v>
+      </c>
+      <c r="AEB2" t="n">
+        <v>738103</v>
+      </c>
+      <c r="AEC2" t="n">
+        <v>586246</v>
+      </c>
+      <c r="AED2" t="n">
+        <v>814444</v>
+      </c>
+      <c r="AEE2" t="n">
+        <v>478711</v>
+      </c>
+      <c r="AEF2" t="n">
+        <v>829401</v>
+      </c>
+      <c r="AEG2" t="n">
+        <v>854228</v>
+      </c>
+      <c r="AEH2" t="n">
+        <v>179478</v>
+      </c>
+      <c r="AEI2" t="n">
+        <v>509256</v>
+      </c>
+      <c r="AEJ2" t="n">
+        <v>884455</v>
+      </c>
+      <c r="AEK2" t="n">
+        <v>352539</v>
+      </c>
+      <c r="AEL2" t="n">
+        <v>356203</v>
+      </c>
+      <c r="AEM2" t="n">
+        <v>952441</v>
+      </c>
+      <c r="AEN2" t="n">
+        <v>905658</v>
+      </c>
+      <c r="AEO2" t="n">
+        <v>1167117</v>
+      </c>
+      <c r="AEP2" t="n">
+        <v>262568</v>
+      </c>
+      <c r="AEQ2" t="n">
+        <v>101718</v>
+      </c>
+      <c r="AER2" t="n">
+        <v>222581</v>
+      </c>
+      <c r="AES2" t="n">
+        <v>1027840</v>
+      </c>
+      <c r="AET2" t="n">
+        <v>1079071</v>
+      </c>
+      <c r="AEU2" t="n">
+        <v>377264</v>
+      </c>
+      <c r="AEV2" t="n">
+        <v>71872</v>
+      </c>
+      <c r="AEW2" t="n">
+        <v>460209</v>
+      </c>
+      <c r="AEX2" t="n">
+        <v>637189</v>
+      </c>
+      <c r="AEY2" t="n">
+        <v>363383</v>
+      </c>
+      <c r="AEZ2" t="n">
+        <v>30471</v>
+      </c>
+      <c r="AFA2" t="n">
+        <v>354095</v>
+      </c>
+      <c r="AFB2" t="n">
+        <v>350688</v>
+      </c>
+      <c r="AFC2" t="n">
+        <v>135483</v>
+      </c>
+      <c r="AFD2" t="n">
+        <v>987682</v>
+      </c>
+      <c r="AFE2" t="n">
+        <v>30229</v>
+      </c>
+      <c r="AFF2" t="n">
+        <v>765014</v>
+      </c>
+      <c r="AFG2" t="n">
+        <v>79306</v>
+      </c>
+      <c r="AFH2" t="n">
+        <v>1046592</v>
+      </c>
+      <c r="AFI2" t="n">
+        <v>886020</v>
+      </c>
+      <c r="AFJ2" t="n">
+        <v>573067</v>
+      </c>
+      <c r="AFK2" t="n">
+        <v>860630</v>
+      </c>
+      <c r="AFL2" t="n">
+        <v>449469</v>
+      </c>
+      <c r="AFM2" t="n">
+        <v>948970</v>
+      </c>
+      <c r="AFN2" t="n">
+        <v>363953</v>
+      </c>
+      <c r="AFO2" t="n">
+        <v>928265</v>
+      </c>
+      <c r="AFP2" t="n">
+        <v>277204</v>
+      </c>
+      <c r="AFQ2" t="n">
+        <v>214748</v>
+      </c>
+      <c r="AFR2" t="n">
+        <v>808948</v>
+      </c>
+      <c r="AFS2" t="n">
+        <v>1178012</v>
+      </c>
+      <c r="AFT2" t="n">
+        <v>484261</v>
+      </c>
+      <c r="AFU2" t="n">
+        <v>21770</v>
+      </c>
+      <c r="AFV2" t="n">
+        <v>1131098</v>
+      </c>
+      <c r="AFW2" t="n">
+        <v>879267</v>
+      </c>
+      <c r="AFX2" t="n">
+        <v>419453</v>
+      </c>
+      <c r="AFY2" t="n">
+        <v>670341</v>
+      </c>
+      <c r="AFZ2" t="n">
+        <v>263895</v>
+      </c>
+      <c r="AGA2" t="n">
+        <v>372393</v>
+      </c>
+      <c r="AGB2" t="n">
+        <v>934042</v>
+      </c>
+      <c r="AGC2" t="n">
+        <v>788669</v>
+      </c>
+      <c r="AGD2" t="n">
+        <v>534570</v>
+      </c>
+      <c r="AGE2" t="n">
+        <v>543125</v>
+      </c>
+      <c r="AGF2" t="n">
+        <v>891782</v>
+      </c>
+      <c r="AGG2" t="n">
+        <v>514206</v>
+      </c>
+      <c r="AGH2" t="n">
+        <v>223178</v>
+      </c>
+      <c r="AGI2" t="n">
+        <v>280043</v>
+      </c>
+      <c r="AGJ2" t="n">
+        <v>261012</v>
+      </c>
+      <c r="AGK2" t="n">
+        <v>1182556</v>
+      </c>
+      <c r="AGL2" t="n">
+        <v>1015855</v>
+      </c>
+      <c r="AGM2" t="n">
+        <v>865604</v>
+      </c>
+      <c r="AGN2" t="n">
+        <v>1076150</v>
+      </c>
+      <c r="AGO2" t="n">
+        <v>745680</v>
+      </c>
+      <c r="AGP2" t="n">
+        <v>26234</v>
+      </c>
+      <c r="AGQ2" t="n">
+        <v>546731</v>
+      </c>
+      <c r="AGR2" t="n">
+        <v>603620</v>
+      </c>
+      <c r="AGS2" t="n">
+        <v>458628</v>
+      </c>
+      <c r="AGT2" t="n">
+        <v>646154</v>
+      </c>
+      <c r="AGU2" t="n">
+        <v>333819</v>
+      </c>
+      <c r="AGV2" t="n">
+        <v>896955</v>
+      </c>
+      <c r="AGW2" t="n">
+        <v>532700</v>
+      </c>
+      <c r="AGX2" t="n">
+        <v>971107</v>
+      </c>
+      <c r="AGY2" t="n">
+        <v>310923</v>
+      </c>
+      <c r="AGZ2" t="n">
+        <v>490850</v>
+      </c>
+      <c r="AHA2" t="n">
+        <v>255783</v>
+      </c>
+      <c r="AHB2" t="n">
+        <v>228488</v>
+      </c>
+      <c r="AHC2" t="n">
+        <v>106369</v>
+      </c>
+      <c r="AHD2" t="n">
+        <v>1154699</v>
+      </c>
+      <c r="AHE2" t="n">
+        <v>72958</v>
+      </c>
+      <c r="AHF2" t="n">
+        <v>265336</v>
+      </c>
+      <c r="AHG2" t="n">
+        <v>822128</v>
+      </c>
+      <c r="AHH2" t="n">
+        <v>69706</v>
+      </c>
+      <c r="AHI2" t="n">
+        <v>453588</v>
+      </c>
+      <c r="AHJ2" t="n">
+        <v>54050</v>
+      </c>
+      <c r="AHK2" t="n">
+        <v>1071155</v>
+      </c>
+      <c r="AHL2" t="n">
+        <v>415153</v>
+      </c>
+      <c r="AHM2" t="n">
+        <v>89139</v>
+      </c>
+      <c r="AHN2" t="n">
+        <v>932293</v>
+      </c>
+      <c r="AHO2" t="n">
+        <v>1119013</v>
+      </c>
+      <c r="AHP2" t="n">
+        <v>952428</v>
+      </c>
+      <c r="AHQ2" t="n">
+        <v>881897</v>
+      </c>
+      <c r="AHR2" t="n">
+        <v>129459</v>
+      </c>
+      <c r="AHS2" t="n">
+        <v>477161</v>
+      </c>
+      <c r="AHT2" t="n">
+        <v>782052</v>
+      </c>
+      <c r="AHU2" t="n">
+        <v>791695</v>
+      </c>
+      <c r="AHV2" t="n">
+        <v>441328</v>
+      </c>
+      <c r="AHW2" t="n">
+        <v>451013</v>
+      </c>
+      <c r="AHX2" t="n">
+        <v>539012</v>
+      </c>
+      <c r="AHY2" t="n">
+        <v>701517</v>
+      </c>
+      <c r="AHZ2" t="n">
+        <v>51408</v>
+      </c>
+      <c r="AIA2" t="n">
+        <v>467563</v>
+      </c>
+      <c r="AIB2" t="n">
+        <v>1196672</v>
+      </c>
+      <c r="AIC2" t="n">
+        <v>270446</v>
+      </c>
+      <c r="AID2" t="n">
+        <v>1170752</v>
+      </c>
+      <c r="AIE2" t="n">
+        <v>905967</v>
+      </c>
+      <c r="AIF2" t="n">
+        <v>1163673</v>
+      </c>
+      <c r="AIG2" t="n">
+        <v>789124</v>
+      </c>
+      <c r="AIH2" t="n">
+        <v>681221</v>
+      </c>
+      <c r="AII2" t="n">
+        <v>1123910</v>
+      </c>
+      <c r="AIJ2" t="n">
+        <v>57653</v>
+      </c>
+      <c r="AIK2" t="n">
+        <v>509865</v>
+      </c>
+      <c r="AIL2" t="n">
+        <v>1047176</v>
+      </c>
+      <c r="AIM2" t="n">
+        <v>709420</v>
+      </c>
+      <c r="AIN2" t="n">
+        <v>607004</v>
+      </c>
+      <c r="AIO2" t="n">
+        <v>659448</v>
+      </c>
+      <c r="AIP2" t="n">
+        <v>323410</v>
+      </c>
+      <c r="AIQ2" t="n">
+        <v>1133695</v>
+      </c>
+      <c r="AIR2" t="n">
+        <v>553698</v>
+      </c>
+      <c r="AIS2" t="n">
+        <v>1097645</v>
+      </c>
+      <c r="AIT2" t="n">
+        <v>647687</v>
+      </c>
+      <c r="AIU2" t="n">
+        <v>664695</v>
+      </c>
+      <c r="AIV2" t="n">
+        <v>979970</v>
+      </c>
+      <c r="AIW2" t="n">
+        <v>318290</v>
+      </c>
+      <c r="AIX2" t="n">
+        <v>1081186</v>
+      </c>
+      <c r="AIY2" t="n">
+        <v>1057028</v>
+      </c>
+      <c r="AIZ2" t="n">
+        <v>1046545</v>
+      </c>
+      <c r="AJA2" t="n">
+        <v>899795</v>
+      </c>
+      <c r="AJB2" t="n">
+        <v>699672</v>
+      </c>
+      <c r="AJC2" t="n">
+        <v>541639</v>
+      </c>
+      <c r="AJD2" t="n">
+        <v>1122278</v>
+      </c>
+      <c r="AJE2" t="n">
+        <v>286073</v>
+      </c>
+      <c r="AJF2" t="n">
+        <v>735817</v>
+      </c>
+      <c r="AJG2" t="n">
+        <v>957852</v>
+      </c>
+      <c r="AJH2" t="n">
+        <v>130818</v>
+      </c>
+      <c r="AJI2" t="n">
+        <v>1092260</v>
+      </c>
+      <c r="AJJ2" t="n">
+        <v>1084559</v>
+      </c>
+      <c r="AJK2" t="n">
+        <v>496956</v>
+      </c>
+      <c r="AJL2" t="n">
+        <v>346178</v>
+      </c>
+      <c r="AJM2" t="n">
+        <v>197090</v>
+      </c>
+      <c r="AJN2" t="n">
+        <v>2262</v>
+      </c>
+      <c r="AJO2" t="n">
+        <v>471488</v>
+      </c>
+      <c r="AJP2" t="n">
+        <v>418890</v>
+      </c>
+      <c r="AJQ2" t="n">
+        <v>116443</v>
+      </c>
+      <c r="AJR2" t="n">
+        <v>432301</v>
+      </c>
+      <c r="AJS2" t="n">
+        <v>62385</v>
+      </c>
+      <c r="AJT2" t="n">
+        <v>864353</v>
+      </c>
+      <c r="AJU2" t="n">
+        <v>174351</v>
+      </c>
+      <c r="AJV2" t="n">
+        <v>1148822</v>
+      </c>
+      <c r="AJW2" t="n">
+        <v>592963</v>
+      </c>
+      <c r="AJX2" t="n">
+        <v>1004897</v>
+      </c>
+      <c r="AJY2" t="n">
+        <v>539302</v>
+      </c>
+      <c r="AJZ2" t="n">
+        <v>699620</v>
+      </c>
+      <c r="AKA2" t="n">
+        <v>877224</v>
+      </c>
+      <c r="AKB2" t="n">
+        <v>446775</v>
+      </c>
+      <c r="AKC2" t="n">
+        <v>99345</v>
+      </c>
+      <c r="AKD2" t="n">
+        <v>651399</v>
+      </c>
+      <c r="AKE2" t="n">
+        <v>939434</v>
+      </c>
+      <c r="AKF2" t="n">
+        <v>572544</v>
+      </c>
+      <c r="AKG2" t="n">
+        <v>632275</v>
+      </c>
+      <c r="AKH2" t="n">
+        <v>216215</v>
+      </c>
+      <c r="AKI2" t="n">
+        <v>629512</v>
+      </c>
+      <c r="AKJ2" t="n">
+        <v>776456</v>
+      </c>
+      <c r="AKK2" t="n">
+        <v>448133</v>
+      </c>
+      <c r="AKL2" t="n">
+        <v>887146</v>
+      </c>
+      <c r="AKM2" t="n">
+        <v>903500</v>
+      </c>
+      <c r="AKN2" t="n">
+        <v>576211</v>
+      </c>
+      <c r="AKO2" t="n">
+        <v>557960</v>
+      </c>
+      <c r="AKP2" t="n">
+        <v>460110</v>
+      </c>
+      <c r="AKQ2" t="n">
+        <v>465171</v>
+      </c>
+      <c r="AKR2" t="n">
+        <v>983763</v>
+      </c>
+      <c r="AKS2" t="n">
+        <v>36035</v>
+      </c>
+      <c r="AKT2" t="n">
+        <v>1099464</v>
+      </c>
+      <c r="AKU2" t="n">
+        <v>2747</v>
+      </c>
+      <c r="AKV2" t="n">
+        <v>694159</v>
+      </c>
+      <c r="AKW2" t="n">
+        <v>5872</v>
+      </c>
+      <c r="AKX2" t="n">
+        <v>992850</v>
+      </c>
+      <c r="AKY2" t="n">
+        <v>324585</v>
+      </c>
+      <c r="AKZ2" t="n">
+        <v>634718</v>
+      </c>
+      <c r="ALA2" t="n">
+        <v>293011</v>
+      </c>
+      <c r="ALB2" t="n">
+        <v>1158956</v>
+      </c>
+      <c r="ALC2" t="n">
+        <v>121066</v>
+      </c>
+      <c r="ALD2" t="n">
+        <v>52539</v>
+      </c>
+      <c r="ALE2" t="n">
+        <v>262235</v>
+      </c>
+      <c r="ALF2" t="n">
+        <v>851043</v>
+      </c>
+      <c r="ALG2" t="n">
+        <v>285554</v>
+      </c>
+      <c r="ALH2" t="n">
+        <v>401206</v>
+      </c>
+      <c r="ALI2" t="n">
+        <v>842160</v>
+      </c>
+      <c r="ALJ2" t="n">
+        <v>894488</v>
+      </c>
+      <c r="ALK2" t="n">
+        <v>569066</v>
+      </c>
+      <c r="ALL2" t="n">
+        <v>804834</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -844,14 +5843,6 @@
       <c r="B1" t="n">
         <v>36</v>
       </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -883,6 +5874,330 @@
       </c>
       <c r="J2" t="n">
         <v>769</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>6476948</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3600646</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>35680</v>
+      </c>
+      <c r="B2" t="n">
+        <v>22131</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50196</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31020</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35677</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10287</v>
+      </c>
+      <c r="G2" t="n">
+        <v>54083</v>
+      </c>
+      <c r="H2" t="n">
+        <v>121359</v>
+      </c>
+      <c r="I2" t="n">
+        <v>127208</v>
+      </c>
+      <c r="J2" t="n">
+        <v>71289</v>
+      </c>
+      <c r="K2" t="n">
+        <v>16023</v>
+      </c>
+      <c r="L2" t="n">
+        <v>107588</v>
+      </c>
+      <c r="M2" t="n">
+        <v>87072</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4144</v>
+      </c>
+      <c r="O2" t="n">
+        <v>27780</v>
+      </c>
+      <c r="P2" t="n">
+        <v>45679</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>90739</v>
+      </c>
+      <c r="R2" t="n">
+        <v>79615</v>
+      </c>
+      <c r="S2" t="n">
+        <v>59584</v>
+      </c>
+      <c r="T2" t="n">
+        <v>19997</v>
+      </c>
+      <c r="U2" t="n">
+        <v>20952</v>
+      </c>
+      <c r="V2" t="n">
+        <v>91129</v>
+      </c>
+      <c r="W2" t="n">
+        <v>30429</v>
+      </c>
+      <c r="X2" t="n">
+        <v>123446</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>111549</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>116691</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>60979</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>74419</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1054</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>24589</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>10429</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>68792</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2270</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>67757</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>59337</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>21428</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>73307</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>19305</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>50301</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>52094</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>83096</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>77478</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>57004</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>14977</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>94052</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>84458</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>39615</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>118138</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>64815</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>32589</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>80823</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>130394</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>42504</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>16149</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>100093</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>14430</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>108800</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>5502</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>63756</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>102418</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>106756</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>118173</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>7410</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>123048</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>87072</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>72577</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>45476</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>94934</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>34570</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>54247</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>42885</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>114200</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>59074</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>6120</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>96518</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>38197</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>49443</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>42611</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>39890</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>97755</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>103878</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>100410</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>27416</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>127041</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>24386</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>82733</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>73589</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>9180</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>104496</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>9969</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>114199</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>47173</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>117609</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>111051</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>26673</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>37993</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>12853</v>
       </c>
     </row>
   </sheetData>

--- a/code/resultados/NWJSSP_OADG_NEH(InsertionUPFirstImprovement).xlsx
+++ b/code/resultados/NWJSSP_OADG_NEH(InsertionUPFirstImprovement).xlsx
@@ -20,6 +20,7 @@
     <sheet name="tai_j100_m100_1" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="tai_j100_m100_1r" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="tai_j1000_m10_1" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="tai_j1000_m10_1r" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1448,6 +1449,3030 @@
       </c>
       <c r="B1" t="n">
         <v>3678155</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1041527</v>
+      </c>
+      <c r="B2" t="n">
+        <v>291193</v>
+      </c>
+      <c r="C2" t="n">
+        <v>623361</v>
+      </c>
+      <c r="D2" t="n">
+        <v>190866</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36981</v>
+      </c>
+      <c r="F2" t="n">
+        <v>178554</v>
+      </c>
+      <c r="G2" t="n">
+        <v>989593</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4391</v>
+      </c>
+      <c r="I2" t="n">
+        <v>281255</v>
+      </c>
+      <c r="J2" t="n">
+        <v>599782</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1112257</v>
+      </c>
+      <c r="L2" t="n">
+        <v>939146</v>
+      </c>
+      <c r="M2" t="n">
+        <v>714150</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1036754</v>
+      </c>
+      <c r="O2" t="n">
+        <v>964178</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1067111</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>650581</v>
+      </c>
+      <c r="R2" t="n">
+        <v>948341</v>
+      </c>
+      <c r="S2" t="n">
+        <v>161530</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1079654</v>
+      </c>
+      <c r="U2" t="n">
+        <v>118832</v>
+      </c>
+      <c r="V2" t="n">
+        <v>963157</v>
+      </c>
+      <c r="W2" t="n">
+        <v>210976</v>
+      </c>
+      <c r="X2" t="n">
+        <v>118353</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>266606</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>338163</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>593392</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>331403</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>83040</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2061</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>174631</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>429774</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>137552</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>870013</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>185526</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>694362</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>582988</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>152827</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>943317</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>595668</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>132079</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>744748</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1041100</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>628175</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1147614</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>943127</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>219837</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1058817</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>177515</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>682122</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>47981</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1176468</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>368133</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>621975</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>737922</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>982354</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>37498</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>15978</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1108346</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>172342</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>157347</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>154978</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1174727</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>620406</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1111703</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1003034</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>219671</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>874049</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>762079</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>8229</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>399346</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>3769</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>13920</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1182657</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>235862</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1066397</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>595399</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>1043318</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>274805</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>770855</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>1004477</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>1071430</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>802799</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>609310</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>949663</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>910344</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>458146</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>58689</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>310854</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>917844</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>258464</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>112013</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>997775</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>69185</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>423857</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>162496</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>39516</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>1051868</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>718292</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>644242</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>773766</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>501498</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>1191740</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>1136935</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>46721</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>787365</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>743397</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>29293</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>503312</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>117092</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>298435</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>717110</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>838692</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>420491</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>373131</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>667018</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>305977</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>144934</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1128655</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>417062</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>614788</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1117295</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>992840</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>999131</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>795538</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>573370</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>171277</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>219894</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>489825</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>507412</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>683544</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>465207</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>77394</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>733185</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>34850</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>1059492</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>25075</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>190126</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>1144767</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>20742</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>535128</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>757621</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>427286</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>683371</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>1822</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>1174341</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>901580</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>972941</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>553975</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>514064</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>702640</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>843861</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>854896</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>845831</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>231488</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>299143</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>818882</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>1135396</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>1120682</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>643587</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>470054</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>247278</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>169624</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>439465</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>133336</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>1093435</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>837896</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>746683</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>464233</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>1030409</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>807036</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>741354</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>862403</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>55479</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>86331</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>500676</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>1024105</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>725844</v>
+      </c>
+      <c r="FX2" t="n">
+        <v>1115110</v>
+      </c>
+      <c r="FY2" t="n">
+        <v>656988</v>
+      </c>
+      <c r="FZ2" t="n">
+        <v>851121</v>
+      </c>
+      <c r="GA2" t="n">
+        <v>800463</v>
+      </c>
+      <c r="GB2" t="n">
+        <v>422036</v>
+      </c>
+      <c r="GC2" t="n">
+        <v>692005</v>
+      </c>
+      <c r="GD2" t="n">
+        <v>181285</v>
+      </c>
+      <c r="GE2" t="n">
+        <v>824298</v>
+      </c>
+      <c r="GF2" t="n">
+        <v>18129</v>
+      </c>
+      <c r="GG2" t="n">
+        <v>718096</v>
+      </c>
+      <c r="GH2" t="n">
+        <v>241259</v>
+      </c>
+      <c r="GI2" t="n">
+        <v>207364</v>
+      </c>
+      <c r="GJ2" t="n">
+        <v>1131133</v>
+      </c>
+      <c r="GK2" t="n">
+        <v>995125</v>
+      </c>
+      <c r="GL2" t="n">
+        <v>279066</v>
+      </c>
+      <c r="GM2" t="n">
+        <v>885285</v>
+      </c>
+      <c r="GN2" t="n">
+        <v>1073149</v>
+      </c>
+      <c r="GO2" t="n">
+        <v>358622</v>
+      </c>
+      <c r="GP2" t="n">
+        <v>234553</v>
+      </c>
+      <c r="GQ2" t="n">
+        <v>198080</v>
+      </c>
+      <c r="GR2" t="n">
+        <v>21157</v>
+      </c>
+      <c r="GS2" t="n">
+        <v>313881</v>
+      </c>
+      <c r="GT2" t="n">
+        <v>386699</v>
+      </c>
+      <c r="GU2" t="n">
+        <v>724237</v>
+      </c>
+      <c r="GV2" t="n">
+        <v>788679</v>
+      </c>
+      <c r="GW2" t="n">
+        <v>912486</v>
+      </c>
+      <c r="GX2" t="n">
+        <v>723284</v>
+      </c>
+      <c r="GY2" t="n">
+        <v>1043389</v>
+      </c>
+      <c r="GZ2" t="n">
+        <v>59061</v>
+      </c>
+      <c r="HA2" t="n">
+        <v>317506</v>
+      </c>
+      <c r="HB2" t="n">
+        <v>114942</v>
+      </c>
+      <c r="HC2" t="n">
+        <v>1117277</v>
+      </c>
+      <c r="HD2" t="n">
+        <v>469125</v>
+      </c>
+      <c r="HE2" t="n">
+        <v>765470</v>
+      </c>
+      <c r="HF2" t="n">
+        <v>273394</v>
+      </c>
+      <c r="HG2" t="n">
+        <v>350815</v>
+      </c>
+      <c r="HH2" t="n">
+        <v>696814</v>
+      </c>
+      <c r="HI2" t="n">
+        <v>319744</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>356337</v>
+      </c>
+      <c r="HK2" t="n">
+        <v>940621</v>
+      </c>
+      <c r="HL2" t="n">
+        <v>266232</v>
+      </c>
+      <c r="HM2" t="n">
+        <v>326241</v>
+      </c>
+      <c r="HN2" t="n">
+        <v>629805</v>
+      </c>
+      <c r="HO2" t="n">
+        <v>563916</v>
+      </c>
+      <c r="HP2" t="n">
+        <v>387655</v>
+      </c>
+      <c r="HQ2" t="n">
+        <v>379267</v>
+      </c>
+      <c r="HR2" t="n">
+        <v>303485</v>
+      </c>
+      <c r="HS2" t="n">
+        <v>126058</v>
+      </c>
+      <c r="HT2" t="n">
+        <v>797386</v>
+      </c>
+      <c r="HU2" t="n">
+        <v>617534</v>
+      </c>
+      <c r="HV2" t="n">
+        <v>775339</v>
+      </c>
+      <c r="HW2" t="n">
+        <v>231319</v>
+      </c>
+      <c r="HX2" t="n">
+        <v>882174</v>
+      </c>
+      <c r="HY2" t="n">
+        <v>962977</v>
+      </c>
+      <c r="HZ2" t="n">
+        <v>23466</v>
+      </c>
+      <c r="IA2" t="n">
+        <v>248911</v>
+      </c>
+      <c r="IB2" t="n">
+        <v>727928</v>
+      </c>
+      <c r="IC2" t="n">
+        <v>1087058</v>
+      </c>
+      <c r="ID2" t="n">
+        <v>856198</v>
+      </c>
+      <c r="IE2" t="n">
+        <v>565348</v>
+      </c>
+      <c r="IF2" t="n">
+        <v>282714</v>
+      </c>
+      <c r="IG2" t="n">
+        <v>45094</v>
+      </c>
+      <c r="IH2" t="n">
+        <v>919106</v>
+      </c>
+      <c r="II2" t="n">
+        <v>194071</v>
+      </c>
+      <c r="IJ2" t="n">
+        <v>663324</v>
+      </c>
+      <c r="IK2" t="n">
+        <v>664327</v>
+      </c>
+      <c r="IL2" t="n">
+        <v>984909</v>
+      </c>
+      <c r="IM2" t="n">
+        <v>910752</v>
+      </c>
+      <c r="IN2" t="n">
+        <v>154146</v>
+      </c>
+      <c r="IO2" t="n">
+        <v>166571</v>
+      </c>
+      <c r="IP2" t="n">
+        <v>719433</v>
+      </c>
+      <c r="IQ2" t="n">
+        <v>233554</v>
+      </c>
+      <c r="IR2" t="n">
+        <v>424704</v>
+      </c>
+      <c r="IS2" t="n">
+        <v>943905</v>
+      </c>
+      <c r="IT2" t="n">
+        <v>251129</v>
+      </c>
+      <c r="IU2" t="n">
+        <v>816168</v>
+      </c>
+      <c r="IV2" t="n">
+        <v>328325</v>
+      </c>
+      <c r="IW2" t="n">
+        <v>815978</v>
+      </c>
+      <c r="IX2" t="n">
+        <v>725602</v>
+      </c>
+      <c r="IY2" t="n">
+        <v>454765</v>
+      </c>
+      <c r="IZ2" t="n">
+        <v>413742</v>
+      </c>
+      <c r="JA2" t="n">
+        <v>1014294</v>
+      </c>
+      <c r="JB2" t="n">
+        <v>493923</v>
+      </c>
+      <c r="JC2" t="n">
+        <v>929103</v>
+      </c>
+      <c r="JD2" t="n">
+        <v>751806</v>
+      </c>
+      <c r="JE2" t="n">
+        <v>487853</v>
+      </c>
+      <c r="JF2" t="n">
+        <v>976636</v>
+      </c>
+      <c r="JG2" t="n">
+        <v>412094</v>
+      </c>
+      <c r="JH2" t="n">
+        <v>1162479</v>
+      </c>
+      <c r="JI2" t="n">
+        <v>639505</v>
+      </c>
+      <c r="JJ2" t="n">
+        <v>1026291</v>
+      </c>
+      <c r="JK2" t="n">
+        <v>1090058</v>
+      </c>
+      <c r="JL2" t="n">
+        <v>559350</v>
+      </c>
+      <c r="JM2" t="n">
+        <v>590426</v>
+      </c>
+      <c r="JN2" t="n">
+        <v>1088854</v>
+      </c>
+      <c r="JO2" t="n">
+        <v>625716</v>
+      </c>
+      <c r="JP2" t="n">
+        <v>975363</v>
+      </c>
+      <c r="JQ2" t="n">
+        <v>1052326</v>
+      </c>
+      <c r="JR2" t="n">
+        <v>301759</v>
+      </c>
+      <c r="JS2" t="n">
+        <v>143361</v>
+      </c>
+      <c r="JT2" t="n">
+        <v>361701</v>
+      </c>
+      <c r="JU2" t="n">
+        <v>1078800</v>
+      </c>
+      <c r="JV2" t="n">
+        <v>107575</v>
+      </c>
+      <c r="JW2" t="n">
+        <v>829075</v>
+      </c>
+      <c r="JX2" t="n">
+        <v>1052663</v>
+      </c>
+      <c r="JY2" t="n">
+        <v>97293</v>
+      </c>
+      <c r="JZ2" t="n">
+        <v>409580</v>
+      </c>
+      <c r="KA2" t="n">
+        <v>987057</v>
+      </c>
+      <c r="KB2" t="n">
+        <v>992014</v>
+      </c>
+      <c r="KC2" t="n">
+        <v>468225</v>
+      </c>
+      <c r="KD2" t="n">
+        <v>380176</v>
+      </c>
+      <c r="KE2" t="n">
+        <v>825642</v>
+      </c>
+      <c r="KF2" t="n">
+        <v>43159</v>
+      </c>
+      <c r="KG2" t="n">
+        <v>530615</v>
+      </c>
+      <c r="KH2" t="n">
+        <v>977464</v>
+      </c>
+      <c r="KI2" t="n">
+        <v>1029764</v>
+      </c>
+      <c r="KJ2" t="n">
+        <v>349159</v>
+      </c>
+      <c r="KK2" t="n">
+        <v>127507</v>
+      </c>
+      <c r="KL2" t="n">
+        <v>482729</v>
+      </c>
+      <c r="KM2" t="n">
+        <v>996079</v>
+      </c>
+      <c r="KN2" t="n">
+        <v>1061436</v>
+      </c>
+      <c r="KO2" t="n">
+        <v>655222</v>
+      </c>
+      <c r="KP2" t="n">
+        <v>383449</v>
+      </c>
+      <c r="KQ2" t="n">
+        <v>1113054</v>
+      </c>
+      <c r="KR2" t="n">
+        <v>654130</v>
+      </c>
+      <c r="KS2" t="n">
+        <v>338436</v>
+      </c>
+      <c r="KT2" t="n">
+        <v>402324</v>
+      </c>
+      <c r="KU2" t="n">
+        <v>384850</v>
+      </c>
+      <c r="KV2" t="n">
+        <v>473891</v>
+      </c>
+      <c r="KW2" t="n">
+        <v>473082</v>
+      </c>
+      <c r="KX2" t="n">
+        <v>360057</v>
+      </c>
+      <c r="KY2" t="n">
+        <v>820946</v>
+      </c>
+      <c r="KZ2" t="n">
+        <v>1061623</v>
+      </c>
+      <c r="LA2" t="n">
+        <v>227138</v>
+      </c>
+      <c r="LB2" t="n">
+        <v>995892</v>
+      </c>
+      <c r="LC2" t="n">
+        <v>1012501</v>
+      </c>
+      <c r="LD2" t="n">
+        <v>166655</v>
+      </c>
+      <c r="LE2" t="n">
+        <v>88186</v>
+      </c>
+      <c r="LF2" t="n">
+        <v>32046</v>
+      </c>
+      <c r="LG2" t="n">
+        <v>202509</v>
+      </c>
+      <c r="LH2" t="n">
+        <v>1108092</v>
+      </c>
+      <c r="LI2" t="n">
+        <v>754950</v>
+      </c>
+      <c r="LJ2" t="n">
+        <v>520109</v>
+      </c>
+      <c r="LK2" t="n">
+        <v>208139</v>
+      </c>
+      <c r="LL2" t="n">
+        <v>684289</v>
+      </c>
+      <c r="LM2" t="n">
+        <v>580600</v>
+      </c>
+      <c r="LN2" t="n">
+        <v>1200796</v>
+      </c>
+      <c r="LO2" t="n">
+        <v>304118</v>
+      </c>
+      <c r="LP2" t="n">
+        <v>374316</v>
+      </c>
+      <c r="LQ2" t="n">
+        <v>1033439</v>
+      </c>
+      <c r="LR2" t="n">
+        <v>405972</v>
+      </c>
+      <c r="LS2" t="n">
+        <v>865614</v>
+      </c>
+      <c r="LT2" t="n">
+        <v>28250</v>
+      </c>
+      <c r="LU2" t="n">
+        <v>687878</v>
+      </c>
+      <c r="LV2" t="n">
+        <v>1036328</v>
+      </c>
+      <c r="LW2" t="n">
+        <v>395070</v>
+      </c>
+      <c r="LX2" t="n">
+        <v>1152385</v>
+      </c>
+      <c r="LY2" t="n">
+        <v>761330</v>
+      </c>
+      <c r="LZ2" t="n">
+        <v>505525</v>
+      </c>
+      <c r="MA2" t="n">
+        <v>1019449</v>
+      </c>
+      <c r="MB2" t="n">
+        <v>184654</v>
+      </c>
+      <c r="MC2" t="n">
+        <v>793212</v>
+      </c>
+      <c r="MD2" t="n">
+        <v>462058</v>
+      </c>
+      <c r="ME2" t="n">
+        <v>345056</v>
+      </c>
+      <c r="MF2" t="n">
+        <v>390020</v>
+      </c>
+      <c r="MG2" t="n">
+        <v>403062</v>
+      </c>
+      <c r="MH2" t="n">
+        <v>878634</v>
+      </c>
+      <c r="MI2" t="n">
+        <v>738989</v>
+      </c>
+      <c r="MJ2" t="n">
+        <v>914006</v>
+      </c>
+      <c r="MK2" t="n">
+        <v>862852</v>
+      </c>
+      <c r="ML2" t="n">
+        <v>159441</v>
+      </c>
+      <c r="MM2" t="n">
+        <v>176643</v>
+      </c>
+      <c r="MN2" t="n">
+        <v>1010319</v>
+      </c>
+      <c r="MO2" t="n">
+        <v>938756</v>
+      </c>
+      <c r="MP2" t="n">
+        <v>354491</v>
+      </c>
+      <c r="MQ2" t="n">
+        <v>907534</v>
+      </c>
+      <c r="MR2" t="n">
+        <v>658106</v>
+      </c>
+      <c r="MS2" t="n">
+        <v>778824</v>
+      </c>
+      <c r="MT2" t="n">
+        <v>714020</v>
+      </c>
+      <c r="MU2" t="n">
+        <v>930451</v>
+      </c>
+      <c r="MV2" t="n">
+        <v>960101</v>
+      </c>
+      <c r="MW2" t="n">
+        <v>857111</v>
+      </c>
+      <c r="MX2" t="n">
+        <v>94454</v>
+      </c>
+      <c r="MY2" t="n">
+        <v>17438</v>
+      </c>
+      <c r="MZ2" t="n">
+        <v>99988</v>
+      </c>
+      <c r="NA2" t="n">
+        <v>271923</v>
+      </c>
+      <c r="NB2" t="n">
+        <v>284233</v>
+      </c>
+      <c r="NC2" t="n">
+        <v>1000880</v>
+      </c>
+      <c r="ND2" t="n">
+        <v>898636</v>
+      </c>
+      <c r="NE2" t="n">
+        <v>954103</v>
+      </c>
+      <c r="NF2" t="n">
+        <v>485859</v>
+      </c>
+      <c r="NG2" t="n">
+        <v>428710</v>
+      </c>
+      <c r="NH2" t="n">
+        <v>229403</v>
+      </c>
+      <c r="NI2" t="n">
+        <v>1099232</v>
+      </c>
+      <c r="NJ2" t="n">
+        <v>76058</v>
+      </c>
+      <c r="NK2" t="n">
+        <v>86430</v>
+      </c>
+      <c r="NL2" t="n">
+        <v>806347</v>
+      </c>
+      <c r="NM2" t="n">
+        <v>23472</v>
+      </c>
+      <c r="NN2" t="n">
+        <v>55276</v>
+      </c>
+      <c r="NO2" t="n">
+        <v>24837</v>
+      </c>
+      <c r="NP2" t="n">
+        <v>967055</v>
+      </c>
+      <c r="NQ2" t="n">
+        <v>478817</v>
+      </c>
+      <c r="NR2" t="n">
+        <v>254538</v>
+      </c>
+      <c r="NS2" t="n">
+        <v>106506</v>
+      </c>
+      <c r="NT2" t="n">
+        <v>66966</v>
+      </c>
+      <c r="NU2" t="n">
+        <v>1183656</v>
+      </c>
+      <c r="NV2" t="n">
+        <v>826369</v>
+      </c>
+      <c r="NW2" t="n">
+        <v>161443</v>
+      </c>
+      <c r="NX2" t="n">
+        <v>259168</v>
+      </c>
+      <c r="NY2" t="n">
+        <v>34151</v>
+      </c>
+      <c r="NZ2" t="n">
+        <v>375013</v>
+      </c>
+      <c r="OA2" t="n">
+        <v>1191368</v>
+      </c>
+      <c r="OB2" t="n">
+        <v>323704</v>
+      </c>
+      <c r="OC2" t="n">
+        <v>1128965</v>
+      </c>
+      <c r="OD2" t="n">
+        <v>1069449</v>
+      </c>
+      <c r="OE2" t="n">
+        <v>1193239</v>
+      </c>
+      <c r="OF2" t="n">
+        <v>652491</v>
+      </c>
+      <c r="OG2" t="n">
+        <v>728631</v>
+      </c>
+      <c r="OH2" t="n">
+        <v>142936</v>
+      </c>
+      <c r="OI2" t="n">
+        <v>852771</v>
+      </c>
+      <c r="OJ2" t="n">
+        <v>15955</v>
+      </c>
+      <c r="OK2" t="n">
+        <v>1139192</v>
+      </c>
+      <c r="OL2" t="n">
+        <v>1197503</v>
+      </c>
+      <c r="OM2" t="n">
+        <v>897190</v>
+      </c>
+      <c r="ON2" t="n">
+        <v>587503</v>
+      </c>
+      <c r="OO2" t="n">
+        <v>1038835</v>
+      </c>
+      <c r="OP2" t="n">
+        <v>1180184</v>
+      </c>
+      <c r="OQ2" t="n">
+        <v>166266</v>
+      </c>
+      <c r="OR2" t="n">
+        <v>182703</v>
+      </c>
+      <c r="OS2" t="n">
+        <v>148493</v>
+      </c>
+      <c r="OT2" t="n">
+        <v>772119</v>
+      </c>
+      <c r="OU2" t="n">
+        <v>678647</v>
+      </c>
+      <c r="OV2" t="n">
+        <v>236740</v>
+      </c>
+      <c r="OW2" t="n">
+        <v>1159297</v>
+      </c>
+      <c r="OX2" t="n">
+        <v>674064</v>
+      </c>
+      <c r="OY2" t="n">
+        <v>78636</v>
+      </c>
+      <c r="OZ2" t="n">
+        <v>665034</v>
+      </c>
+      <c r="PA2" t="n">
+        <v>61084</v>
+      </c>
+      <c r="PB2" t="n">
+        <v>892529</v>
+      </c>
+      <c r="PC2" t="n">
+        <v>915777</v>
+      </c>
+      <c r="PD2" t="n">
+        <v>471626</v>
+      </c>
+      <c r="PE2" t="n">
+        <v>531059</v>
+      </c>
+      <c r="PF2" t="n">
+        <v>609700</v>
+      </c>
+      <c r="PG2" t="n">
+        <v>245218</v>
+      </c>
+      <c r="PH2" t="n">
+        <v>831406</v>
+      </c>
+      <c r="PI2" t="n">
+        <v>551229</v>
+      </c>
+      <c r="PJ2" t="n">
+        <v>424222</v>
+      </c>
+      <c r="PK2" t="n">
+        <v>614046</v>
+      </c>
+      <c r="PL2" t="n">
+        <v>1018265</v>
+      </c>
+      <c r="PM2" t="n">
+        <v>749397</v>
+      </c>
+      <c r="PN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="PO2" t="n">
+        <v>732882</v>
+      </c>
+      <c r="PP2" t="n">
+        <v>916645</v>
+      </c>
+      <c r="PQ2" t="n">
+        <v>178535</v>
+      </c>
+      <c r="PR2" t="n">
+        <v>1027903</v>
+      </c>
+      <c r="PS2" t="n">
+        <v>523606</v>
+      </c>
+      <c r="PT2" t="n">
+        <v>1155311</v>
+      </c>
+      <c r="PU2" t="n">
+        <v>550310</v>
+      </c>
+      <c r="PV2" t="n">
+        <v>84786</v>
+      </c>
+      <c r="PW2" t="n">
+        <v>112108</v>
+      </c>
+      <c r="PX2" t="n">
+        <v>13290</v>
+      </c>
+      <c r="PY2" t="n">
+        <v>1003358</v>
+      </c>
+      <c r="PZ2" t="n">
+        <v>309325</v>
+      </c>
+      <c r="QA2" t="n">
+        <v>172636</v>
+      </c>
+      <c r="QB2" t="n">
+        <v>925738</v>
+      </c>
+      <c r="QC2" t="n">
+        <v>921108</v>
+      </c>
+      <c r="QD2" t="n">
+        <v>669402</v>
+      </c>
+      <c r="QE2" t="n">
+        <v>1162760</v>
+      </c>
+      <c r="QF2" t="n">
+        <v>634948</v>
+      </c>
+      <c r="QG2" t="n">
+        <v>522475</v>
+      </c>
+      <c r="QH2" t="n">
+        <v>213555</v>
+      </c>
+      <c r="QI2" t="n">
+        <v>1023693</v>
+      </c>
+      <c r="QJ2" t="n">
+        <v>579973</v>
+      </c>
+      <c r="QK2" t="n">
+        <v>642958</v>
+      </c>
+      <c r="QL2" t="n">
+        <v>578810</v>
+      </c>
+      <c r="QM2" t="n">
+        <v>769027</v>
+      </c>
+      <c r="QN2" t="n">
+        <v>168203</v>
+      </c>
+      <c r="QO2" t="n">
+        <v>9633</v>
+      </c>
+      <c r="QP2" t="n">
+        <v>83438</v>
+      </c>
+      <c r="QQ2" t="n">
+        <v>860282</v>
+      </c>
+      <c r="QR2" t="n">
+        <v>407894</v>
+      </c>
+      <c r="QS2" t="n">
+        <v>813663</v>
+      </c>
+      <c r="QT2" t="n">
+        <v>194225</v>
+      </c>
+      <c r="QU2" t="n">
+        <v>47833</v>
+      </c>
+      <c r="QV2" t="n">
+        <v>294919</v>
+      </c>
+      <c r="QW2" t="n">
+        <v>747788</v>
+      </c>
+      <c r="QX2" t="n">
+        <v>346589</v>
+      </c>
+      <c r="QY2" t="n">
+        <v>631124</v>
+      </c>
+      <c r="QZ2" t="n">
+        <v>498573</v>
+      </c>
+      <c r="RA2" t="n">
+        <v>112707</v>
+      </c>
+      <c r="RB2" t="n">
+        <v>97163</v>
+      </c>
+      <c r="RC2" t="n">
+        <v>14544</v>
+      </c>
+      <c r="RD2" t="n">
+        <v>103069</v>
+      </c>
+      <c r="RE2" t="n">
+        <v>20141</v>
+      </c>
+      <c r="RF2" t="n">
+        <v>429425</v>
+      </c>
+      <c r="RG2" t="n">
+        <v>340876</v>
+      </c>
+      <c r="RH2" t="n">
+        <v>689363</v>
+      </c>
+      <c r="RI2" t="n">
+        <v>251564</v>
+      </c>
+      <c r="RJ2" t="n">
+        <v>1156864</v>
+      </c>
+      <c r="RK2" t="n">
+        <v>327480</v>
+      </c>
+      <c r="RL2" t="n">
+        <v>204463</v>
+      </c>
+      <c r="RM2" t="n">
+        <v>449243</v>
+      </c>
+      <c r="RN2" t="n">
+        <v>956166</v>
+      </c>
+      <c r="RO2" t="n">
+        <v>85040</v>
+      </c>
+      <c r="RP2" t="n">
+        <v>227210</v>
+      </c>
+      <c r="RQ2" t="n">
+        <v>41301</v>
+      </c>
+      <c r="RR2" t="n">
+        <v>969865</v>
+      </c>
+      <c r="RS2" t="n">
+        <v>393204</v>
+      </c>
+      <c r="RT2" t="n">
+        <v>12031</v>
+      </c>
+      <c r="RU2" t="n">
+        <v>946411</v>
+      </c>
+      <c r="RV2" t="n">
+        <v>935031</v>
+      </c>
+      <c r="RW2" t="n">
+        <v>525956</v>
+      </c>
+      <c r="RX2" t="n">
+        <v>528274</v>
+      </c>
+      <c r="RY2" t="n">
+        <v>493747</v>
+      </c>
+      <c r="RZ2" t="n">
+        <v>164286</v>
+      </c>
+      <c r="SA2" t="n">
+        <v>1098391</v>
+      </c>
+      <c r="SB2" t="n">
+        <v>319075</v>
+      </c>
+      <c r="SC2" t="n">
+        <v>781666</v>
+      </c>
+      <c r="SD2" t="n">
+        <v>406982</v>
+      </c>
+      <c r="SE2" t="n">
+        <v>1006490</v>
+      </c>
+      <c r="SF2" t="n">
+        <v>196512</v>
+      </c>
+      <c r="SG2" t="n">
+        <v>335105</v>
+      </c>
+      <c r="SH2" t="n">
+        <v>584162</v>
+      </c>
+      <c r="SI2" t="n">
+        <v>937692</v>
+      </c>
+      <c r="SJ2" t="n">
+        <v>1101148</v>
+      </c>
+      <c r="SK2" t="n">
+        <v>1032470</v>
+      </c>
+      <c r="SL2" t="n">
+        <v>1125988</v>
+      </c>
+      <c r="SM2" t="n">
+        <v>1011932</v>
+      </c>
+      <c r="SN2" t="n">
+        <v>901972</v>
+      </c>
+      <c r="SO2" t="n">
+        <v>1076451</v>
+      </c>
+      <c r="SP2" t="n">
+        <v>397631</v>
+      </c>
+      <c r="SQ2" t="n">
+        <v>647867</v>
+      </c>
+      <c r="SR2" t="n">
+        <v>8669</v>
+      </c>
+      <c r="SS2" t="n">
+        <v>529492</v>
+      </c>
+      <c r="ST2" t="n">
+        <v>370693</v>
+      </c>
+      <c r="SU2" t="n">
+        <v>787397</v>
+      </c>
+      <c r="SV2" t="n">
+        <v>158323</v>
+      </c>
+      <c r="SW2" t="n">
+        <v>875324</v>
+      </c>
+      <c r="SX2" t="n">
+        <v>436861</v>
+      </c>
+      <c r="SY2" t="n">
+        <v>520888</v>
+      </c>
+      <c r="SZ2" t="n">
+        <v>648874</v>
+      </c>
+      <c r="TA2" t="n">
+        <v>518397</v>
+      </c>
+      <c r="TB2" t="n">
+        <v>141222</v>
+      </c>
+      <c r="TC2" t="n">
+        <v>5196</v>
+      </c>
+      <c r="TD2" t="n">
+        <v>807386</v>
+      </c>
+      <c r="TE2" t="n">
+        <v>752676</v>
+      </c>
+      <c r="TF2" t="n">
+        <v>637200</v>
+      </c>
+      <c r="TG2" t="n">
+        <v>926225</v>
+      </c>
+      <c r="TH2" t="n">
+        <v>251819</v>
+      </c>
+      <c r="TI2" t="n">
+        <v>970363</v>
+      </c>
+      <c r="TJ2" t="n">
+        <v>1194966</v>
+      </c>
+      <c r="TK2" t="n">
+        <v>35384</v>
+      </c>
+      <c r="TL2" t="n">
+        <v>13290</v>
+      </c>
+      <c r="TM2" t="n">
+        <v>873892</v>
+      </c>
+      <c r="TN2" t="n">
+        <v>895393</v>
+      </c>
+      <c r="TO2" t="n">
+        <v>356963</v>
+      </c>
+      <c r="TP2" t="n">
+        <v>869738</v>
+      </c>
+      <c r="TQ2" t="n">
+        <v>836500</v>
+      </c>
+      <c r="TR2" t="n">
+        <v>10450</v>
+      </c>
+      <c r="TS2" t="n">
+        <v>525536</v>
+      </c>
+      <c r="TT2" t="n">
+        <v>921095</v>
+      </c>
+      <c r="TU2" t="n">
+        <v>705895</v>
+      </c>
+      <c r="TV2" t="n">
+        <v>1037452</v>
+      </c>
+      <c r="TW2" t="n">
+        <v>382304</v>
+      </c>
+      <c r="TX2" t="n">
+        <v>222239</v>
+      </c>
+      <c r="TY2" t="n">
+        <v>342342</v>
+      </c>
+      <c r="TZ2" t="n">
+        <v>1105985</v>
+      </c>
+      <c r="UA2" t="n">
+        <v>303122</v>
+      </c>
+      <c r="UB2" t="n">
+        <v>411856</v>
+      </c>
+      <c r="UC2" t="n">
+        <v>566928</v>
+      </c>
+      <c r="UD2" t="n">
+        <v>492252</v>
+      </c>
+      <c r="UE2" t="n">
+        <v>703744</v>
+      </c>
+      <c r="UF2" t="n">
+        <v>74439</v>
+      </c>
+      <c r="UG2" t="n">
+        <v>96081</v>
+      </c>
+      <c r="UH2" t="n">
+        <v>1171667</v>
+      </c>
+      <c r="UI2" t="n">
+        <v>756075</v>
+      </c>
+      <c r="UJ2" t="n">
+        <v>1062643</v>
+      </c>
+      <c r="UK2" t="n">
+        <v>267913</v>
+      </c>
+      <c r="UL2" t="n">
+        <v>65604</v>
+      </c>
+      <c r="UM2" t="n">
+        <v>711134</v>
+      </c>
+      <c r="UN2" t="n">
+        <v>90950</v>
+      </c>
+      <c r="UO2" t="n">
+        <v>561224</v>
+      </c>
+      <c r="UP2" t="n">
+        <v>121398</v>
+      </c>
+      <c r="UQ2" t="n">
+        <v>672363</v>
+      </c>
+      <c r="UR2" t="n">
+        <v>982340</v>
+      </c>
+      <c r="US2" t="n">
+        <v>367261</v>
+      </c>
+      <c r="UT2" t="n">
+        <v>841195</v>
+      </c>
+      <c r="UU2" t="n">
+        <v>345950</v>
+      </c>
+      <c r="UV2" t="n">
+        <v>729455</v>
+      </c>
+      <c r="UW2" t="n">
+        <v>766737</v>
+      </c>
+      <c r="UX2" t="n">
+        <v>109739</v>
+      </c>
+      <c r="UY2" t="n">
+        <v>618258</v>
+      </c>
+      <c r="UZ2" t="n">
+        <v>804052</v>
+      </c>
+      <c r="VA2" t="n">
+        <v>587962</v>
+      </c>
+      <c r="VB2" t="n">
+        <v>604725</v>
+      </c>
+      <c r="VC2" t="n">
+        <v>673088</v>
+      </c>
+      <c r="VD2" t="n">
+        <v>391592</v>
+      </c>
+      <c r="VE2" t="n">
+        <v>611985</v>
+      </c>
+      <c r="VF2" t="n">
+        <v>974893</v>
+      </c>
+      <c r="VG2" t="n">
+        <v>405154</v>
+      </c>
+      <c r="VH2" t="n">
+        <v>454443</v>
+      </c>
+      <c r="VI2" t="n">
+        <v>833341</v>
+      </c>
+      <c r="VJ2" t="n">
+        <v>516221</v>
+      </c>
+      <c r="VK2" t="n">
+        <v>598115</v>
+      </c>
+      <c r="VL2" t="n">
+        <v>1137932</v>
+      </c>
+      <c r="VM2" t="n">
+        <v>1104255</v>
+      </c>
+      <c r="VN2" t="n">
+        <v>105877</v>
+      </c>
+      <c r="VO2" t="n">
+        <v>968003</v>
+      </c>
+      <c r="VP2" t="n">
+        <v>20306</v>
+      </c>
+      <c r="VQ2" t="n">
+        <v>538510</v>
+      </c>
+      <c r="VR2" t="n">
+        <v>571554</v>
+      </c>
+      <c r="VS2" t="n">
+        <v>80843</v>
+      </c>
+      <c r="VT2" t="n">
+        <v>476660</v>
+      </c>
+      <c r="VU2" t="n">
+        <v>81631</v>
+      </c>
+      <c r="VV2" t="n">
+        <v>868030</v>
+      </c>
+      <c r="VW2" t="n">
+        <v>709461</v>
+      </c>
+      <c r="VX2" t="n">
+        <v>293800</v>
+      </c>
+      <c r="VY2" t="n">
+        <v>91110</v>
+      </c>
+      <c r="VZ2" t="n">
+        <v>436841</v>
+      </c>
+      <c r="WA2" t="n">
+        <v>676934</v>
+      </c>
+      <c r="WB2" t="n">
+        <v>731742</v>
+      </c>
+      <c r="WC2" t="n">
+        <v>314663</v>
+      </c>
+      <c r="WD2" t="n">
+        <v>800526</v>
+      </c>
+      <c r="WE2" t="n">
+        <v>298045</v>
+      </c>
+      <c r="WF2" t="n">
+        <v>512713</v>
+      </c>
+      <c r="WG2" t="n">
+        <v>720282</v>
+      </c>
+      <c r="WH2" t="n">
+        <v>150886</v>
+      </c>
+      <c r="WI2" t="n">
+        <v>139523</v>
+      </c>
+      <c r="WJ2" t="n">
+        <v>225863</v>
+      </c>
+      <c r="WK2" t="n">
+        <v>564748</v>
+      </c>
+      <c r="WL2" t="n">
+        <v>288640</v>
+      </c>
+      <c r="WM2" t="n">
+        <v>294618</v>
+      </c>
+      <c r="WN2" t="n">
+        <v>722541</v>
+      </c>
+      <c r="WO2" t="n">
+        <v>561407</v>
+      </c>
+      <c r="WP2" t="n">
+        <v>205268</v>
+      </c>
+      <c r="WQ2" t="n">
+        <v>707820</v>
+      </c>
+      <c r="WR2" t="n">
+        <v>514626</v>
+      </c>
+      <c r="WS2" t="n">
+        <v>376246</v>
+      </c>
+      <c r="WT2" t="n">
+        <v>393280</v>
+      </c>
+      <c r="WU2" t="n">
+        <v>333556</v>
+      </c>
+      <c r="WV2" t="n">
+        <v>40051</v>
+      </c>
+      <c r="WW2" t="n">
+        <v>827547</v>
+      </c>
+      <c r="WX2" t="n">
+        <v>891623</v>
+      </c>
+      <c r="WY2" t="n">
+        <v>41022</v>
+      </c>
+      <c r="WZ2" t="n">
+        <v>202278</v>
+      </c>
+      <c r="XA2" t="n">
+        <v>812493</v>
+      </c>
+      <c r="XB2" t="n">
+        <v>502433</v>
+      </c>
+      <c r="XC2" t="n">
+        <v>731272</v>
+      </c>
+      <c r="XD2" t="n">
+        <v>691211</v>
+      </c>
+      <c r="XE2" t="n">
+        <v>735831</v>
+      </c>
+      <c r="XF2" t="n">
+        <v>481080</v>
+      </c>
+      <c r="XG2" t="n">
+        <v>545902</v>
+      </c>
+      <c r="XH2" t="n">
+        <v>257629</v>
+      </c>
+      <c r="XI2" t="n">
+        <v>552729</v>
+      </c>
+      <c r="XJ2" t="n">
+        <v>435386</v>
+      </c>
+      <c r="XK2" t="n">
+        <v>904589</v>
+      </c>
+      <c r="XL2" t="n">
+        <v>232342</v>
+      </c>
+      <c r="XM2" t="n">
+        <v>575735</v>
+      </c>
+      <c r="XN2" t="n">
+        <v>1139917</v>
+      </c>
+      <c r="XO2" t="n">
+        <v>51196</v>
+      </c>
+      <c r="XP2" t="n">
+        <v>76314</v>
+      </c>
+      <c r="XQ2" t="n">
+        <v>958689</v>
+      </c>
+      <c r="XR2" t="n">
+        <v>314379</v>
+      </c>
+      <c r="XS2" t="n">
+        <v>196824</v>
+      </c>
+      <c r="XT2" t="n">
+        <v>485604</v>
+      </c>
+      <c r="XU2" t="n">
+        <v>508089</v>
+      </c>
+      <c r="XV2" t="n">
+        <v>677470</v>
+      </c>
+      <c r="XW2" t="n">
+        <v>362718</v>
+      </c>
+      <c r="XX2" t="n">
+        <v>118000</v>
+      </c>
+      <c r="XY2" t="n">
+        <v>478093</v>
+      </c>
+      <c r="XZ2" t="n">
+        <v>1069964</v>
+      </c>
+      <c r="YA2" t="n">
+        <v>442047</v>
+      </c>
+      <c r="YB2" t="n">
+        <v>1124824</v>
+      </c>
+      <c r="YC2" t="n">
+        <v>336217</v>
+      </c>
+      <c r="YD2" t="n">
+        <v>1200925</v>
+      </c>
+      <c r="YE2" t="n">
+        <v>67489</v>
+      </c>
+      <c r="YF2" t="n">
+        <v>830578</v>
+      </c>
+      <c r="YG2" t="n">
+        <v>123411</v>
+      </c>
+      <c r="YH2" t="n">
+        <v>625313</v>
+      </c>
+      <c r="YI2" t="n">
+        <v>75606</v>
+      </c>
+      <c r="YJ2" t="n">
+        <v>876462</v>
+      </c>
+      <c r="YK2" t="n">
+        <v>289405</v>
+      </c>
+      <c r="YL2" t="n">
+        <v>1019372</v>
+      </c>
+      <c r="YM2" t="n">
+        <v>932166</v>
+      </c>
+      <c r="YN2" t="n">
+        <v>103375</v>
+      </c>
+      <c r="YO2" t="n">
+        <v>1167629</v>
+      </c>
+      <c r="YP2" t="n">
+        <v>143428</v>
+      </c>
+      <c r="YQ2" t="n">
+        <v>111408</v>
+      </c>
+      <c r="YR2" t="n">
+        <v>819408</v>
+      </c>
+      <c r="YS2" t="n">
+        <v>1150262</v>
+      </c>
+      <c r="YT2" t="n">
+        <v>1047549</v>
+      </c>
+      <c r="YU2" t="n">
+        <v>431910</v>
+      </c>
+      <c r="YV2" t="n">
+        <v>590617</v>
+      </c>
+      <c r="YW2" t="n">
+        <v>1141713</v>
+      </c>
+      <c r="YX2" t="n">
+        <v>958651</v>
+      </c>
+      <c r="YY2" t="n">
+        <v>397336</v>
+      </c>
+      <c r="YZ2" t="n">
+        <v>442792</v>
+      </c>
+      <c r="ZA2" t="n">
+        <v>135040</v>
+      </c>
+      <c r="ZB2" t="n">
+        <v>63756</v>
+      </c>
+      <c r="ZC2" t="n">
+        <v>641525</v>
+      </c>
+      <c r="ZD2" t="n">
+        <v>557617</v>
+      </c>
+      <c r="ZE2" t="n">
+        <v>475297</v>
+      </c>
+      <c r="ZF2" t="n">
+        <v>50309</v>
+      </c>
+      <c r="ZG2" t="n">
+        <v>834094</v>
+      </c>
+      <c r="ZH2" t="n">
+        <v>123576</v>
+      </c>
+      <c r="ZI2" t="n">
+        <v>403568</v>
+      </c>
+      <c r="ZJ2" t="n">
+        <v>381415</v>
+      </c>
+      <c r="ZK2" t="n">
+        <v>585524</v>
+      </c>
+      <c r="ZL2" t="n">
+        <v>1085371</v>
+      </c>
+      <c r="ZM2" t="n">
+        <v>61382</v>
+      </c>
+      <c r="ZN2" t="n">
+        <v>216646</v>
+      </c>
+      <c r="ZO2" t="n">
+        <v>539835</v>
+      </c>
+      <c r="ZP2" t="n">
+        <v>223959</v>
+      </c>
+      <c r="ZQ2" t="n">
+        <v>545959</v>
+      </c>
+      <c r="ZR2" t="n">
+        <v>945187</v>
+      </c>
+      <c r="ZS2" t="n">
+        <v>383793</v>
+      </c>
+      <c r="ZT2" t="n">
+        <v>487235</v>
+      </c>
+      <c r="ZU2" t="n">
+        <v>740108</v>
+      </c>
+      <c r="ZV2" t="n">
+        <v>542082</v>
+      </c>
+      <c r="ZW2" t="n">
+        <v>333460</v>
+      </c>
+      <c r="ZX2" t="n">
+        <v>391325</v>
+      </c>
+      <c r="ZY2" t="n">
+        <v>153297</v>
+      </c>
+      <c r="ZZ2" t="n">
+        <v>208810</v>
+      </c>
+      <c r="AAA2" t="n">
+        <v>923494</v>
+      </c>
+      <c r="AAB2" t="n">
+        <v>555692</v>
+      </c>
+      <c r="AAC2" t="n">
+        <v>667931</v>
+      </c>
+      <c r="AAD2" t="n">
+        <v>1008835</v>
+      </c>
+      <c r="AAE2" t="n">
+        <v>767656</v>
+      </c>
+      <c r="AAF2" t="n">
+        <v>870595</v>
+      </c>
+      <c r="AAG2" t="n">
+        <v>1112719</v>
+      </c>
+      <c r="AAH2" t="n">
+        <v>385315</v>
+      </c>
+      <c r="AAI2" t="n">
+        <v>256252</v>
+      </c>
+      <c r="AAJ2" t="n">
+        <v>1095662</v>
+      </c>
+      <c r="AAK2" t="n">
+        <v>1049219</v>
+      </c>
+      <c r="AAL2" t="n">
+        <v>320810</v>
+      </c>
+      <c r="AAM2" t="n">
+        <v>202892</v>
+      </c>
+      <c r="AAN2" t="n">
+        <v>245755</v>
+      </c>
+      <c r="AAO2" t="n">
+        <v>146453</v>
+      </c>
+      <c r="AAP2" t="n">
+        <v>1115317</v>
+      </c>
+      <c r="AAQ2" t="n">
+        <v>606578</v>
+      </c>
+      <c r="AAR2" t="n">
+        <v>964914</v>
+      </c>
+      <c r="AAS2" t="n">
+        <v>1171225</v>
+      </c>
+      <c r="AAT2" t="n">
+        <v>810987</v>
+      </c>
+      <c r="AAU2" t="n">
+        <v>704857</v>
+      </c>
+      <c r="AAV2" t="n">
+        <v>458621</v>
+      </c>
+      <c r="AAW2" t="n">
+        <v>549035</v>
+      </c>
+      <c r="AAX2" t="n">
+        <v>129731</v>
+      </c>
+      <c r="AAY2" t="n">
+        <v>1054311</v>
+      </c>
+      <c r="AAZ2" t="n">
+        <v>1187215</v>
+      </c>
+      <c r="ABA2" t="n">
+        <v>6862</v>
+      </c>
+      <c r="ABB2" t="n">
+        <v>759162</v>
+      </c>
+      <c r="ABC2" t="n">
+        <v>412149</v>
+      </c>
+      <c r="ABD2" t="n">
+        <v>1188772</v>
+      </c>
+      <c r="ABE2" t="n">
+        <v>770696</v>
+      </c>
+      <c r="ABF2" t="n">
+        <v>783339</v>
+      </c>
+      <c r="ABG2" t="n">
+        <v>686460</v>
+      </c>
+      <c r="ABH2" t="n">
+        <v>848755</v>
+      </c>
+      <c r="ABI2" t="n">
+        <v>272875</v>
+      </c>
+      <c r="ABJ2" t="n">
+        <v>622916</v>
+      </c>
+      <c r="ABK2" t="n">
+        <v>1143399</v>
+      </c>
+      <c r="ABL2" t="n">
+        <v>750463</v>
+      </c>
+      <c r="ABM2" t="n">
+        <v>597642</v>
+      </c>
+      <c r="ABN2" t="n">
+        <v>778062</v>
+      </c>
+      <c r="ABO2" t="n">
+        <v>620242</v>
+      </c>
+      <c r="ABP2" t="n">
+        <v>605572</v>
+      </c>
+      <c r="ABQ2" t="n">
+        <v>741237</v>
+      </c>
+      <c r="ABR2" t="n">
+        <v>239660</v>
+      </c>
+      <c r="ABS2" t="n">
+        <v>784119</v>
+      </c>
+      <c r="ABT2" t="n">
+        <v>305750</v>
+      </c>
+      <c r="ABU2" t="n">
+        <v>1026585</v>
+      </c>
+      <c r="ABV2" t="n">
+        <v>845779</v>
+      </c>
+      <c r="ABW2" t="n">
+        <v>187679</v>
+      </c>
+      <c r="ABX2" t="n">
+        <v>454418</v>
+      </c>
+      <c r="ABY2" t="n">
+        <v>242296</v>
+      </c>
+      <c r="ABZ2" t="n">
+        <v>675088</v>
+      </c>
+      <c r="ACA2" t="n">
+        <v>244169</v>
+      </c>
+      <c r="ACB2" t="n">
+        <v>762196</v>
+      </c>
+      <c r="ACC2" t="n">
+        <v>210920</v>
+      </c>
+      <c r="ACD2" t="n">
+        <v>433773</v>
+      </c>
+      <c r="ACE2" t="n">
+        <v>544386</v>
+      </c>
+      <c r="ACF2" t="n">
+        <v>200733</v>
+      </c>
+      <c r="ACG2" t="n">
+        <v>801686</v>
+      </c>
+      <c r="ACH2" t="n">
+        <v>1020372</v>
+      </c>
+      <c r="ACI2" t="n">
+        <v>1185865</v>
+      </c>
+      <c r="ACJ2" t="n">
+        <v>495552</v>
+      </c>
+      <c r="ACK2" t="n">
+        <v>280279</v>
+      </c>
+      <c r="ACL2" t="n">
+        <v>696762</v>
+      </c>
+      <c r="ACM2" t="n">
+        <v>45503</v>
+      </c>
+      <c r="ACN2" t="n">
+        <v>712106</v>
+      </c>
+      <c r="ACO2" t="n">
+        <v>779408</v>
+      </c>
+      <c r="ACP2" t="n">
+        <v>292866</v>
+      </c>
+      <c r="ACQ2" t="n">
+        <v>798019</v>
+      </c>
+      <c r="ACR2" t="n">
+        <v>847262</v>
+      </c>
+      <c r="ACS2" t="n">
+        <v>793319</v>
+      </c>
+      <c r="ACT2" t="n">
+        <v>185923</v>
+      </c>
+      <c r="ACU2" t="n">
+        <v>1082521</v>
+      </c>
+      <c r="ACV2" t="n">
+        <v>616434</v>
+      </c>
+      <c r="ACW2" t="n">
+        <v>238803</v>
+      </c>
+      <c r="ACX2" t="n">
+        <v>1103864</v>
+      </c>
+      <c r="ACY2" t="n">
+        <v>308813</v>
+      </c>
+      <c r="ACZ2" t="n">
+        <v>147337</v>
+      </c>
+      <c r="ADA2" t="n">
+        <v>910365</v>
+      </c>
+      <c r="ADB2" t="n">
+        <v>1153271</v>
+      </c>
+      <c r="ADC2" t="n">
+        <v>600854</v>
+      </c>
+      <c r="ADD2" t="n">
+        <v>275420</v>
+      </c>
+      <c r="ADE2" t="n">
+        <v>979486</v>
+      </c>
+      <c r="ADF2" t="n">
+        <v>1110104</v>
+      </c>
+      <c r="ADG2" t="n">
+        <v>150149</v>
+      </c>
+      <c r="ADH2" t="n">
+        <v>444860</v>
+      </c>
+      <c r="ADI2" t="n">
+        <v>614672</v>
+      </c>
+      <c r="ADJ2" t="n">
+        <v>93851</v>
+      </c>
+      <c r="ADK2" t="n">
+        <v>662054</v>
+      </c>
+      <c r="ADL2" t="n">
+        <v>1090111</v>
+      </c>
+      <c r="ADM2" t="n">
+        <v>183113</v>
+      </c>
+      <c r="ADN2" t="n">
+        <v>533619</v>
+      </c>
+      <c r="ADO2" t="n">
+        <v>1065879</v>
+      </c>
+      <c r="ADP2" t="n">
+        <v>365429</v>
+      </c>
+      <c r="ADQ2" t="n">
+        <v>287616</v>
+      </c>
+      <c r="ADR2" t="n">
+        <v>794584</v>
+      </c>
+      <c r="ADS2" t="n">
+        <v>414698</v>
+      </c>
+      <c r="ADT2" t="n">
+        <v>536810</v>
+      </c>
+      <c r="ADU2" t="n">
+        <v>191623</v>
+      </c>
+      <c r="ADV2" t="n">
+        <v>890286</v>
+      </c>
+      <c r="ADW2" t="n">
+        <v>463174</v>
+      </c>
+      <c r="ADX2" t="n">
+        <v>1165634</v>
+      </c>
+      <c r="ADY2" t="n">
+        <v>689475</v>
+      </c>
+      <c r="ADZ2" t="n">
+        <v>368759</v>
+      </c>
+      <c r="AEA2" t="n">
+        <v>601860</v>
+      </c>
+      <c r="AEB2" t="n">
+        <v>738103</v>
+      </c>
+      <c r="AEC2" t="n">
+        <v>586246</v>
+      </c>
+      <c r="AED2" t="n">
+        <v>814444</v>
+      </c>
+      <c r="AEE2" t="n">
+        <v>478711</v>
+      </c>
+      <c r="AEF2" t="n">
+        <v>829401</v>
+      </c>
+      <c r="AEG2" t="n">
+        <v>854228</v>
+      </c>
+      <c r="AEH2" t="n">
+        <v>179478</v>
+      </c>
+      <c r="AEI2" t="n">
+        <v>509256</v>
+      </c>
+      <c r="AEJ2" t="n">
+        <v>884455</v>
+      </c>
+      <c r="AEK2" t="n">
+        <v>352539</v>
+      </c>
+      <c r="AEL2" t="n">
+        <v>356203</v>
+      </c>
+      <c r="AEM2" t="n">
+        <v>952441</v>
+      </c>
+      <c r="AEN2" t="n">
+        <v>905658</v>
+      </c>
+      <c r="AEO2" t="n">
+        <v>1167117</v>
+      </c>
+      <c r="AEP2" t="n">
+        <v>262568</v>
+      </c>
+      <c r="AEQ2" t="n">
+        <v>101718</v>
+      </c>
+      <c r="AER2" t="n">
+        <v>222581</v>
+      </c>
+      <c r="AES2" t="n">
+        <v>1027840</v>
+      </c>
+      <c r="AET2" t="n">
+        <v>1079071</v>
+      </c>
+      <c r="AEU2" t="n">
+        <v>377264</v>
+      </c>
+      <c r="AEV2" t="n">
+        <v>71872</v>
+      </c>
+      <c r="AEW2" t="n">
+        <v>460209</v>
+      </c>
+      <c r="AEX2" t="n">
+        <v>637189</v>
+      </c>
+      <c r="AEY2" t="n">
+        <v>363383</v>
+      </c>
+      <c r="AEZ2" t="n">
+        <v>30471</v>
+      </c>
+      <c r="AFA2" t="n">
+        <v>354095</v>
+      </c>
+      <c r="AFB2" t="n">
+        <v>350688</v>
+      </c>
+      <c r="AFC2" t="n">
+        <v>135483</v>
+      </c>
+      <c r="AFD2" t="n">
+        <v>987682</v>
+      </c>
+      <c r="AFE2" t="n">
+        <v>30229</v>
+      </c>
+      <c r="AFF2" t="n">
+        <v>765014</v>
+      </c>
+      <c r="AFG2" t="n">
+        <v>79306</v>
+      </c>
+      <c r="AFH2" t="n">
+        <v>1046592</v>
+      </c>
+      <c r="AFI2" t="n">
+        <v>886020</v>
+      </c>
+      <c r="AFJ2" t="n">
+        <v>573067</v>
+      </c>
+      <c r="AFK2" t="n">
+        <v>860630</v>
+      </c>
+      <c r="AFL2" t="n">
+        <v>449469</v>
+      </c>
+      <c r="AFM2" t="n">
+        <v>948970</v>
+      </c>
+      <c r="AFN2" t="n">
+        <v>363953</v>
+      </c>
+      <c r="AFO2" t="n">
+        <v>928265</v>
+      </c>
+      <c r="AFP2" t="n">
+        <v>277204</v>
+      </c>
+      <c r="AFQ2" t="n">
+        <v>214748</v>
+      </c>
+      <c r="AFR2" t="n">
+        <v>808948</v>
+      </c>
+      <c r="AFS2" t="n">
+        <v>1178012</v>
+      </c>
+      <c r="AFT2" t="n">
+        <v>484261</v>
+      </c>
+      <c r="AFU2" t="n">
+        <v>21770</v>
+      </c>
+      <c r="AFV2" t="n">
+        <v>1131098</v>
+      </c>
+      <c r="AFW2" t="n">
+        <v>879267</v>
+      </c>
+      <c r="AFX2" t="n">
+        <v>419453</v>
+      </c>
+      <c r="AFY2" t="n">
+        <v>670341</v>
+      </c>
+      <c r="AFZ2" t="n">
+        <v>263895</v>
+      </c>
+      <c r="AGA2" t="n">
+        <v>372393</v>
+      </c>
+      <c r="AGB2" t="n">
+        <v>934042</v>
+      </c>
+      <c r="AGC2" t="n">
+        <v>788669</v>
+      </c>
+      <c r="AGD2" t="n">
+        <v>534570</v>
+      </c>
+      <c r="AGE2" t="n">
+        <v>543125</v>
+      </c>
+      <c r="AGF2" t="n">
+        <v>891782</v>
+      </c>
+      <c r="AGG2" t="n">
+        <v>514206</v>
+      </c>
+      <c r="AGH2" t="n">
+        <v>223178</v>
+      </c>
+      <c r="AGI2" t="n">
+        <v>280043</v>
+      </c>
+      <c r="AGJ2" t="n">
+        <v>261012</v>
+      </c>
+      <c r="AGK2" t="n">
+        <v>1182556</v>
+      </c>
+      <c r="AGL2" t="n">
+        <v>1015855</v>
+      </c>
+      <c r="AGM2" t="n">
+        <v>865604</v>
+      </c>
+      <c r="AGN2" t="n">
+        <v>1076150</v>
+      </c>
+      <c r="AGO2" t="n">
+        <v>745680</v>
+      </c>
+      <c r="AGP2" t="n">
+        <v>26234</v>
+      </c>
+      <c r="AGQ2" t="n">
+        <v>546731</v>
+      </c>
+      <c r="AGR2" t="n">
+        <v>603620</v>
+      </c>
+      <c r="AGS2" t="n">
+        <v>458628</v>
+      </c>
+      <c r="AGT2" t="n">
+        <v>646154</v>
+      </c>
+      <c r="AGU2" t="n">
+        <v>333819</v>
+      </c>
+      <c r="AGV2" t="n">
+        <v>896955</v>
+      </c>
+      <c r="AGW2" t="n">
+        <v>532700</v>
+      </c>
+      <c r="AGX2" t="n">
+        <v>971107</v>
+      </c>
+      <c r="AGY2" t="n">
+        <v>310923</v>
+      </c>
+      <c r="AGZ2" t="n">
+        <v>490850</v>
+      </c>
+      <c r="AHA2" t="n">
+        <v>255783</v>
+      </c>
+      <c r="AHB2" t="n">
+        <v>228488</v>
+      </c>
+      <c r="AHC2" t="n">
+        <v>106369</v>
+      </c>
+      <c r="AHD2" t="n">
+        <v>1154699</v>
+      </c>
+      <c r="AHE2" t="n">
+        <v>72958</v>
+      </c>
+      <c r="AHF2" t="n">
+        <v>265336</v>
+      </c>
+      <c r="AHG2" t="n">
+        <v>822128</v>
+      </c>
+      <c r="AHH2" t="n">
+        <v>69706</v>
+      </c>
+      <c r="AHI2" t="n">
+        <v>453588</v>
+      </c>
+      <c r="AHJ2" t="n">
+        <v>54050</v>
+      </c>
+      <c r="AHK2" t="n">
+        <v>1071155</v>
+      </c>
+      <c r="AHL2" t="n">
+        <v>415153</v>
+      </c>
+      <c r="AHM2" t="n">
+        <v>89139</v>
+      </c>
+      <c r="AHN2" t="n">
+        <v>932293</v>
+      </c>
+      <c r="AHO2" t="n">
+        <v>1119013</v>
+      </c>
+      <c r="AHP2" t="n">
+        <v>952428</v>
+      </c>
+      <c r="AHQ2" t="n">
+        <v>881897</v>
+      </c>
+      <c r="AHR2" t="n">
+        <v>129459</v>
+      </c>
+      <c r="AHS2" t="n">
+        <v>477161</v>
+      </c>
+      <c r="AHT2" t="n">
+        <v>782052</v>
+      </c>
+      <c r="AHU2" t="n">
+        <v>791695</v>
+      </c>
+      <c r="AHV2" t="n">
+        <v>441328</v>
+      </c>
+      <c r="AHW2" t="n">
+        <v>451013</v>
+      </c>
+      <c r="AHX2" t="n">
+        <v>539012</v>
+      </c>
+      <c r="AHY2" t="n">
+        <v>701517</v>
+      </c>
+      <c r="AHZ2" t="n">
+        <v>51408</v>
+      </c>
+      <c r="AIA2" t="n">
+        <v>467563</v>
+      </c>
+      <c r="AIB2" t="n">
+        <v>1196672</v>
+      </c>
+      <c r="AIC2" t="n">
+        <v>270446</v>
+      </c>
+      <c r="AID2" t="n">
+        <v>1170752</v>
+      </c>
+      <c r="AIE2" t="n">
+        <v>905967</v>
+      </c>
+      <c r="AIF2" t="n">
+        <v>1163673</v>
+      </c>
+      <c r="AIG2" t="n">
+        <v>789124</v>
+      </c>
+      <c r="AIH2" t="n">
+        <v>681221</v>
+      </c>
+      <c r="AII2" t="n">
+        <v>1123910</v>
+      </c>
+      <c r="AIJ2" t="n">
+        <v>57653</v>
+      </c>
+      <c r="AIK2" t="n">
+        <v>509865</v>
+      </c>
+      <c r="AIL2" t="n">
+        <v>1047176</v>
+      </c>
+      <c r="AIM2" t="n">
+        <v>709420</v>
+      </c>
+      <c r="AIN2" t="n">
+        <v>607004</v>
+      </c>
+      <c r="AIO2" t="n">
+        <v>659448</v>
+      </c>
+      <c r="AIP2" t="n">
+        <v>323410</v>
+      </c>
+      <c r="AIQ2" t="n">
+        <v>1133695</v>
+      </c>
+      <c r="AIR2" t="n">
+        <v>553698</v>
+      </c>
+      <c r="AIS2" t="n">
+        <v>1097645</v>
+      </c>
+      <c r="AIT2" t="n">
+        <v>647687</v>
+      </c>
+      <c r="AIU2" t="n">
+        <v>664695</v>
+      </c>
+      <c r="AIV2" t="n">
+        <v>979970</v>
+      </c>
+      <c r="AIW2" t="n">
+        <v>318290</v>
+      </c>
+      <c r="AIX2" t="n">
+        <v>1081186</v>
+      </c>
+      <c r="AIY2" t="n">
+        <v>1057028</v>
+      </c>
+      <c r="AIZ2" t="n">
+        <v>1046545</v>
+      </c>
+      <c r="AJA2" t="n">
+        <v>899795</v>
+      </c>
+      <c r="AJB2" t="n">
+        <v>699672</v>
+      </c>
+      <c r="AJC2" t="n">
+        <v>541639</v>
+      </c>
+      <c r="AJD2" t="n">
+        <v>1122278</v>
+      </c>
+      <c r="AJE2" t="n">
+        <v>286073</v>
+      </c>
+      <c r="AJF2" t="n">
+        <v>735817</v>
+      </c>
+      <c r="AJG2" t="n">
+        <v>957852</v>
+      </c>
+      <c r="AJH2" t="n">
+        <v>130818</v>
+      </c>
+      <c r="AJI2" t="n">
+        <v>1092260</v>
+      </c>
+      <c r="AJJ2" t="n">
+        <v>1084559</v>
+      </c>
+      <c r="AJK2" t="n">
+        <v>496956</v>
+      </c>
+      <c r="AJL2" t="n">
+        <v>346178</v>
+      </c>
+      <c r="AJM2" t="n">
+        <v>197090</v>
+      </c>
+      <c r="AJN2" t="n">
+        <v>2262</v>
+      </c>
+      <c r="AJO2" t="n">
+        <v>471488</v>
+      </c>
+      <c r="AJP2" t="n">
+        <v>418890</v>
+      </c>
+      <c r="AJQ2" t="n">
+        <v>116443</v>
+      </c>
+      <c r="AJR2" t="n">
+        <v>432301</v>
+      </c>
+      <c r="AJS2" t="n">
+        <v>62385</v>
+      </c>
+      <c r="AJT2" t="n">
+        <v>864353</v>
+      </c>
+      <c r="AJU2" t="n">
+        <v>174351</v>
+      </c>
+      <c r="AJV2" t="n">
+        <v>1148822</v>
+      </c>
+      <c r="AJW2" t="n">
+        <v>592963</v>
+      </c>
+      <c r="AJX2" t="n">
+        <v>1004897</v>
+      </c>
+      <c r="AJY2" t="n">
+        <v>539302</v>
+      </c>
+      <c r="AJZ2" t="n">
+        <v>699620</v>
+      </c>
+      <c r="AKA2" t="n">
+        <v>877224</v>
+      </c>
+      <c r="AKB2" t="n">
+        <v>446775</v>
+      </c>
+      <c r="AKC2" t="n">
+        <v>99345</v>
+      </c>
+      <c r="AKD2" t="n">
+        <v>651399</v>
+      </c>
+      <c r="AKE2" t="n">
+        <v>939434</v>
+      </c>
+      <c r="AKF2" t="n">
+        <v>572544</v>
+      </c>
+      <c r="AKG2" t="n">
+        <v>632275</v>
+      </c>
+      <c r="AKH2" t="n">
+        <v>216215</v>
+      </c>
+      <c r="AKI2" t="n">
+        <v>629512</v>
+      </c>
+      <c r="AKJ2" t="n">
+        <v>776456</v>
+      </c>
+      <c r="AKK2" t="n">
+        <v>448133</v>
+      </c>
+      <c r="AKL2" t="n">
+        <v>887146</v>
+      </c>
+      <c r="AKM2" t="n">
+        <v>903500</v>
+      </c>
+      <c r="AKN2" t="n">
+        <v>576211</v>
+      </c>
+      <c r="AKO2" t="n">
+        <v>557960</v>
+      </c>
+      <c r="AKP2" t="n">
+        <v>460110</v>
+      </c>
+      <c r="AKQ2" t="n">
+        <v>465171</v>
+      </c>
+      <c r="AKR2" t="n">
+        <v>983763</v>
+      </c>
+      <c r="AKS2" t="n">
+        <v>36035</v>
+      </c>
+      <c r="AKT2" t="n">
+        <v>1099464</v>
+      </c>
+      <c r="AKU2" t="n">
+        <v>2747</v>
+      </c>
+      <c r="AKV2" t="n">
+        <v>694159</v>
+      </c>
+      <c r="AKW2" t="n">
+        <v>5872</v>
+      </c>
+      <c r="AKX2" t="n">
+        <v>992850</v>
+      </c>
+      <c r="AKY2" t="n">
+        <v>324585</v>
+      </c>
+      <c r="AKZ2" t="n">
+        <v>634718</v>
+      </c>
+      <c r="ALA2" t="n">
+        <v>293011</v>
+      </c>
+      <c r="ALB2" t="n">
+        <v>1158956</v>
+      </c>
+      <c r="ALC2" t="n">
+        <v>121066</v>
+      </c>
+      <c r="ALD2" t="n">
+        <v>52539</v>
+      </c>
+      <c r="ALE2" t="n">
+        <v>262235</v>
+      </c>
+      <c r="ALF2" t="n">
+        <v>851043</v>
+      </c>
+      <c r="ALG2" t="n">
+        <v>285554</v>
+      </c>
+      <c r="ALH2" t="n">
+        <v>401206</v>
+      </c>
+      <c r="ALI2" t="n">
+        <v>842160</v>
+      </c>
+      <c r="ALJ2" t="n">
+        <v>894488</v>
+      </c>
+      <c r="ALK2" t="n">
+        <v>569066</v>
+      </c>
+      <c r="ALL2" t="n">
+        <v>804834</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:ALL2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>578857375</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3619314</v>
       </c>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>
@@ -2450,3004 +5475,3004 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1041527</v>
+        <v>1236718</v>
       </c>
       <c r="B2" t="n">
-        <v>291193</v>
+        <v>1076985</v>
       </c>
       <c r="C2" t="n">
-        <v>623361</v>
+        <v>545654</v>
       </c>
       <c r="D2" t="n">
-        <v>190866</v>
+        <v>1058562</v>
       </c>
       <c r="E2" t="n">
-        <v>36981</v>
+        <v>870438</v>
       </c>
       <c r="F2" t="n">
-        <v>178554</v>
+        <v>640977</v>
       </c>
       <c r="G2" t="n">
-        <v>989593</v>
+        <v>1011190</v>
       </c>
       <c r="H2" t="n">
-        <v>4391</v>
+        <v>150025</v>
       </c>
       <c r="I2" t="n">
-        <v>281255</v>
+        <v>915176</v>
       </c>
       <c r="J2" t="n">
-        <v>599782</v>
+        <v>358383</v>
       </c>
       <c r="K2" t="n">
-        <v>1112257</v>
+        <v>344860</v>
       </c>
       <c r="L2" t="n">
-        <v>939146</v>
+        <v>746125</v>
       </c>
       <c r="M2" t="n">
-        <v>714150</v>
+        <v>1007504</v>
       </c>
       <c r="N2" t="n">
+        <v>1097094</v>
+      </c>
+      <c r="O2" t="n">
+        <v>657500</v>
+      </c>
+      <c r="P2" t="n">
+        <v>954429</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>601975</v>
+      </c>
+      <c r="R2" t="n">
+        <v>224021</v>
+      </c>
+      <c r="S2" t="n">
+        <v>462123</v>
+      </c>
+      <c r="T2" t="n">
+        <v>840448</v>
+      </c>
+      <c r="U2" t="n">
+        <v>461673</v>
+      </c>
+      <c r="V2" t="n">
+        <v>324017</v>
+      </c>
+      <c r="W2" t="n">
+        <v>179463</v>
+      </c>
+      <c r="X2" t="n">
+        <v>633469</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>897517</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>787630</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>747115</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>110299</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>729043</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>337687</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>577494</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>297288</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>381019</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>882890</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>145220</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>543688</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>715197</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>339330</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>398391</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>535187</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>776634</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>265777</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>304907</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>58705</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1182845</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>963298</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>932736</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>353288</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>998728</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>464293</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>427802</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>585009</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>707448</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>262604</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>878175</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>266834</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>651609</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>958542</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>507106</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>602759</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>379151</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>266885</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>580597</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>125223</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>570006</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>134638</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>166493</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1021429</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>171228</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>612877</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>305359</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1008489</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>442022</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>204365</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1100616</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>523751</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>315657</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>924357</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>150653</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>416574</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>667272</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>169818</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>743790</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>1047937</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>833562</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1014593</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>573380</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>1044570</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1017095</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>501037</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>509897</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>926931</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>721494</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>1073430</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>844442</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>340838</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>31351</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>835624</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>6584</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>967149</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>552918</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>670183</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>875181</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>78452</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>793319</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>129231</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>196978</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>270268</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>109081</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>581043</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>684252</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>617549</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>394689</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1042070</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>18947</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>975677</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>414741</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>986936</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1153595</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>563085</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1146517</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>440152</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1134157</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>516399</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>776500</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1062544</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>817867</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1213921</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>524302</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1152503</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>621597</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>425649</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>106566</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>93312</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>753792</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>711314</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>908493</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>780749</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>1156770</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>1130910</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>191339</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>522210</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>993729</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>593225</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>947049</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>186658</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>15189</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>317395</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>242809</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>343379</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>122530</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>1200465</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>383213</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>551749</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>889492</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>511443</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>472055</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>991345</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>571134</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>1122627</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>766046</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>953158</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>649036</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>417859</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>328011</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>23543</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>399615</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>60410</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>323562</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>6959</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>40896</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>1019659</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>288183</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>695498</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>433680</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>887365</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>755353</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>1033869</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>785214</v>
+      </c>
+      <c r="FX2" t="n">
+        <v>691160</v>
+      </c>
+      <c r="FY2" t="n">
+        <v>603981</v>
+      </c>
+      <c r="FZ2" t="n">
+        <v>978337</v>
+      </c>
+      <c r="GA2" t="n">
+        <v>227771</v>
+      </c>
+      <c r="GB2" t="n">
+        <v>97192</v>
+      </c>
+      <c r="GC2" t="n">
+        <v>759499</v>
+      </c>
+      <c r="GD2" t="n">
+        <v>1149124</v>
+      </c>
+      <c r="GE2" t="n">
+        <v>261373</v>
+      </c>
+      <c r="GF2" t="n">
+        <v>678420</v>
+      </c>
+      <c r="GG2" t="n">
+        <v>1003396</v>
+      </c>
+      <c r="GH2" t="n">
+        <v>20837</v>
+      </c>
+      <c r="GI2" t="n">
+        <v>483762</v>
+      </c>
+      <c r="GJ2" t="n">
+        <v>78266</v>
+      </c>
+      <c r="GK2" t="n">
+        <v>1068450</v>
+      </c>
+      <c r="GL2" t="n">
+        <v>492516</v>
+      </c>
+      <c r="GM2" t="n">
+        <v>553858</v>
+      </c>
+      <c r="GN2" t="n">
+        <v>912087</v>
+      </c>
+      <c r="GO2" t="n">
+        <v>799390</v>
+      </c>
+      <c r="GP2" t="n">
+        <v>408157</v>
+      </c>
+      <c r="GQ2" t="n">
+        <v>4463</v>
+      </c>
+      <c r="GR2" t="n">
+        <v>131694</v>
+      </c>
+      <c r="GS2" t="n">
+        <v>630484</v>
+      </c>
+      <c r="GT2" t="n">
+        <v>82503</v>
+      </c>
+      <c r="GU2" t="n">
+        <v>236831</v>
+      </c>
+      <c r="GV2" t="n">
+        <v>119573</v>
+      </c>
+      <c r="GW2" t="n">
+        <v>376993</v>
+      </c>
+      <c r="GX2" t="n">
+        <v>956621</v>
+      </c>
+      <c r="GY2" t="n">
+        <v>843633</v>
+      </c>
+      <c r="GZ2" t="n">
+        <v>130374</v>
+      </c>
+      <c r="HA2" t="n">
+        <v>776944</v>
+      </c>
+      <c r="HB2" t="n">
+        <v>592261</v>
+      </c>
+      <c r="HC2" t="n">
+        <v>16001</v>
+      </c>
+      <c r="HD2" t="n">
+        <v>882085</v>
+      </c>
+      <c r="HE2" t="n">
+        <v>673338</v>
+      </c>
+      <c r="HF2" t="n">
+        <v>226211</v>
+      </c>
+      <c r="HG2" t="n">
+        <v>310955</v>
+      </c>
+      <c r="HH2" t="n">
+        <v>322609</v>
+      </c>
+      <c r="HI2" t="n">
+        <v>782037</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>1203184</v>
+      </c>
+      <c r="HK2" t="n">
+        <v>1114488</v>
+      </c>
+      <c r="HL2" t="n">
+        <v>767869</v>
+      </c>
+      <c r="HM2" t="n">
+        <v>154311</v>
+      </c>
+      <c r="HN2" t="n">
+        <v>607564</v>
+      </c>
+      <c r="HO2" t="n">
+        <v>1225093</v>
+      </c>
+      <c r="HP2" t="n">
+        <v>240789</v>
+      </c>
+      <c r="HQ2" t="n">
+        <v>782485</v>
+      </c>
+      <c r="HR2" t="n">
+        <v>490428</v>
+      </c>
+      <c r="HS2" t="n">
+        <v>585500</v>
+      </c>
+      <c r="HT2" t="n">
+        <v>1064392</v>
+      </c>
+      <c r="HU2" t="n">
+        <v>645309</v>
+      </c>
+      <c r="HV2" t="n">
+        <v>561700</v>
+      </c>
+      <c r="HW2" t="n">
+        <v>812292</v>
+      </c>
+      <c r="HX2" t="n">
+        <v>1138278</v>
+      </c>
+      <c r="HY2" t="n">
+        <v>653059</v>
+      </c>
+      <c r="HZ2" t="n">
+        <v>212889</v>
+      </c>
+      <c r="IA2" t="n">
+        <v>1050101</v>
+      </c>
+      <c r="IB2" t="n">
+        <v>938229</v>
+      </c>
+      <c r="IC2" t="n">
+        <v>143160</v>
+      </c>
+      <c r="ID2" t="n">
+        <v>350380</v>
+      </c>
+      <c r="IE2" t="n">
+        <v>341334</v>
+      </c>
+      <c r="IF2" t="n">
+        <v>306573</v>
+      </c>
+      <c r="IG2" t="n">
+        <v>4216</v>
+      </c>
+      <c r="IH2" t="n">
+        <v>830324</v>
+      </c>
+      <c r="II2" t="n">
+        <v>520448</v>
+      </c>
+      <c r="IJ2" t="n">
+        <v>311720</v>
+      </c>
+      <c r="IK2" t="n">
+        <v>771488</v>
+      </c>
+      <c r="IL2" t="n">
+        <v>88066</v>
+      </c>
+      <c r="IM2" t="n">
+        <v>37521</v>
+      </c>
+      <c r="IN2" t="n">
+        <v>606985</v>
+      </c>
+      <c r="IO2" t="n">
+        <v>393049</v>
+      </c>
+      <c r="IP2" t="n">
+        <v>247674</v>
+      </c>
+      <c r="IQ2" t="n">
+        <v>935257</v>
+      </c>
+      <c r="IR2" t="n">
+        <v>802871</v>
+      </c>
+      <c r="IS2" t="n">
+        <v>1128839</v>
+      </c>
+      <c r="IT2" t="n">
+        <v>430463</v>
+      </c>
+      <c r="IU2" t="n">
+        <v>542917</v>
+      </c>
+      <c r="IV2" t="n">
+        <v>1024465</v>
+      </c>
+      <c r="IW2" t="n">
+        <v>56327</v>
+      </c>
+      <c r="IX2" t="n">
+        <v>178584</v>
+      </c>
+      <c r="IY2" t="n">
+        <v>733157</v>
+      </c>
+      <c r="IZ2" t="n">
+        <v>374007</v>
+      </c>
+      <c r="JA2" t="n">
+        <v>446520</v>
+      </c>
+      <c r="JB2" t="n">
+        <v>232186</v>
+      </c>
+      <c r="JC2" t="n">
+        <v>1231839</v>
+      </c>
+      <c r="JD2" t="n">
+        <v>963636</v>
+      </c>
+      <c r="JE2" t="n">
+        <v>537314</v>
+      </c>
+      <c r="JF2" t="n">
+        <v>425434</v>
+      </c>
+      <c r="JG2" t="n">
+        <v>237907</v>
+      </c>
+      <c r="JH2" t="n">
+        <v>410203</v>
+      </c>
+      <c r="JI2" t="n">
+        <v>51624</v>
+      </c>
+      <c r="JJ2" t="n">
+        <v>710587</v>
+      </c>
+      <c r="JK2" t="n">
+        <v>1222055</v>
+      </c>
+      <c r="JL2" t="n">
+        <v>300907</v>
+      </c>
+      <c r="JM2" t="n">
+        <v>790305</v>
+      </c>
+      <c r="JN2" t="n">
+        <v>531259</v>
+      </c>
+      <c r="JO2" t="n">
+        <v>578742</v>
+      </c>
+      <c r="JP2" t="n">
+        <v>1105186</v>
+      </c>
+      <c r="JQ2" t="n">
+        <v>965060</v>
+      </c>
+      <c r="JR2" t="n">
+        <v>26139</v>
+      </c>
+      <c r="JS2" t="n">
+        <v>883872</v>
+      </c>
+      <c r="JT2" t="n">
+        <v>790413</v>
+      </c>
+      <c r="JU2" t="n">
+        <v>788195</v>
+      </c>
+      <c r="JV2" t="n">
+        <v>460193</v>
+      </c>
+      <c r="JW2" t="n">
+        <v>294045</v>
+      </c>
+      <c r="JX2" t="n">
+        <v>1196134</v>
+      </c>
+      <c r="JY2" t="n">
+        <v>660072</v>
+      </c>
+      <c r="JZ2" t="n">
+        <v>797431</v>
+      </c>
+      <c r="KA2" t="n">
+        <v>913018</v>
+      </c>
+      <c r="KB2" t="n">
+        <v>63487</v>
+      </c>
+      <c r="KC2" t="n">
+        <v>656504</v>
+      </c>
+      <c r="KD2" t="n">
+        <v>60599</v>
+      </c>
+      <c r="KE2" t="n">
+        <v>259232</v>
+      </c>
+      <c r="KF2" t="n">
+        <v>862339</v>
+      </c>
+      <c r="KG2" t="n">
+        <v>413196</v>
+      </c>
+      <c r="KH2" t="n">
+        <v>210090</v>
+      </c>
+      <c r="KI2" t="n">
+        <v>826445</v>
+      </c>
+      <c r="KJ2" t="n">
+        <v>904660</v>
+      </c>
+      <c r="KK2" t="n">
+        <v>1227187</v>
+      </c>
+      <c r="KL2" t="n">
+        <v>820076</v>
+      </c>
+      <c r="KM2" t="n">
+        <v>363224</v>
+      </c>
+      <c r="KN2" t="n">
+        <v>418161</v>
+      </c>
+      <c r="KO2" t="n">
+        <v>847905</v>
+      </c>
+      <c r="KP2" t="n">
+        <v>1094649</v>
+      </c>
+      <c r="KQ2" t="n">
+        <v>269391</v>
+      </c>
+      <c r="KR2" t="n">
+        <v>926028</v>
+      </c>
+      <c r="KS2" t="n">
+        <v>156116</v>
+      </c>
+      <c r="KT2" t="n">
+        <v>599566</v>
+      </c>
+      <c r="KU2" t="n">
+        <v>116210</v>
+      </c>
+      <c r="KV2" t="n">
+        <v>560572</v>
+      </c>
+      <c r="KW2" t="n">
+        <v>462731</v>
+      </c>
+      <c r="KX2" t="n">
+        <v>791753</v>
+      </c>
+      <c r="KY2" t="n">
+        <v>1185705</v>
+      </c>
+      <c r="KZ2" t="n">
+        <v>189558</v>
+      </c>
+      <c r="LA2" t="n">
+        <v>165531</v>
+      </c>
+      <c r="LB2" t="n">
+        <v>239486</v>
+      </c>
+      <c r="LC2" t="n">
+        <v>331295</v>
+      </c>
+      <c r="LD2" t="n">
+        <v>970083</v>
+      </c>
+      <c r="LE2" t="n">
+        <v>676829</v>
+      </c>
+      <c r="LF2" t="n">
+        <v>216593</v>
+      </c>
+      <c r="LG2" t="n">
+        <v>885402</v>
+      </c>
+      <c r="LH2" t="n">
+        <v>559852</v>
+      </c>
+      <c r="LI2" t="n">
+        <v>639593</v>
+      </c>
+      <c r="LJ2" t="n">
+        <v>1098716</v>
+      </c>
+      <c r="LK2" t="n">
+        <v>538020</v>
+      </c>
+      <c r="LL2" t="n">
+        <v>1057253</v>
+      </c>
+      <c r="LM2" t="n">
+        <v>287021</v>
+      </c>
+      <c r="LN2" t="n">
+        <v>80698</v>
+      </c>
+      <c r="LO2" t="n">
+        <v>156606</v>
+      </c>
+      <c r="LP2" t="n">
+        <v>325975</v>
+      </c>
+      <c r="LQ2" t="n">
+        <v>715327</v>
+      </c>
+      <c r="LR2" t="n">
+        <v>409551</v>
+      </c>
+      <c r="LS2" t="n">
+        <v>142839</v>
+      </c>
+      <c r="LT2" t="n">
+        <v>640279</v>
+      </c>
+      <c r="LU2" t="n">
+        <v>1189552</v>
+      </c>
+      <c r="LV2" t="n">
+        <v>1233124</v>
+      </c>
+      <c r="LW2" t="n">
+        <v>968875</v>
+      </c>
+      <c r="LX2" t="n">
+        <v>951039</v>
+      </c>
+      <c r="LY2" t="n">
+        <v>9702</v>
+      </c>
+      <c r="LZ2" t="n">
+        <v>587035</v>
+      </c>
+      <c r="MA2" t="n">
+        <v>550443</v>
+      </c>
+      <c r="MB2" t="n">
+        <v>852851</v>
+      </c>
+      <c r="MC2" t="n">
+        <v>824605</v>
+      </c>
+      <c r="MD2" t="n">
+        <v>703501</v>
+      </c>
+      <c r="ME2" t="n">
+        <v>173974</v>
+      </c>
+      <c r="MF2" t="n">
+        <v>962997</v>
+      </c>
+      <c r="MG2" t="n">
+        <v>487783</v>
+      </c>
+      <c r="MH2" t="n">
+        <v>1139102</v>
+      </c>
+      <c r="MI2" t="n">
+        <v>290118</v>
+      </c>
+      <c r="MJ2" t="n">
+        <v>455556</v>
+      </c>
+      <c r="MK2" t="n">
+        <v>1055423</v>
+      </c>
+      <c r="ML2" t="n">
+        <v>987220</v>
+      </c>
+      <c r="MM2" t="n">
+        <v>470714</v>
+      </c>
+      <c r="MN2" t="n">
+        <v>360880</v>
+      </c>
+      <c r="MO2" t="n">
+        <v>1119162</v>
+      </c>
+      <c r="MP2" t="n">
+        <v>581127</v>
+      </c>
+      <c r="MQ2" t="n">
+        <v>404452</v>
+      </c>
+      <c r="MR2" t="n">
+        <v>566412</v>
+      </c>
+      <c r="MS2" t="n">
+        <v>906196</v>
+      </c>
+      <c r="MT2" t="n">
+        <v>193502</v>
+      </c>
+      <c r="MU2" t="n">
+        <v>257019</v>
+      </c>
+      <c r="MV2" t="n">
+        <v>243793</v>
+      </c>
+      <c r="MW2" t="n">
+        <v>1085358</v>
+      </c>
+      <c r="MX2" t="n">
+        <v>229359</v>
+      </c>
+      <c r="MY2" t="n">
+        <v>813497</v>
+      </c>
+      <c r="MZ2" t="n">
+        <v>1100984</v>
+      </c>
+      <c r="NA2" t="n">
+        <v>235961</v>
+      </c>
+      <c r="NB2" t="n">
+        <v>901148</v>
+      </c>
+      <c r="NC2" t="n">
+        <v>17080</v>
+      </c>
+      <c r="ND2" t="n">
+        <v>858455</v>
+      </c>
+      <c r="NE2" t="n">
+        <v>204590</v>
+      </c>
+      <c r="NF2" t="n">
+        <v>458281</v>
+      </c>
+      <c r="NG2" t="n">
+        <v>252873</v>
+      </c>
+      <c r="NH2" t="n">
+        <v>250817</v>
+      </c>
+      <c r="NI2" t="n">
+        <v>995184</v>
+      </c>
+      <c r="NJ2" t="n">
+        <v>830987</v>
+      </c>
+      <c r="NK2" t="n">
+        <v>703251</v>
+      </c>
+      <c r="NL2" t="n">
+        <v>765005</v>
+      </c>
+      <c r="NM2" t="n">
+        <v>275300</v>
+      </c>
+      <c r="NN2" t="n">
+        <v>941953</v>
+      </c>
+      <c r="NO2" t="n">
+        <v>556188</v>
+      </c>
+      <c r="NP2" t="n">
+        <v>995642</v>
+      </c>
+      <c r="NQ2" t="n">
+        <v>162907</v>
+      </c>
+      <c r="NR2" t="n">
+        <v>637118</v>
+      </c>
+      <c r="NS2" t="n">
+        <v>374672</v>
+      </c>
+      <c r="NT2" t="n">
+        <v>899172</v>
+      </c>
+      <c r="NU2" t="n">
+        <v>652792</v>
+      </c>
+      <c r="NV2" t="n">
+        <v>192701</v>
+      </c>
+      <c r="NW2" t="n">
+        <v>266079</v>
+      </c>
+      <c r="NX2" t="n">
+        <v>136553</v>
+      </c>
+      <c r="NY2" t="n">
+        <v>1110354</v>
+      </c>
+      <c r="NZ2" t="n">
+        <v>854653</v>
+      </c>
+      <c r="OA2" t="n">
+        <v>449184</v>
+      </c>
+      <c r="OB2" t="n">
+        <v>940873</v>
+      </c>
+      <c r="OC2" t="n">
+        <v>420586</v>
+      </c>
+      <c r="OD2" t="n">
+        <v>504556</v>
+      </c>
+      <c r="OE2" t="n">
+        <v>1167550</v>
+      </c>
+      <c r="OF2" t="n">
+        <v>598637</v>
+      </c>
+      <c r="OG2" t="n">
+        <v>368071</v>
+      </c>
+      <c r="OH2" t="n">
+        <v>385532</v>
+      </c>
+      <c r="OI2" t="n">
+        <v>1005218</v>
+      </c>
+      <c r="OJ2" t="n">
+        <v>195616</v>
+      </c>
+      <c r="OK2" t="n">
+        <v>30873</v>
+      </c>
+      <c r="OL2" t="n">
+        <v>490084</v>
+      </c>
+      <c r="OM2" t="n">
+        <v>1166849</v>
+      </c>
+      <c r="ON2" t="n">
+        <v>85912</v>
+      </c>
+      <c r="OO2" t="n">
+        <v>104101</v>
+      </c>
+      <c r="OP2" t="n">
+        <v>1189670</v>
+      </c>
+      <c r="OQ2" t="n">
+        <v>8567</v>
+      </c>
+      <c r="OR2" t="n">
+        <v>1118555</v>
+      </c>
+      <c r="OS2" t="n">
+        <v>441207</v>
+      </c>
+      <c r="OT2" t="n">
+        <v>314499</v>
+      </c>
+      <c r="OU2" t="n">
+        <v>663779</v>
+      </c>
+      <c r="OV2" t="n">
+        <v>1093233</v>
+      </c>
+      <c r="OW2" t="n">
+        <v>275074</v>
+      </c>
+      <c r="OX2" t="n">
+        <v>1028480</v>
+      </c>
+      <c r="OY2" t="n">
+        <v>859772</v>
+      </c>
+      <c r="OZ2" t="n">
+        <v>1085584</v>
+      </c>
+      <c r="PA2" t="n">
+        <v>1206408</v>
+      </c>
+      <c r="PB2" t="n">
+        <v>919805</v>
+      </c>
+      <c r="PC2" t="n">
+        <v>829303</v>
+      </c>
+      <c r="PD2" t="n">
+        <v>985202</v>
+      </c>
+      <c r="PE2" t="n">
+        <v>723172</v>
+      </c>
+      <c r="PF2" t="n">
+        <v>784803</v>
+      </c>
+      <c r="PG2" t="n">
+        <v>327303</v>
+      </c>
+      <c r="PH2" t="n">
+        <v>1022216</v>
+      </c>
+      <c r="PI2" t="n">
+        <v>910185</v>
+      </c>
+      <c r="PJ2" t="n">
+        <v>181153</v>
+      </c>
+      <c r="PK2" t="n">
+        <v>513215</v>
+      </c>
+      <c r="PL2" t="n">
+        <v>285062</v>
+      </c>
+      <c r="PM2" t="n">
+        <v>452308</v>
+      </c>
+      <c r="PN2" t="n">
+        <v>517716</v>
+      </c>
+      <c r="PO2" t="n">
+        <v>953473</v>
+      </c>
+      <c r="PP2" t="n">
+        <v>548254</v>
+      </c>
+      <c r="PQ2" t="n">
+        <v>940625</v>
+      </c>
+      <c r="PR2" t="n">
+        <v>857309</v>
+      </c>
+      <c r="PS2" t="n">
+        <v>1000329</v>
+      </c>
+      <c r="PT2" t="n">
+        <v>487468</v>
+      </c>
+      <c r="PU2" t="n">
+        <v>366959</v>
+      </c>
+      <c r="PV2" t="n">
+        <v>740761</v>
+      </c>
+      <c r="PW2" t="n">
+        <v>472453</v>
+      </c>
+      <c r="PX2" t="n">
+        <v>105256</v>
+      </c>
+      <c r="PY2" t="n">
+        <v>960474</v>
+      </c>
+      <c r="PZ2" t="n">
+        <v>387456</v>
+      </c>
+      <c r="QA2" t="n">
+        <v>452811</v>
+      </c>
+      <c r="QB2" t="n">
+        <v>650211</v>
+      </c>
+      <c r="QC2" t="n">
+        <v>680761</v>
+      </c>
+      <c r="QD2" t="n">
+        <v>92047</v>
+      </c>
+      <c r="QE2" t="n">
+        <v>745305</v>
+      </c>
+      <c r="QF2" t="n">
+        <v>118433</v>
+      </c>
+      <c r="QG2" t="n">
+        <v>403843</v>
+      </c>
+      <c r="QH2" t="n">
+        <v>1039669</v>
+      </c>
+      <c r="QI2" t="n">
+        <v>1104078</v>
+      </c>
+      <c r="QJ2" t="n">
+        <v>512015</v>
+      </c>
+      <c r="QK2" t="n">
+        <v>68902</v>
+      </c>
+      <c r="QL2" t="n">
+        <v>972283</v>
+      </c>
+      <c r="QM2" t="n">
+        <v>723253</v>
+      </c>
+      <c r="QN2" t="n">
+        <v>482232</v>
+      </c>
+      <c r="QO2" t="n">
+        <v>82424</v>
+      </c>
+      <c r="QP2" t="n">
+        <v>547321</v>
+      </c>
+      <c r="QQ2" t="n">
+        <v>1082635</v>
+      </c>
+      <c r="QR2" t="n">
+        <v>594736</v>
+      </c>
+      <c r="QS2" t="n">
+        <v>172305</v>
+      </c>
+      <c r="QT2" t="n">
+        <v>921910</v>
+      </c>
+      <c r="QU2" t="n">
+        <v>981256</v>
+      </c>
+      <c r="QV2" t="n">
+        <v>33590</v>
+      </c>
+      <c r="QW2" t="n">
+        <v>209824</v>
+      </c>
+      <c r="QX2" t="n">
+        <v>1078178</v>
+      </c>
+      <c r="QY2" t="n">
+        <v>70854</v>
+      </c>
+      <c r="QZ2" t="n">
+        <v>872509</v>
+      </c>
+      <c r="RA2" t="n">
+        <v>430122</v>
+      </c>
+      <c r="RB2" t="n">
+        <v>1078377</v>
+      </c>
+      <c r="RC2" t="n">
+        <v>618734</v>
+      </c>
+      <c r="RD2" t="n">
+        <v>726843</v>
+      </c>
+      <c r="RE2" t="n">
+        <v>211580</v>
+      </c>
+      <c r="RF2" t="n">
+        <v>319201</v>
+      </c>
+      <c r="RG2" t="n">
+        <v>221682</v>
+      </c>
+      <c r="RH2" t="n">
+        <v>727433</v>
+      </c>
+      <c r="RI2" t="n">
+        <v>18775</v>
+      </c>
+      <c r="RJ2" t="n">
+        <v>287700</v>
+      </c>
+      <c r="RK2" t="n">
+        <v>805297</v>
+      </c>
+      <c r="RL2" t="n">
+        <v>539615</v>
+      </c>
+      <c r="RM2" t="n">
+        <v>466243</v>
+      </c>
+      <c r="RN2" t="n">
+        <v>858017</v>
+      </c>
+      <c r="RO2" t="n">
+        <v>248856</v>
+      </c>
+      <c r="RP2" t="n">
+        <v>865085</v>
+      </c>
+      <c r="RQ2" t="n">
+        <v>137208</v>
+      </c>
+      <c r="RR2" t="n">
+        <v>1008885</v>
+      </c>
+      <c r="RS2" t="n">
+        <v>1169570</v>
+      </c>
+      <c r="RT2" t="n">
+        <v>300018</v>
+      </c>
+      <c r="RU2" t="n">
+        <v>93834</v>
+      </c>
+      <c r="RV2" t="n">
+        <v>377926</v>
+      </c>
+      <c r="RW2" t="n">
+        <v>348385</v>
+      </c>
+      <c r="RX2" t="n">
+        <v>386729</v>
+      </c>
+      <c r="RY2" t="n">
+        <v>1162432</v>
+      </c>
+      <c r="RZ2" t="n">
+        <v>1226495</v>
+      </c>
+      <c r="SA2" t="n">
+        <v>1133086</v>
+      </c>
+      <c r="SB2" t="n">
+        <v>407989</v>
+      </c>
+      <c r="SC2" t="n">
+        <v>635291</v>
+      </c>
+      <c r="SD2" t="n">
+        <v>424083</v>
+      </c>
+      <c r="SE2" t="n">
+        <v>13690</v>
+      </c>
+      <c r="SF2" t="n">
+        <v>183109</v>
+      </c>
+      <c r="SG2" t="n">
+        <v>679505</v>
+      </c>
+      <c r="SH2" t="n">
+        <v>355339</v>
+      </c>
+      <c r="SI2" t="n">
+        <v>214305</v>
+      </c>
+      <c r="SJ2" t="n">
+        <v>337526</v>
+      </c>
+      <c r="SK2" t="n">
+        <v>1214590</v>
+      </c>
+      <c r="SL2" t="n">
+        <v>97805</v>
+      </c>
+      <c r="SM2" t="n">
+        <v>195447</v>
+      </c>
+      <c r="SN2" t="n">
+        <v>861791</v>
+      </c>
+      <c r="SO2" t="n">
+        <v>872181</v>
+      </c>
+      <c r="SP2" t="n">
+        <v>65873</v>
+      </c>
+      <c r="SQ2" t="n">
+        <v>700886</v>
+      </c>
+      <c r="SR2" t="n">
+        <v>259537</v>
+      </c>
+      <c r="SS2" t="n">
+        <v>161579</v>
+      </c>
+      <c r="ST2" t="n">
+        <v>623235</v>
+      </c>
+      <c r="SU2" t="n">
+        <v>151650</v>
+      </c>
+      <c r="SV2" t="n">
+        <v>615840</v>
+      </c>
+      <c r="SW2" t="n">
+        <v>696077</v>
+      </c>
+      <c r="SX2" t="n">
+        <v>818442</v>
+      </c>
+      <c r="SY2" t="n">
+        <v>1155463</v>
+      </c>
+      <c r="SZ2" t="n">
+        <v>816692</v>
+      </c>
+      <c r="TA2" t="n">
+        <v>59782</v>
+      </c>
+      <c r="TB2" t="n">
+        <v>383818</v>
+      </c>
+      <c r="TC2" t="n">
+        <v>176676</v>
+      </c>
+      <c r="TD2" t="n">
+        <v>149032</v>
+      </c>
+      <c r="TE2" t="n">
+        <v>45862</v>
+      </c>
+      <c r="TF2" t="n">
+        <v>294543</v>
+      </c>
+      <c r="TG2" t="n">
+        <v>246134</v>
+      </c>
+      <c r="TH2" t="n">
+        <v>466911</v>
+      </c>
+      <c r="TI2" t="n">
+        <v>991716</v>
+      </c>
+      <c r="TJ2" t="n">
+        <v>135621</v>
+      </c>
+      <c r="TK2" t="n">
+        <v>220273</v>
+      </c>
+      <c r="TL2" t="n">
+        <v>172209</v>
+      </c>
+      <c r="TM2" t="n">
+        <v>557617</v>
+      </c>
+      <c r="TN2" t="n">
+        <v>497467</v>
+      </c>
+      <c r="TO2" t="n">
+        <v>9881</v>
+      </c>
+      <c r="TP2" t="n">
+        <v>371009</v>
+      </c>
+      <c r="TQ2" t="n">
+        <v>374555</v>
+      </c>
+      <c r="TR2" t="n">
+        <v>1948</v>
+      </c>
+      <c r="TS2" t="n">
+        <v>307950</v>
+      </c>
+      <c r="TT2" t="n">
+        <v>49848</v>
+      </c>
+      <c r="TU2" t="n">
+        <v>893297</v>
+      </c>
+      <c r="TV2" t="n">
+        <v>1136061</v>
+      </c>
+      <c r="TW2" t="n">
+        <v>1038970</v>
+      </c>
+      <c r="TX2" t="n">
+        <v>478772</v>
+      </c>
+      <c r="TY2" t="n">
+        <v>690496</v>
+      </c>
+      <c r="TZ2" t="n">
+        <v>331496</v>
+      </c>
+      <c r="UA2" t="n">
+        <v>686276</v>
+      </c>
+      <c r="UB2" t="n">
+        <v>1115300</v>
+      </c>
+      <c r="UC2" t="n">
+        <v>684662</v>
+      </c>
+      <c r="UD2" t="n">
+        <v>480422</v>
+      </c>
+      <c r="UE2" t="n">
+        <v>90485</v>
+      </c>
+      <c r="UF2" t="n">
+        <v>438382</v>
+      </c>
+      <c r="UG2" t="n">
+        <v>522195</v>
+      </c>
+      <c r="UH2" t="n">
+        <v>920210</v>
+      </c>
+      <c r="UI2" t="n">
+        <v>610075</v>
+      </c>
+      <c r="UJ2" t="n">
+        <v>32613</v>
+      </c>
+      <c r="UK2" t="n">
+        <v>62738</v>
+      </c>
+      <c r="UL2" t="n">
+        <v>333226</v>
+      </c>
+      <c r="UM2" t="n">
+        <v>1183566</v>
+      </c>
+      <c r="UN2" t="n">
+        <v>38186</v>
+      </c>
+      <c r="UO2" t="n">
+        <v>143974</v>
+      </c>
+      <c r="UP2" t="n">
+        <v>682738</v>
+      </c>
+      <c r="UQ2" t="n">
+        <v>1026779</v>
+      </c>
+      <c r="UR2" t="n">
+        <v>839013</v>
+      </c>
+      <c r="US2" t="n">
+        <v>588536</v>
+      </c>
+      <c r="UT2" t="n">
+        <v>197875</v>
+      </c>
+      <c r="UU2" t="n">
+        <v>190408</v>
+      </c>
+      <c r="UV2" t="n">
+        <v>718636</v>
+      </c>
+      <c r="UW2" t="n">
+        <v>609089</v>
+      </c>
+      <c r="UX2" t="n">
+        <v>974952</v>
+      </c>
+      <c r="UY2" t="n">
+        <v>474775</v>
+      </c>
+      <c r="UZ2" t="n">
+        <v>379016</v>
+      </c>
+      <c r="VA2" t="n">
+        <v>1187347</v>
+      </c>
+      <c r="VB2" t="n">
+        <v>1145472</v>
+      </c>
+      <c r="VC2" t="n">
+        <v>1052289</v>
+      </c>
+      <c r="VD2" t="n">
+        <v>762398</v>
+      </c>
+      <c r="VE2" t="n">
+        <v>815558</v>
+      </c>
+      <c r="VF2" t="n">
+        <v>1173002</v>
+      </c>
+      <c r="VG2" t="n">
+        <v>486020</v>
+      </c>
+      <c r="VH2" t="n">
+        <v>356605</v>
+      </c>
+      <c r="VI2" t="n">
+        <v>1037353</v>
+      </c>
+      <c r="VJ2" t="n">
+        <v>802235</v>
+      </c>
+      <c r="VK2" t="n">
+        <v>110545</v>
+      </c>
+      <c r="VL2" t="n">
+        <v>613412</v>
+      </c>
+      <c r="VM2" t="n">
+        <v>841928</v>
+      </c>
+      <c r="VN2" t="n">
+        <v>864245</v>
+      </c>
+      <c r="VO2" t="n">
+        <v>660359</v>
+      </c>
+      <c r="VP2" t="n">
+        <v>897532</v>
+      </c>
+      <c r="VQ2" t="n">
+        <v>113218</v>
+      </c>
+      <c r="VR2" t="n">
+        <v>906630</v>
+      </c>
+      <c r="VS2" t="n">
+        <v>388858</v>
+      </c>
+      <c r="VT2" t="n">
+        <v>973151</v>
+      </c>
+      <c r="VU2" t="n">
+        <v>701917</v>
+      </c>
+      <c r="VV2" t="n">
+        <v>369301</v>
+      </c>
+      <c r="VW2" t="n">
+        <v>469269</v>
+      </c>
+      <c r="VX2" t="n">
+        <v>1117796</v>
+      </c>
+      <c r="VY2" t="n">
+        <v>359311</v>
+      </c>
+      <c r="VZ2" t="n">
+        <v>412636</v>
+      </c>
+      <c r="WA2" t="n">
+        <v>716968</v>
+      </c>
+      <c r="WB2" t="n">
+        <v>292705</v>
+      </c>
+      <c r="WC2" t="n">
+        <v>631266</v>
+      </c>
+      <c r="WD2" t="n">
+        <v>533399</v>
+      </c>
+      <c r="WE2" t="n">
+        <v>313381</v>
+      </c>
+      <c r="WF2" t="n">
+        <v>672194</v>
+      </c>
+      <c r="WG2" t="n">
+        <v>22119</v>
+      </c>
+      <c r="WH2" t="n">
+        <v>902356</v>
+      </c>
+      <c r="WI2" t="n">
+        <v>167886</v>
+      </c>
+      <c r="WJ2" t="n">
+        <v>42264</v>
+      </c>
+      <c r="WK2" t="n">
+        <v>1033807</v>
+      </c>
+      <c r="WL2" t="n">
+        <v>808123</v>
+      </c>
+      <c r="WM2" t="n">
+        <v>956704</v>
+      </c>
+      <c r="WN2" t="n">
+        <v>157976</v>
+      </c>
+      <c r="WO2" t="n">
+        <v>1174061</v>
+      </c>
+      <c r="WP2" t="n">
+        <v>134194</v>
+      </c>
+      <c r="WQ2" t="n">
+        <v>749617</v>
+      </c>
+      <c r="WR2" t="n">
+        <v>1210961</v>
+      </c>
+      <c r="WS2" t="n">
+        <v>980806</v>
+      </c>
+      <c r="WT2" t="n">
+        <v>939</v>
+      </c>
+      <c r="WU2" t="n">
+        <v>627762</v>
+      </c>
+      <c r="WV2" t="n">
+        <v>782803</v>
+      </c>
+      <c r="WW2" t="n">
+        <v>254309</v>
+      </c>
+      <c r="WX2" t="n">
+        <v>810749</v>
+      </c>
+      <c r="WY2" t="n">
+        <v>301027</v>
+      </c>
+      <c r="WZ2" t="n">
+        <v>753217</v>
+      </c>
+      <c r="XA2" t="n">
+        <v>851760</v>
+      </c>
+      <c r="XB2" t="n">
+        <v>137999</v>
+      </c>
+      <c r="XC2" t="n">
+        <v>665839</v>
+      </c>
+      <c r="XD2" t="n">
+        <v>645954</v>
+      </c>
+      <c r="XE2" t="n">
+        <v>549642</v>
+      </c>
+      <c r="XF2" t="n">
+        <v>576634</v>
+      </c>
+      <c r="XG2" t="n">
+        <v>738924</v>
+      </c>
+      <c r="XH2" t="n">
+        <v>496428</v>
+      </c>
+      <c r="XI2" t="n">
+        <v>107583</v>
+      </c>
+      <c r="XJ2" t="n">
+        <v>643118</v>
+      </c>
+      <c r="XK2" t="n">
+        <v>450921</v>
+      </c>
+      <c r="XL2" t="n">
+        <v>92809</v>
+      </c>
+      <c r="XM2" t="n">
+        <v>357478</v>
+      </c>
+      <c r="XN2" t="n">
+        <v>1000768</v>
+      </c>
+      <c r="XO2" t="n">
+        <v>467841</v>
+      </c>
+      <c r="XP2" t="n">
+        <v>100634</v>
+      </c>
+      <c r="XQ2" t="n">
+        <v>597335</v>
+      </c>
+      <c r="XR2" t="n">
+        <v>45831</v>
+      </c>
+      <c r="XS2" t="n">
+        <v>800517</v>
+      </c>
+      <c r="XT2" t="n">
+        <v>1041601</v>
+      </c>
+      <c r="XU2" t="n">
+        <v>558631</v>
+      </c>
+      <c r="XV2" t="n">
+        <v>435741</v>
+      </c>
+      <c r="XW2" t="n">
+        <v>674237</v>
+      </c>
+      <c r="XX2" t="n">
+        <v>848608</v>
+      </c>
+      <c r="XY2" t="n">
+        <v>1003270</v>
+      </c>
+      <c r="XZ2" t="n">
+        <v>46808</v>
+      </c>
+      <c r="YA2" t="n">
+        <v>31576</v>
+      </c>
+      <c r="YB2" t="n">
+        <v>221176</v>
+      </c>
+      <c r="YC2" t="n">
+        <v>786638</v>
+      </c>
+      <c r="YD2" t="n">
+        <v>315694</v>
+      </c>
+      <c r="YE2" t="n">
+        <v>126807</v>
+      </c>
+      <c r="YF2" t="n">
+        <v>1214736</v>
+      </c>
+      <c r="YG2" t="n">
+        <v>741337</v>
+      </c>
+      <c r="YH2" t="n">
+        <v>159181</v>
+      </c>
+      <c r="YI2" t="n">
+        <v>362340</v>
+      </c>
+      <c r="YJ2" t="n">
+        <v>117323</v>
+      </c>
+      <c r="YK2" t="n">
+        <v>221694</v>
+      </c>
+      <c r="YL2" t="n">
+        <v>655428</v>
+      </c>
+      <c r="YM2" t="n">
+        <v>403204</v>
+      </c>
+      <c r="YN2" t="n">
+        <v>168217</v>
+      </c>
+      <c r="YO2" t="n">
+        <v>390593</v>
+      </c>
+      <c r="YP2" t="n">
+        <v>111898</v>
+      </c>
+      <c r="YQ2" t="n">
+        <v>614341</v>
+      </c>
+      <c r="YR2" t="n">
+        <v>49741</v>
+      </c>
+      <c r="YS2" t="n">
+        <v>982996</v>
+      </c>
+      <c r="YT2" t="n">
+        <v>1198404</v>
+      </c>
+      <c r="YU2" t="n">
+        <v>419450</v>
+      </c>
+      <c r="YV2" t="n">
+        <v>518762</v>
+      </c>
+      <c r="YW2" t="n">
+        <v>948540</v>
+      </c>
+      <c r="YX2" t="n">
+        <v>884610</v>
+      </c>
+      <c r="YY2" t="n">
+        <v>279991</v>
+      </c>
+      <c r="YZ2" t="n">
+        <v>901308</v>
+      </c>
+      <c r="ZA2" t="n">
+        <v>796203</v>
+      </c>
+      <c r="ZB2" t="n">
+        <v>814896</v>
+      </c>
+      <c r="ZC2" t="n">
+        <v>774272</v>
+      </c>
+      <c r="ZD2" t="n">
+        <v>1024053</v>
+      </c>
+      <c r="ZE2" t="n">
+        <v>100797</v>
+      </c>
+      <c r="ZF2" t="n">
+        <v>498654</v>
+      </c>
+      <c r="ZG2" t="n">
+        <v>391933</v>
+      </c>
+      <c r="ZH2" t="n">
+        <v>583018</v>
+      </c>
+      <c r="ZI2" t="n">
+        <v>217558</v>
+      </c>
+      <c r="ZJ2" t="n">
+        <v>846251</v>
+      </c>
+      <c r="ZK2" t="n">
+        <v>481378</v>
+      </c>
+      <c r="ZL2" t="n">
+        <v>199972</v>
+      </c>
+      <c r="ZM2" t="n">
+        <v>146434</v>
+      </c>
+      <c r="ZN2" t="n">
+        <v>413058</v>
+      </c>
+      <c r="ZO2" t="n">
+        <v>51256</v>
+      </c>
+      <c r="ZP2" t="n">
+        <v>625798</v>
+      </c>
+      <c r="ZQ2" t="n">
+        <v>95625</v>
+      </c>
+      <c r="ZR2" t="n">
+        <v>622355</v>
+      </c>
+      <c r="ZS2" t="n">
+        <v>1111446</v>
+      </c>
+      <c r="ZT2" t="n">
         <v>1036754</v>
       </c>
-      <c r="O2" t="n">
-        <v>964178</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1067111</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>650581</v>
-      </c>
-      <c r="R2" t="n">
-        <v>948341</v>
-      </c>
-      <c r="S2" t="n">
-        <v>161530</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1079654</v>
-      </c>
-      <c r="U2" t="n">
-        <v>118832</v>
-      </c>
-      <c r="V2" t="n">
-        <v>963157</v>
-      </c>
-      <c r="W2" t="n">
-        <v>210976</v>
-      </c>
-      <c r="X2" t="n">
-        <v>118353</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>266606</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>338163</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>593392</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>331403</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>83040</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2061</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>174631</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>429774</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>137552</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>870013</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>185526</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>694362</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>582988</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>152827</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>943317</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>595668</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>132079</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>744748</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1041100</v>
-      </c>
-      <c r="AR2" t="n">
+      <c r="ZU2" t="n">
+        <v>77214</v>
+      </c>
+      <c r="ZV2" t="n">
+        <v>186445</v>
+      </c>
+      <c r="ZW2" t="n">
+        <v>307956</v>
+      </c>
+      <c r="ZX2" t="n">
+        <v>1105219</v>
+      </c>
+      <c r="ZY2" t="n">
+        <v>335329</v>
+      </c>
+      <c r="ZZ2" t="n">
+        <v>37305</v>
+      </c>
+      <c r="AAA2" t="n">
+        <v>510435</v>
+      </c>
+      <c r="AAB2" t="n">
+        <v>735320</v>
+      </c>
+      <c r="AAC2" t="n">
+        <v>923909</v>
+      </c>
+      <c r="AAD2" t="n">
+        <v>337052</v>
+      </c>
+      <c r="AAE2" t="n">
+        <v>371414</v>
+      </c>
+      <c r="AAF2" t="n">
+        <v>1205759</v>
+      </c>
+      <c r="AAG2" t="n">
+        <v>46264</v>
+      </c>
+      <c r="AAH2" t="n">
+        <v>1025179</v>
+      </c>
+      <c r="AAI2" t="n">
+        <v>929532</v>
+      </c>
+      <c r="AAJ2" t="n">
+        <v>85511</v>
+      </c>
+      <c r="AAK2" t="n">
+        <v>1200866</v>
+      </c>
+      <c r="AAL2" t="n">
+        <v>704566</v>
+      </c>
+      <c r="AAM2" t="n">
+        <v>23029</v>
+      </c>
+      <c r="AAN2" t="n">
+        <v>443729</v>
+      </c>
+      <c r="AAO2" t="n">
+        <v>75424</v>
+      </c>
+      <c r="AAP2" t="n">
+        <v>334581</v>
+      </c>
+      <c r="AAQ2" t="n">
+        <v>293046</v>
+      </c>
+      <c r="AAR2" t="n">
+        <v>534864</v>
+      </c>
+      <c r="AAS2" t="n">
+        <v>114544</v>
+      </c>
+      <c r="AAT2" t="n">
+        <v>870715</v>
+      </c>
+      <c r="AAU2" t="n">
+        <v>1123542</v>
+      </c>
+      <c r="AAV2" t="n">
+        <v>13755</v>
+      </c>
+      <c r="AAW2" t="n">
+        <v>491986</v>
+      </c>
+      <c r="AAX2" t="n">
+        <v>231301</v>
+      </c>
+      <c r="AAY2" t="n">
+        <v>391164</v>
+      </c>
+      <c r="AAZ2" t="n">
+        <v>347182</v>
+      </c>
+      <c r="ABA2" t="n">
+        <v>201206</v>
+      </c>
+      <c r="ABB2" t="n">
+        <v>663422</v>
+      </c>
+      <c r="ABC2" t="n">
+        <v>53728</v>
+      </c>
+      <c r="ABD2" t="n">
+        <v>384233</v>
+      </c>
+      <c r="ABE2" t="n">
+        <v>567417</v>
+      </c>
+      <c r="ABF2" t="n">
+        <v>1177322</v>
+      </c>
+      <c r="ABG2" t="n">
+        <v>1088176</v>
+      </c>
+      <c r="ABH2" t="n">
+        <v>364731</v>
+      </c>
+      <c r="ABI2" t="n">
+        <v>357554</v>
+      </c>
+      <c r="ABJ2" t="n">
+        <v>1851</v>
+      </c>
+      <c r="ABK2" t="n">
+        <v>595254</v>
+      </c>
+      <c r="ABL2" t="n">
+        <v>44070</v>
+      </c>
+      <c r="ABM2" t="n">
+        <v>762448</v>
+      </c>
+      <c r="ABN2" t="n">
+        <v>74296</v>
+      </c>
+      <c r="ABO2" t="n">
+        <v>19412</v>
+      </c>
+      <c r="ABP2" t="n">
+        <v>178251</v>
+      </c>
+      <c r="ABQ2" t="n">
+        <v>260806</v>
+      </c>
+      <c r="ABR2" t="n">
+        <v>526609</v>
+      </c>
+      <c r="ABS2" t="n">
+        <v>207277</v>
+      </c>
+      <c r="ABT2" t="n">
+        <v>801020</v>
+      </c>
+      <c r="ABU2" t="n">
+        <v>682881</v>
+      </c>
+      <c r="ABV2" t="n">
+        <v>158045</v>
+      </c>
+      <c r="ABW2" t="n">
+        <v>977054</v>
+      </c>
+      <c r="ABX2" t="n">
+        <v>944639</v>
+      </c>
+      <c r="ABY2" t="n">
+        <v>530554</v>
+      </c>
+      <c r="ABZ2" t="n">
+        <v>501249</v>
+      </c>
+      <c r="ACA2" t="n">
+        <v>945833</v>
+      </c>
+      <c r="ACB2" t="n">
+        <v>729853</v>
+      </c>
+      <c r="ACC2" t="n">
+        <v>1014586</v>
+      </c>
+      <c r="ACD2" t="n">
+        <v>421167</v>
+      </c>
+      <c r="ACE2" t="n">
+        <v>1142532</v>
+      </c>
+      <c r="ACF2" t="n">
+        <v>690277</v>
+      </c>
+      <c r="ACG2" t="n">
+        <v>243748</v>
+      </c>
+      <c r="ACH2" t="n">
+        <v>321518</v>
+      </c>
+      <c r="ACI2" t="n">
+        <v>453866</v>
+      </c>
+      <c r="ACJ2" t="n">
+        <v>750696</v>
+      </c>
+      <c r="ACK2" t="n">
+        <v>1208914</v>
+      </c>
+      <c r="ACL2" t="n">
+        <v>1144305</v>
+      </c>
+      <c r="ACM2" t="n">
+        <v>128013</v>
+      </c>
+      <c r="ACN2" t="n">
+        <v>273127</v>
+      </c>
+      <c r="ACO2" t="n">
+        <v>139855</v>
+      </c>
+      <c r="ACP2" t="n">
+        <v>133111</v>
+      </c>
+      <c r="ACQ2" t="n">
+        <v>85179</v>
+      </c>
+      <c r="ACR2" t="n">
+        <v>349554</v>
+      </c>
+      <c r="ACS2" t="n">
+        <v>454623</v>
+      </c>
+      <c r="ACT2" t="n">
+        <v>917944</v>
+      </c>
+      <c r="ACU2" t="n">
+        <v>862261</v>
+      </c>
+      <c r="ACV2" t="n">
+        <v>1091819</v>
+      </c>
+      <c r="ACW2" t="n">
+        <v>869236</v>
+      </c>
+      <c r="ACX2" t="n">
+        <v>57008</v>
+      </c>
+      <c r="ACY2" t="n">
+        <v>667335</v>
+      </c>
+      <c r="ACZ2" t="n">
+        <v>352091</v>
+      </c>
+      <c r="ADA2" t="n">
+        <v>68328</v>
+      </c>
+      <c r="ADB2" t="n">
+        <v>181867</v>
+      </c>
+      <c r="ADC2" t="n">
+        <v>41719</v>
+      </c>
+      <c r="ADD2" t="n">
+        <v>1160089</v>
+      </c>
+      <c r="ADE2" t="n">
+        <v>214470</v>
+      </c>
+      <c r="ADF2" t="n">
+        <v>283474</v>
+      </c>
+      <c r="ADG2" t="n">
+        <v>474159</v>
+      </c>
+      <c r="ADH2" t="n">
+        <v>25652</v>
+      </c>
+      <c r="ADI2" t="n">
+        <v>70399</v>
+      </c>
+      <c r="ADJ2" t="n">
+        <v>747217</v>
+      </c>
+      <c r="ADK2" t="n">
+        <v>73193</v>
+      </c>
+      <c r="ADL2" t="n">
+        <v>1015782</v>
+      </c>
+      <c r="ADM2" t="n">
+        <v>366634</v>
+      </c>
+      <c r="ADN2" t="n">
+        <v>153078</v>
+      </c>
+      <c r="ADO2" t="n">
+        <v>176159</v>
+      </c>
+      <c r="ADP2" t="n">
+        <v>771090</v>
+      </c>
+      <c r="ADQ2" t="n">
+        <v>1218173</v>
+      </c>
+      <c r="ADR2" t="n">
+        <v>1041431</v>
+      </c>
+      <c r="ADS2" t="n">
+        <v>588733</v>
+      </c>
+      <c r="ADT2" t="n">
+        <v>208496</v>
+      </c>
+      <c r="ADU2" t="n">
+        <v>1097217</v>
+      </c>
+      <c r="ADV2" t="n">
+        <v>317924</v>
+      </c>
+      <c r="ADW2" t="n">
+        <v>282364</v>
+      </c>
+      <c r="ADX2" t="n">
+        <v>506624</v>
+      </c>
+      <c r="ADY2" t="n">
+        <v>648974</v>
+      </c>
+      <c r="ADZ2" t="n">
+        <v>620356</v>
+      </c>
+      <c r="AEA2" t="n">
+        <v>71452</v>
+      </c>
+      <c r="AEB2" t="n">
+        <v>270786</v>
+      </c>
+      <c r="AEC2" t="n">
+        <v>1032461</v>
+      </c>
+      <c r="AED2" t="n">
+        <v>255082</v>
+      </c>
+      <c r="AEE2" t="n">
+        <v>275323</v>
+      </c>
+      <c r="AEF2" t="n">
+        <v>501561</v>
+      </c>
+      <c r="AEG2" t="n">
+        <v>1081968</v>
+      </c>
+      <c r="AEH2" t="n">
+        <v>573877</v>
+      </c>
+      <c r="AEI2" t="n">
+        <v>11586</v>
+      </c>
+      <c r="AEJ2" t="n">
+        <v>280328</v>
+      </c>
+      <c r="AEK2" t="n">
+        <v>201767</v>
+      </c>
+      <c r="AEL2" t="n">
+        <v>736598</v>
+      </c>
+      <c r="AEM2" t="n">
+        <v>202699</v>
+      </c>
+      <c r="AEN2" t="n">
+        <v>1011010</v>
+      </c>
+      <c r="AEO2" t="n">
+        <v>235595</v>
+      </c>
+      <c r="AEP2" t="n">
+        <v>919799</v>
+      </c>
+      <c r="AEQ2" t="n">
+        <v>877242</v>
+      </c>
+      <c r="AER2" t="n">
+        <v>1152484</v>
+      </c>
+      <c r="AES2" t="n">
+        <v>865186</v>
+      </c>
+      <c r="AET2" t="n">
+        <v>369350</v>
+      </c>
+      <c r="AEU2" t="n">
+        <v>99650</v>
+      </c>
+      <c r="AEV2" t="n">
+        <v>434824</v>
+      </c>
+      <c r="AEW2" t="n">
+        <v>1121046</v>
+      </c>
+      <c r="AEX2" t="n">
+        <v>890796</v>
+      </c>
+      <c r="AEY2" t="n">
+        <v>66705</v>
+      </c>
+      <c r="AEZ2" t="n">
+        <v>218712</v>
+      </c>
+      <c r="AFA2" t="n">
+        <v>707647</v>
+      </c>
+      <c r="AFB2" t="n">
+        <v>959653</v>
+      </c>
+      <c r="AFC2" t="n">
+        <v>693450</v>
+      </c>
+      <c r="AFD2" t="n">
+        <v>152477</v>
+      </c>
+      <c r="AFE2" t="n">
+        <v>892017</v>
+      </c>
+      <c r="AFF2" t="n">
+        <v>1175469</v>
+      </c>
+      <c r="AFG2" t="n">
+        <v>102031</v>
+      </c>
+      <c r="AFH2" t="n">
+        <v>639364</v>
+      </c>
+      <c r="AFI2" t="n">
+        <v>256025</v>
+      </c>
+      <c r="AFJ2" t="n">
+        <v>825025</v>
+      </c>
+      <c r="AFK2" t="n">
+        <v>113173</v>
+      </c>
+      <c r="AFL2" t="n">
+        <v>1195065</v>
+      </c>
+      <c r="AFM2" t="n">
+        <v>888041</v>
+      </c>
+      <c r="AFN2" t="n">
+        <v>769614</v>
+      </c>
+      <c r="AFO2" t="n">
+        <v>678987</v>
+      </c>
+      <c r="AFP2" t="n">
+        <v>1070270</v>
+      </c>
+      <c r="AFQ2" t="n">
+        <v>850098</v>
+      </c>
+      <c r="AFR2" t="n">
+        <v>756034</v>
+      </c>
+      <c r="AFS2" t="n">
+        <v>162307</v>
+      </c>
+      <c r="AFT2" t="n">
+        <v>389783</v>
+      </c>
+      <c r="AFU2" t="n">
+        <v>605454</v>
+      </c>
+      <c r="AFV2" t="n">
+        <v>129087</v>
+      </c>
+      <c r="AFW2" t="n">
+        <v>482144</v>
+      </c>
+      <c r="AFX2" t="n">
+        <v>984239</v>
+      </c>
+      <c r="AFY2" t="n">
+        <v>714324</v>
+      </c>
+      <c r="AFZ2" t="n">
+        <v>854011</v>
+      </c>
+      <c r="AGA2" t="n">
+        <v>123737</v>
+      </c>
+      <c r="AGB2" t="n">
+        <v>400816</v>
+      </c>
+      <c r="AGC2" t="n">
+        <v>667591</v>
+      </c>
+      <c r="AGD2" t="n">
+        <v>448881</v>
+      </c>
+      <c r="AGE2" t="n">
+        <v>1162262</v>
+      </c>
+      <c r="AGF2" t="n">
+        <v>524610</v>
+      </c>
+      <c r="AGG2" t="n">
+        <v>1150232</v>
+      </c>
+      <c r="AGH2" t="n">
+        <v>948823</v>
+      </c>
+      <c r="AGI2" t="n">
+        <v>251941</v>
+      </c>
+      <c r="AGJ2" t="n">
+        <v>436185</v>
+      </c>
+      <c r="AGK2" t="n">
+        <v>117348</v>
+      </c>
+      <c r="AGL2" t="n">
+        <v>162206</v>
+      </c>
+      <c r="AGM2" t="n">
+        <v>395077</v>
+      </c>
+      <c r="AGN2" t="n">
+        <v>943613</v>
+      </c>
+      <c r="AGO2" t="n">
+        <v>895465</v>
+      </c>
+      <c r="AGP2" t="n">
+        <v>744342</v>
+      </c>
+      <c r="AGQ2" t="n">
+        <v>422335</v>
+      </c>
+      <c r="AGR2" t="n">
+        <v>1089657</v>
+      </c>
+      <c r="AGS2" t="n">
+        <v>188059</v>
+      </c>
+      <c r="AGT2" t="n">
+        <v>99167</v>
+      </c>
+      <c r="AGU2" t="n">
+        <v>444187</v>
+      </c>
+      <c r="AGV2" t="n">
+        <v>1220033</v>
+      </c>
+      <c r="AGW2" t="n">
+        <v>825629</v>
+      </c>
+      <c r="AGX2" t="n">
+        <v>591241</v>
+      </c>
+      <c r="AGY2" t="n">
+        <v>794248</v>
+      </c>
+      <c r="AGZ2" t="n">
+        <v>515456</v>
+      </c>
+      <c r="AHA2" t="n">
+        <v>71881</v>
+      </c>
+      <c r="AHB2" t="n">
+        <v>184975</v>
+      </c>
+      <c r="AHC2" t="n">
+        <v>1107108</v>
+      </c>
+      <c r="AHD2" t="n">
+        <v>263186</v>
+      </c>
+      <c r="AHE2" t="n">
+        <v>272142</v>
+      </c>
+      <c r="AHF2" t="n">
+        <v>1066713</v>
+      </c>
+      <c r="AHG2" t="n">
+        <v>341691</v>
+      </c>
+      <c r="AHH2" t="n">
+        <v>494542</v>
+      </c>
+      <c r="AHI2" t="n">
+        <v>644741</v>
+      </c>
+      <c r="AHJ2" t="n">
+        <v>529076</v>
+      </c>
+      <c r="AHK2" t="n">
+        <v>1112973</v>
+      </c>
+      <c r="AHL2" t="n">
+        <v>77907</v>
+      </c>
+      <c r="AHM2" t="n">
+        <v>810096</v>
+      </c>
+      <c r="AHN2" t="n">
+        <v>353130</v>
+      </c>
+      <c r="AHO2" t="n">
+        <v>248139</v>
+      </c>
+      <c r="AHP2" t="n">
+        <v>690543</v>
+      </c>
+      <c r="AHQ2" t="n">
+        <v>277770</v>
+      </c>
+      <c r="AHR2" t="n">
+        <v>28318</v>
+      </c>
+      <c r="AHS2" t="n">
+        <v>574778</v>
+      </c>
+      <c r="AHT2" t="n">
+        <v>808724</v>
+      </c>
+      <c r="AHU2" t="n">
         <v>0</v>
       </c>
-      <c r="AS2" t="n">
-        <v>628175</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1147614</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>943127</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>219837</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1058817</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>177515</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>682122</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>47981</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1176468</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>368133</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>621975</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>737922</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>982354</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>37498</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>15978</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1108346</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>172342</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>157347</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>154978</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1174727</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>620406</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1111703</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1003034</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>219671</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>874049</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>762079</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>8229</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>399346</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>3769</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>13920</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1182657</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>235862</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>1066397</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>595399</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>1043318</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>274805</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>770855</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>1004477</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>1071430</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>802799</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>609310</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>949663</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>910344</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>458146</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>58689</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>310854</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>917844</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>258464</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>112013</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>997775</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>69185</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>423857</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>162496</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>39516</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>1051868</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>718292</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>644242</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>773766</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>501498</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>1191740</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>1136935</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>46721</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>787365</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>743397</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>29293</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>503312</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>117092</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>298435</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>717110</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>838692</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>420491</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>373131</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>667018</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>305977</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>144934</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>1128655</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>417062</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>614788</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>1117295</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>992840</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>999131</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>795538</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>573370</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>171277</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>219894</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>489825</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>507412</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>683544</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>465207</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>77394</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>733185</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>34850</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>1059492</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>25075</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>190126</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1144767</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>20742</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>535128</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>757621</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>427286</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>683371</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>1822</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>1174341</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>901580</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>972941</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>553975</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>514064</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>702640</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>843861</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>854896</v>
-      </c>
-      <c r="EY2" t="n">
-        <v>845831</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>231488</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>299143</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>818882</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>1135396</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>1120682</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>643587</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>470054</v>
-      </c>
-      <c r="FG2" t="n">
-        <v>247278</v>
-      </c>
-      <c r="FH2" t="n">
-        <v>169624</v>
-      </c>
-      <c r="FI2" t="n">
-        <v>439465</v>
-      </c>
-      <c r="FJ2" t="n">
-        <v>133336</v>
-      </c>
-      <c r="FK2" t="n">
-        <v>1093435</v>
-      </c>
-      <c r="FL2" t="n">
-        <v>837896</v>
-      </c>
-      <c r="FM2" t="n">
-        <v>746683</v>
-      </c>
-      <c r="FN2" t="n">
-        <v>464233</v>
-      </c>
-      <c r="FO2" t="n">
-        <v>1030409</v>
-      </c>
-      <c r="FP2" t="n">
-        <v>807036</v>
-      </c>
-      <c r="FQ2" t="n">
-        <v>741354</v>
-      </c>
-      <c r="FR2" t="n">
-        <v>862403</v>
-      </c>
-      <c r="FS2" t="n">
-        <v>55479</v>
-      </c>
-      <c r="FT2" t="n">
-        <v>86331</v>
-      </c>
-      <c r="FU2" t="n">
-        <v>500676</v>
-      </c>
-      <c r="FV2" t="n">
-        <v>1024105</v>
-      </c>
-      <c r="FW2" t="n">
-        <v>725844</v>
-      </c>
-      <c r="FX2" t="n">
-        <v>1115110</v>
-      </c>
-      <c r="FY2" t="n">
-        <v>656988</v>
-      </c>
-      <c r="FZ2" t="n">
-        <v>851121</v>
-      </c>
-      <c r="GA2" t="n">
-        <v>800463</v>
-      </c>
-      <c r="GB2" t="n">
-        <v>422036</v>
-      </c>
-      <c r="GC2" t="n">
-        <v>692005</v>
-      </c>
-      <c r="GD2" t="n">
-        <v>181285</v>
-      </c>
-      <c r="GE2" t="n">
-        <v>824298</v>
-      </c>
-      <c r="GF2" t="n">
-        <v>18129</v>
-      </c>
-      <c r="GG2" t="n">
-        <v>718096</v>
-      </c>
-      <c r="GH2" t="n">
-        <v>241259</v>
-      </c>
-      <c r="GI2" t="n">
-        <v>207364</v>
-      </c>
-      <c r="GJ2" t="n">
-        <v>1131133</v>
-      </c>
-      <c r="GK2" t="n">
-        <v>995125</v>
-      </c>
-      <c r="GL2" t="n">
-        <v>279066</v>
-      </c>
-      <c r="GM2" t="n">
-        <v>885285</v>
-      </c>
-      <c r="GN2" t="n">
-        <v>1073149</v>
-      </c>
-      <c r="GO2" t="n">
-        <v>358622</v>
-      </c>
-      <c r="GP2" t="n">
-        <v>234553</v>
-      </c>
-      <c r="GQ2" t="n">
-        <v>198080</v>
-      </c>
-      <c r="GR2" t="n">
-        <v>21157</v>
-      </c>
-      <c r="GS2" t="n">
-        <v>313881</v>
-      </c>
-      <c r="GT2" t="n">
-        <v>386699</v>
-      </c>
-      <c r="GU2" t="n">
-        <v>724237</v>
-      </c>
-      <c r="GV2" t="n">
-        <v>788679</v>
-      </c>
-      <c r="GW2" t="n">
-        <v>912486</v>
-      </c>
-      <c r="GX2" t="n">
-        <v>723284</v>
-      </c>
-      <c r="GY2" t="n">
-        <v>1043389</v>
-      </c>
-      <c r="GZ2" t="n">
-        <v>59061</v>
-      </c>
-      <c r="HA2" t="n">
-        <v>317506</v>
-      </c>
-      <c r="HB2" t="n">
-        <v>114942</v>
-      </c>
-      <c r="HC2" t="n">
-        <v>1117277</v>
-      </c>
-      <c r="HD2" t="n">
-        <v>469125</v>
-      </c>
-      <c r="HE2" t="n">
-        <v>765470</v>
-      </c>
-      <c r="HF2" t="n">
-        <v>273394</v>
-      </c>
-      <c r="HG2" t="n">
-        <v>350815</v>
-      </c>
-      <c r="HH2" t="n">
-        <v>696814</v>
-      </c>
-      <c r="HI2" t="n">
-        <v>319744</v>
-      </c>
-      <c r="HJ2" t="n">
-        <v>356337</v>
-      </c>
-      <c r="HK2" t="n">
-        <v>940621</v>
-      </c>
-      <c r="HL2" t="n">
-        <v>266232</v>
-      </c>
-      <c r="HM2" t="n">
-        <v>326241</v>
-      </c>
-      <c r="HN2" t="n">
-        <v>629805</v>
-      </c>
-      <c r="HO2" t="n">
-        <v>563916</v>
-      </c>
-      <c r="HP2" t="n">
-        <v>387655</v>
-      </c>
-      <c r="HQ2" t="n">
-        <v>379267</v>
-      </c>
-      <c r="HR2" t="n">
-        <v>303485</v>
-      </c>
-      <c r="HS2" t="n">
-        <v>126058</v>
-      </c>
-      <c r="HT2" t="n">
-        <v>797386</v>
-      </c>
-      <c r="HU2" t="n">
-        <v>617534</v>
-      </c>
-      <c r="HV2" t="n">
-        <v>775339</v>
-      </c>
-      <c r="HW2" t="n">
-        <v>231319</v>
-      </c>
-      <c r="HX2" t="n">
-        <v>882174</v>
-      </c>
-      <c r="HY2" t="n">
-        <v>962977</v>
-      </c>
-      <c r="HZ2" t="n">
-        <v>23466</v>
-      </c>
-      <c r="IA2" t="n">
-        <v>248911</v>
-      </c>
-      <c r="IB2" t="n">
-        <v>727928</v>
-      </c>
-      <c r="IC2" t="n">
-        <v>1087058</v>
-      </c>
-      <c r="ID2" t="n">
-        <v>856198</v>
-      </c>
-      <c r="IE2" t="n">
-        <v>565348</v>
-      </c>
-      <c r="IF2" t="n">
-        <v>282714</v>
-      </c>
-      <c r="IG2" t="n">
-        <v>45094</v>
-      </c>
-      <c r="IH2" t="n">
-        <v>919106</v>
-      </c>
-      <c r="II2" t="n">
-        <v>194071</v>
-      </c>
-      <c r="IJ2" t="n">
-        <v>663324</v>
-      </c>
-      <c r="IK2" t="n">
-        <v>664327</v>
-      </c>
-      <c r="IL2" t="n">
-        <v>984909</v>
-      </c>
-      <c r="IM2" t="n">
-        <v>910752</v>
-      </c>
-      <c r="IN2" t="n">
-        <v>154146</v>
-      </c>
-      <c r="IO2" t="n">
-        <v>166571</v>
-      </c>
-      <c r="IP2" t="n">
-        <v>719433</v>
-      </c>
-      <c r="IQ2" t="n">
-        <v>233554</v>
-      </c>
-      <c r="IR2" t="n">
-        <v>424704</v>
-      </c>
-      <c r="IS2" t="n">
-        <v>943905</v>
-      </c>
-      <c r="IT2" t="n">
-        <v>251129</v>
-      </c>
-      <c r="IU2" t="n">
-        <v>816168</v>
-      </c>
-      <c r="IV2" t="n">
-        <v>328325</v>
-      </c>
-      <c r="IW2" t="n">
-        <v>815978</v>
-      </c>
-      <c r="IX2" t="n">
-        <v>725602</v>
-      </c>
-      <c r="IY2" t="n">
-        <v>454765</v>
-      </c>
-      <c r="IZ2" t="n">
-        <v>413742</v>
-      </c>
-      <c r="JA2" t="n">
-        <v>1014294</v>
-      </c>
-      <c r="JB2" t="n">
-        <v>493923</v>
-      </c>
-      <c r="JC2" t="n">
-        <v>929103</v>
-      </c>
-      <c r="JD2" t="n">
-        <v>751806</v>
-      </c>
-      <c r="JE2" t="n">
-        <v>487853</v>
-      </c>
-      <c r="JF2" t="n">
-        <v>976636</v>
-      </c>
-      <c r="JG2" t="n">
-        <v>412094</v>
-      </c>
-      <c r="JH2" t="n">
-        <v>1162479</v>
-      </c>
-      <c r="JI2" t="n">
-        <v>639505</v>
-      </c>
-      <c r="JJ2" t="n">
-        <v>1026291</v>
-      </c>
-      <c r="JK2" t="n">
-        <v>1090058</v>
-      </c>
-      <c r="JL2" t="n">
-        <v>559350</v>
-      </c>
-      <c r="JM2" t="n">
-        <v>590426</v>
-      </c>
-      <c r="JN2" t="n">
-        <v>1088854</v>
-      </c>
-      <c r="JO2" t="n">
-        <v>625716</v>
-      </c>
-      <c r="JP2" t="n">
-        <v>975363</v>
-      </c>
-      <c r="JQ2" t="n">
-        <v>1052326</v>
-      </c>
-      <c r="JR2" t="n">
-        <v>301759</v>
-      </c>
-      <c r="JS2" t="n">
-        <v>143361</v>
-      </c>
-      <c r="JT2" t="n">
-        <v>361701</v>
-      </c>
-      <c r="JU2" t="n">
-        <v>1078800</v>
-      </c>
-      <c r="JV2" t="n">
-        <v>107575</v>
-      </c>
-      <c r="JW2" t="n">
-        <v>829075</v>
-      </c>
-      <c r="JX2" t="n">
-        <v>1052663</v>
-      </c>
-      <c r="JY2" t="n">
-        <v>97293</v>
-      </c>
-      <c r="JZ2" t="n">
-        <v>409580</v>
-      </c>
-      <c r="KA2" t="n">
-        <v>987057</v>
-      </c>
-      <c r="KB2" t="n">
-        <v>992014</v>
-      </c>
-      <c r="KC2" t="n">
-        <v>468225</v>
-      </c>
-      <c r="KD2" t="n">
-        <v>380176</v>
-      </c>
-      <c r="KE2" t="n">
-        <v>825642</v>
-      </c>
-      <c r="KF2" t="n">
-        <v>43159</v>
-      </c>
-      <c r="KG2" t="n">
-        <v>530615</v>
-      </c>
-      <c r="KH2" t="n">
-        <v>977464</v>
-      </c>
-      <c r="KI2" t="n">
-        <v>1029764</v>
-      </c>
-      <c r="KJ2" t="n">
-        <v>349159</v>
-      </c>
-      <c r="KK2" t="n">
-        <v>127507</v>
-      </c>
-      <c r="KL2" t="n">
-        <v>482729</v>
-      </c>
-      <c r="KM2" t="n">
-        <v>996079</v>
-      </c>
-      <c r="KN2" t="n">
-        <v>1061436</v>
-      </c>
-      <c r="KO2" t="n">
-        <v>655222</v>
-      </c>
-      <c r="KP2" t="n">
-        <v>383449</v>
-      </c>
-      <c r="KQ2" t="n">
-        <v>1113054</v>
-      </c>
-      <c r="KR2" t="n">
-        <v>654130</v>
-      </c>
-      <c r="KS2" t="n">
-        <v>338436</v>
-      </c>
-      <c r="KT2" t="n">
-        <v>402324</v>
-      </c>
-      <c r="KU2" t="n">
-        <v>384850</v>
-      </c>
-      <c r="KV2" t="n">
-        <v>473891</v>
-      </c>
-      <c r="KW2" t="n">
-        <v>473082</v>
-      </c>
-      <c r="KX2" t="n">
-        <v>360057</v>
-      </c>
-      <c r="KY2" t="n">
-        <v>820946</v>
-      </c>
-      <c r="KZ2" t="n">
-        <v>1061623</v>
-      </c>
-      <c r="LA2" t="n">
-        <v>227138</v>
-      </c>
-      <c r="LB2" t="n">
-        <v>995892</v>
-      </c>
-      <c r="LC2" t="n">
-        <v>1012501</v>
-      </c>
-      <c r="LD2" t="n">
-        <v>166655</v>
-      </c>
-      <c r="LE2" t="n">
-        <v>88186</v>
-      </c>
-      <c r="LF2" t="n">
-        <v>32046</v>
-      </c>
-      <c r="LG2" t="n">
-        <v>202509</v>
-      </c>
-      <c r="LH2" t="n">
-        <v>1108092</v>
-      </c>
-      <c r="LI2" t="n">
-        <v>754950</v>
-      </c>
-      <c r="LJ2" t="n">
-        <v>520109</v>
-      </c>
-      <c r="LK2" t="n">
-        <v>208139</v>
-      </c>
-      <c r="LL2" t="n">
-        <v>684289</v>
-      </c>
-      <c r="LM2" t="n">
-        <v>580600</v>
-      </c>
-      <c r="LN2" t="n">
-        <v>1200796</v>
-      </c>
-      <c r="LO2" t="n">
-        <v>304118</v>
-      </c>
-      <c r="LP2" t="n">
-        <v>374316</v>
-      </c>
-      <c r="LQ2" t="n">
-        <v>1033439</v>
-      </c>
-      <c r="LR2" t="n">
-        <v>405972</v>
-      </c>
-      <c r="LS2" t="n">
-        <v>865614</v>
-      </c>
-      <c r="LT2" t="n">
-        <v>28250</v>
-      </c>
-      <c r="LU2" t="n">
-        <v>687878</v>
-      </c>
-      <c r="LV2" t="n">
-        <v>1036328</v>
-      </c>
-      <c r="LW2" t="n">
-        <v>395070</v>
-      </c>
-      <c r="LX2" t="n">
-        <v>1152385</v>
-      </c>
-      <c r="LY2" t="n">
-        <v>761330</v>
-      </c>
-      <c r="LZ2" t="n">
-        <v>505525</v>
-      </c>
-      <c r="MA2" t="n">
-        <v>1019449</v>
-      </c>
-      <c r="MB2" t="n">
-        <v>184654</v>
-      </c>
-      <c r="MC2" t="n">
-        <v>793212</v>
-      </c>
-      <c r="MD2" t="n">
-        <v>462058</v>
-      </c>
-      <c r="ME2" t="n">
-        <v>345056</v>
-      </c>
-      <c r="MF2" t="n">
-        <v>390020</v>
-      </c>
-      <c r="MG2" t="n">
-        <v>403062</v>
-      </c>
-      <c r="MH2" t="n">
-        <v>878634</v>
-      </c>
-      <c r="MI2" t="n">
-        <v>738989</v>
-      </c>
-      <c r="MJ2" t="n">
-        <v>914006</v>
-      </c>
-      <c r="MK2" t="n">
-        <v>862852</v>
-      </c>
-      <c r="ML2" t="n">
-        <v>159441</v>
-      </c>
-      <c r="MM2" t="n">
-        <v>176643</v>
-      </c>
-      <c r="MN2" t="n">
-        <v>1010319</v>
-      </c>
-      <c r="MO2" t="n">
-        <v>938756</v>
-      </c>
-      <c r="MP2" t="n">
-        <v>354491</v>
-      </c>
-      <c r="MQ2" t="n">
-        <v>907534</v>
-      </c>
-      <c r="MR2" t="n">
-        <v>658106</v>
-      </c>
-      <c r="MS2" t="n">
-        <v>778824</v>
-      </c>
-      <c r="MT2" t="n">
-        <v>714020</v>
-      </c>
-      <c r="MU2" t="n">
-        <v>930451</v>
-      </c>
-      <c r="MV2" t="n">
-        <v>960101</v>
-      </c>
-      <c r="MW2" t="n">
-        <v>857111</v>
-      </c>
-      <c r="MX2" t="n">
-        <v>94454</v>
-      </c>
-      <c r="MY2" t="n">
-        <v>17438</v>
-      </c>
-      <c r="MZ2" t="n">
-        <v>99988</v>
-      </c>
-      <c r="NA2" t="n">
-        <v>271923</v>
-      </c>
-      <c r="NB2" t="n">
-        <v>284233</v>
-      </c>
-      <c r="NC2" t="n">
-        <v>1000880</v>
-      </c>
-      <c r="ND2" t="n">
-        <v>898636</v>
-      </c>
-      <c r="NE2" t="n">
-        <v>954103</v>
-      </c>
-      <c r="NF2" t="n">
-        <v>485859</v>
-      </c>
-      <c r="NG2" t="n">
-        <v>428710</v>
-      </c>
-      <c r="NH2" t="n">
-        <v>229403</v>
-      </c>
-      <c r="NI2" t="n">
-        <v>1099232</v>
-      </c>
-      <c r="NJ2" t="n">
-        <v>76058</v>
-      </c>
-      <c r="NK2" t="n">
-        <v>86430</v>
-      </c>
-      <c r="NL2" t="n">
-        <v>806347</v>
-      </c>
-      <c r="NM2" t="n">
-        <v>23472</v>
-      </c>
-      <c r="NN2" t="n">
-        <v>55276</v>
-      </c>
-      <c r="NO2" t="n">
-        <v>24837</v>
-      </c>
-      <c r="NP2" t="n">
-        <v>967055</v>
-      </c>
-      <c r="NQ2" t="n">
-        <v>478817</v>
-      </c>
-      <c r="NR2" t="n">
-        <v>254538</v>
-      </c>
-      <c r="NS2" t="n">
-        <v>106506</v>
-      </c>
-      <c r="NT2" t="n">
-        <v>66966</v>
-      </c>
-      <c r="NU2" t="n">
-        <v>1183656</v>
-      </c>
-      <c r="NV2" t="n">
-        <v>826369</v>
-      </c>
-      <c r="NW2" t="n">
-        <v>161443</v>
-      </c>
-      <c r="NX2" t="n">
-        <v>259168</v>
-      </c>
-      <c r="NY2" t="n">
-        <v>34151</v>
-      </c>
-      <c r="NZ2" t="n">
-        <v>375013</v>
-      </c>
-      <c r="OA2" t="n">
-        <v>1191368</v>
-      </c>
-      <c r="OB2" t="n">
-        <v>323704</v>
-      </c>
-      <c r="OC2" t="n">
-        <v>1128965</v>
-      </c>
-      <c r="OD2" t="n">
-        <v>1069449</v>
-      </c>
-      <c r="OE2" t="n">
-        <v>1193239</v>
-      </c>
-      <c r="OF2" t="n">
-        <v>652491</v>
-      </c>
-      <c r="OG2" t="n">
-        <v>728631</v>
-      </c>
-      <c r="OH2" t="n">
-        <v>142936</v>
-      </c>
-      <c r="OI2" t="n">
-        <v>852771</v>
-      </c>
-      <c r="OJ2" t="n">
-        <v>15955</v>
-      </c>
-      <c r="OK2" t="n">
-        <v>1139192</v>
-      </c>
-      <c r="OL2" t="n">
-        <v>1197503</v>
-      </c>
-      <c r="OM2" t="n">
-        <v>897190</v>
-      </c>
-      <c r="ON2" t="n">
-        <v>587503</v>
-      </c>
-      <c r="OO2" t="n">
-        <v>1038835</v>
-      </c>
-      <c r="OP2" t="n">
-        <v>1180184</v>
-      </c>
-      <c r="OQ2" t="n">
-        <v>166266</v>
-      </c>
-      <c r="OR2" t="n">
-        <v>182703</v>
-      </c>
-      <c r="OS2" t="n">
-        <v>148493</v>
-      </c>
-      <c r="OT2" t="n">
-        <v>772119</v>
-      </c>
-      <c r="OU2" t="n">
-        <v>678647</v>
-      </c>
-      <c r="OV2" t="n">
-        <v>236740</v>
-      </c>
-      <c r="OW2" t="n">
-        <v>1159297</v>
-      </c>
-      <c r="OX2" t="n">
-        <v>674064</v>
-      </c>
-      <c r="OY2" t="n">
-        <v>78636</v>
-      </c>
-      <c r="OZ2" t="n">
-        <v>665034</v>
-      </c>
-      <c r="PA2" t="n">
-        <v>61084</v>
-      </c>
-      <c r="PB2" t="n">
-        <v>892529</v>
-      </c>
-      <c r="PC2" t="n">
-        <v>915777</v>
-      </c>
-      <c r="PD2" t="n">
-        <v>471626</v>
-      </c>
-      <c r="PE2" t="n">
-        <v>531059</v>
-      </c>
-      <c r="PF2" t="n">
-        <v>609700</v>
-      </c>
-      <c r="PG2" t="n">
-        <v>245218</v>
-      </c>
-      <c r="PH2" t="n">
-        <v>831406</v>
-      </c>
-      <c r="PI2" t="n">
-        <v>551229</v>
-      </c>
-      <c r="PJ2" t="n">
-        <v>424222</v>
-      </c>
-      <c r="PK2" t="n">
-        <v>614046</v>
-      </c>
-      <c r="PL2" t="n">
-        <v>1018265</v>
-      </c>
-      <c r="PM2" t="n">
-        <v>749397</v>
-      </c>
-      <c r="PN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="PO2" t="n">
-        <v>732882</v>
-      </c>
-      <c r="PP2" t="n">
-        <v>916645</v>
-      </c>
-      <c r="PQ2" t="n">
-        <v>178535</v>
-      </c>
-      <c r="PR2" t="n">
-        <v>1027903</v>
-      </c>
-      <c r="PS2" t="n">
-        <v>523606</v>
-      </c>
-      <c r="PT2" t="n">
-        <v>1155311</v>
-      </c>
-      <c r="PU2" t="n">
-        <v>550310</v>
-      </c>
-      <c r="PV2" t="n">
-        <v>84786</v>
-      </c>
-      <c r="PW2" t="n">
-        <v>112108</v>
-      </c>
-      <c r="PX2" t="n">
-        <v>13290</v>
-      </c>
-      <c r="PY2" t="n">
-        <v>1003358</v>
-      </c>
-      <c r="PZ2" t="n">
-        <v>309325</v>
-      </c>
-      <c r="QA2" t="n">
-        <v>172636</v>
-      </c>
-      <c r="QB2" t="n">
-        <v>925738</v>
-      </c>
-      <c r="QC2" t="n">
-        <v>921108</v>
-      </c>
-      <c r="QD2" t="n">
-        <v>669402</v>
-      </c>
-      <c r="QE2" t="n">
-        <v>1162760</v>
-      </c>
-      <c r="QF2" t="n">
-        <v>634948</v>
-      </c>
-      <c r="QG2" t="n">
-        <v>522475</v>
-      </c>
-      <c r="QH2" t="n">
-        <v>213555</v>
-      </c>
-      <c r="QI2" t="n">
-        <v>1023693</v>
-      </c>
-      <c r="QJ2" t="n">
-        <v>579973</v>
-      </c>
-      <c r="QK2" t="n">
-        <v>642958</v>
-      </c>
-      <c r="QL2" t="n">
-        <v>578810</v>
-      </c>
-      <c r="QM2" t="n">
-        <v>769027</v>
-      </c>
-      <c r="QN2" t="n">
-        <v>168203</v>
-      </c>
-      <c r="QO2" t="n">
-        <v>9633</v>
-      </c>
-      <c r="QP2" t="n">
-        <v>83438</v>
-      </c>
-      <c r="QQ2" t="n">
-        <v>860282</v>
-      </c>
-      <c r="QR2" t="n">
-        <v>407894</v>
-      </c>
-      <c r="QS2" t="n">
-        <v>813663</v>
-      </c>
-      <c r="QT2" t="n">
-        <v>194225</v>
-      </c>
-      <c r="QU2" t="n">
-        <v>47833</v>
-      </c>
-      <c r="QV2" t="n">
-        <v>294919</v>
-      </c>
-      <c r="QW2" t="n">
-        <v>747788</v>
-      </c>
-      <c r="QX2" t="n">
-        <v>346589</v>
-      </c>
-      <c r="QY2" t="n">
-        <v>631124</v>
-      </c>
-      <c r="QZ2" t="n">
-        <v>498573</v>
-      </c>
-      <c r="RA2" t="n">
-        <v>112707</v>
-      </c>
-      <c r="RB2" t="n">
-        <v>97163</v>
-      </c>
-      <c r="RC2" t="n">
-        <v>14544</v>
-      </c>
-      <c r="RD2" t="n">
-        <v>103069</v>
-      </c>
-      <c r="RE2" t="n">
-        <v>20141</v>
-      </c>
-      <c r="RF2" t="n">
-        <v>429425</v>
-      </c>
-      <c r="RG2" t="n">
-        <v>340876</v>
-      </c>
-      <c r="RH2" t="n">
-        <v>689363</v>
-      </c>
-      <c r="RI2" t="n">
-        <v>251564</v>
-      </c>
-      <c r="RJ2" t="n">
-        <v>1156864</v>
-      </c>
-      <c r="RK2" t="n">
-        <v>327480</v>
-      </c>
-      <c r="RL2" t="n">
-        <v>204463</v>
-      </c>
-      <c r="RM2" t="n">
-        <v>449243</v>
-      </c>
-      <c r="RN2" t="n">
-        <v>956166</v>
-      </c>
-      <c r="RO2" t="n">
-        <v>85040</v>
-      </c>
-      <c r="RP2" t="n">
-        <v>227210</v>
-      </c>
-      <c r="RQ2" t="n">
-        <v>41301</v>
-      </c>
-      <c r="RR2" t="n">
-        <v>969865</v>
-      </c>
-      <c r="RS2" t="n">
-        <v>393204</v>
-      </c>
-      <c r="RT2" t="n">
-        <v>12031</v>
-      </c>
-      <c r="RU2" t="n">
-        <v>946411</v>
-      </c>
-      <c r="RV2" t="n">
-        <v>935031</v>
-      </c>
-      <c r="RW2" t="n">
-        <v>525956</v>
-      </c>
-      <c r="RX2" t="n">
-        <v>528274</v>
-      </c>
-      <c r="RY2" t="n">
-        <v>493747</v>
-      </c>
-      <c r="RZ2" t="n">
-        <v>164286</v>
-      </c>
-      <c r="SA2" t="n">
-        <v>1098391</v>
-      </c>
-      <c r="SB2" t="n">
-        <v>319075</v>
-      </c>
-      <c r="SC2" t="n">
-        <v>781666</v>
-      </c>
-      <c r="SD2" t="n">
-        <v>406982</v>
-      </c>
-      <c r="SE2" t="n">
-        <v>1006490</v>
-      </c>
-      <c r="SF2" t="n">
-        <v>196512</v>
-      </c>
-      <c r="SG2" t="n">
-        <v>335105</v>
-      </c>
-      <c r="SH2" t="n">
-        <v>584162</v>
-      </c>
-      <c r="SI2" t="n">
-        <v>937692</v>
-      </c>
-      <c r="SJ2" t="n">
-        <v>1101148</v>
-      </c>
-      <c r="SK2" t="n">
-        <v>1032470</v>
-      </c>
-      <c r="SL2" t="n">
-        <v>1125988</v>
-      </c>
-      <c r="SM2" t="n">
-        <v>1011932</v>
-      </c>
-      <c r="SN2" t="n">
-        <v>901972</v>
-      </c>
-      <c r="SO2" t="n">
-        <v>1076451</v>
-      </c>
-      <c r="SP2" t="n">
-        <v>397631</v>
-      </c>
-      <c r="SQ2" t="n">
-        <v>647867</v>
-      </c>
-      <c r="SR2" t="n">
-        <v>8669</v>
-      </c>
-      <c r="SS2" t="n">
-        <v>529492</v>
-      </c>
-      <c r="ST2" t="n">
-        <v>370693</v>
-      </c>
-      <c r="SU2" t="n">
-        <v>787397</v>
-      </c>
-      <c r="SV2" t="n">
-        <v>158323</v>
-      </c>
-      <c r="SW2" t="n">
-        <v>875324</v>
-      </c>
-      <c r="SX2" t="n">
-        <v>436861</v>
-      </c>
-      <c r="SY2" t="n">
-        <v>520888</v>
-      </c>
-      <c r="SZ2" t="n">
-        <v>648874</v>
-      </c>
-      <c r="TA2" t="n">
-        <v>518397</v>
-      </c>
-      <c r="TB2" t="n">
-        <v>141222</v>
-      </c>
-      <c r="TC2" t="n">
-        <v>5196</v>
-      </c>
-      <c r="TD2" t="n">
-        <v>807386</v>
-      </c>
-      <c r="TE2" t="n">
-        <v>752676</v>
-      </c>
-      <c r="TF2" t="n">
-        <v>637200</v>
-      </c>
-      <c r="TG2" t="n">
-        <v>926225</v>
-      </c>
-      <c r="TH2" t="n">
-        <v>251819</v>
-      </c>
-      <c r="TI2" t="n">
-        <v>970363</v>
-      </c>
-      <c r="TJ2" t="n">
-        <v>1194966</v>
-      </c>
-      <c r="TK2" t="n">
-        <v>35384</v>
-      </c>
-      <c r="TL2" t="n">
-        <v>13290</v>
-      </c>
-      <c r="TM2" t="n">
-        <v>873892</v>
-      </c>
-      <c r="TN2" t="n">
-        <v>895393</v>
-      </c>
-      <c r="TO2" t="n">
-        <v>356963</v>
-      </c>
-      <c r="TP2" t="n">
-        <v>869738</v>
-      </c>
-      <c r="TQ2" t="n">
-        <v>836500</v>
-      </c>
-      <c r="TR2" t="n">
-        <v>10450</v>
-      </c>
-      <c r="TS2" t="n">
-        <v>525536</v>
-      </c>
-      <c r="TT2" t="n">
-        <v>921095</v>
-      </c>
-      <c r="TU2" t="n">
-        <v>705895</v>
-      </c>
-      <c r="TV2" t="n">
-        <v>1037452</v>
-      </c>
-      <c r="TW2" t="n">
-        <v>382304</v>
-      </c>
-      <c r="TX2" t="n">
-        <v>222239</v>
-      </c>
-      <c r="TY2" t="n">
-        <v>342342</v>
-      </c>
-      <c r="TZ2" t="n">
-        <v>1105985</v>
-      </c>
-      <c r="UA2" t="n">
-        <v>303122</v>
-      </c>
-      <c r="UB2" t="n">
-        <v>411856</v>
-      </c>
-      <c r="UC2" t="n">
-        <v>566928</v>
-      </c>
-      <c r="UD2" t="n">
-        <v>492252</v>
-      </c>
-      <c r="UE2" t="n">
-        <v>703744</v>
-      </c>
-      <c r="UF2" t="n">
-        <v>74439</v>
-      </c>
-      <c r="UG2" t="n">
-        <v>96081</v>
-      </c>
-      <c r="UH2" t="n">
-        <v>1171667</v>
-      </c>
-      <c r="UI2" t="n">
-        <v>756075</v>
-      </c>
-      <c r="UJ2" t="n">
-        <v>1062643</v>
-      </c>
-      <c r="UK2" t="n">
-        <v>267913</v>
-      </c>
-      <c r="UL2" t="n">
-        <v>65604</v>
-      </c>
-      <c r="UM2" t="n">
-        <v>711134</v>
-      </c>
-      <c r="UN2" t="n">
-        <v>90950</v>
-      </c>
-      <c r="UO2" t="n">
-        <v>561224</v>
-      </c>
-      <c r="UP2" t="n">
-        <v>121398</v>
-      </c>
-      <c r="UQ2" t="n">
-        <v>672363</v>
-      </c>
-      <c r="UR2" t="n">
-        <v>982340</v>
-      </c>
-      <c r="US2" t="n">
-        <v>367261</v>
-      </c>
-      <c r="UT2" t="n">
-        <v>841195</v>
-      </c>
-      <c r="UU2" t="n">
-        <v>345950</v>
-      </c>
-      <c r="UV2" t="n">
-        <v>729455</v>
-      </c>
-      <c r="UW2" t="n">
-        <v>766737</v>
-      </c>
-      <c r="UX2" t="n">
-        <v>109739</v>
-      </c>
-      <c r="UY2" t="n">
-        <v>618258</v>
-      </c>
-      <c r="UZ2" t="n">
-        <v>804052</v>
-      </c>
-      <c r="VA2" t="n">
-        <v>587962</v>
-      </c>
-      <c r="VB2" t="n">
-        <v>604725</v>
-      </c>
-      <c r="VC2" t="n">
-        <v>673088</v>
-      </c>
-      <c r="VD2" t="n">
-        <v>391592</v>
-      </c>
-      <c r="VE2" t="n">
-        <v>611985</v>
-      </c>
-      <c r="VF2" t="n">
-        <v>974893</v>
-      </c>
-      <c r="VG2" t="n">
-        <v>405154</v>
-      </c>
-      <c r="VH2" t="n">
-        <v>454443</v>
-      </c>
-      <c r="VI2" t="n">
-        <v>833341</v>
-      </c>
-      <c r="VJ2" t="n">
-        <v>516221</v>
-      </c>
-      <c r="VK2" t="n">
-        <v>598115</v>
-      </c>
-      <c r="VL2" t="n">
-        <v>1137932</v>
-      </c>
-      <c r="VM2" t="n">
-        <v>1104255</v>
-      </c>
-      <c r="VN2" t="n">
-        <v>105877</v>
-      </c>
-      <c r="VO2" t="n">
-        <v>968003</v>
-      </c>
-      <c r="VP2" t="n">
-        <v>20306</v>
-      </c>
-      <c r="VQ2" t="n">
-        <v>538510</v>
-      </c>
-      <c r="VR2" t="n">
-        <v>571554</v>
-      </c>
-      <c r="VS2" t="n">
-        <v>80843</v>
-      </c>
-      <c r="VT2" t="n">
-        <v>476660</v>
-      </c>
-      <c r="VU2" t="n">
-        <v>81631</v>
-      </c>
-      <c r="VV2" t="n">
-        <v>868030</v>
-      </c>
-      <c r="VW2" t="n">
-        <v>709461</v>
-      </c>
-      <c r="VX2" t="n">
-        <v>293800</v>
-      </c>
-      <c r="VY2" t="n">
-        <v>91110</v>
-      </c>
-      <c r="VZ2" t="n">
-        <v>436841</v>
-      </c>
-      <c r="WA2" t="n">
-        <v>676934</v>
-      </c>
-      <c r="WB2" t="n">
-        <v>731742</v>
-      </c>
-      <c r="WC2" t="n">
-        <v>314663</v>
-      </c>
-      <c r="WD2" t="n">
-        <v>800526</v>
-      </c>
-      <c r="WE2" t="n">
-        <v>298045</v>
-      </c>
-      <c r="WF2" t="n">
-        <v>512713</v>
-      </c>
-      <c r="WG2" t="n">
-        <v>720282</v>
-      </c>
-      <c r="WH2" t="n">
-        <v>150886</v>
-      </c>
-      <c r="WI2" t="n">
-        <v>139523</v>
-      </c>
-      <c r="WJ2" t="n">
-        <v>225863</v>
-      </c>
-      <c r="WK2" t="n">
-        <v>564748</v>
-      </c>
-      <c r="WL2" t="n">
-        <v>288640</v>
-      </c>
-      <c r="WM2" t="n">
-        <v>294618</v>
-      </c>
-      <c r="WN2" t="n">
-        <v>722541</v>
-      </c>
-      <c r="WO2" t="n">
-        <v>561407</v>
-      </c>
-      <c r="WP2" t="n">
-        <v>205268</v>
-      </c>
-      <c r="WQ2" t="n">
-        <v>707820</v>
-      </c>
-      <c r="WR2" t="n">
-        <v>514626</v>
-      </c>
-      <c r="WS2" t="n">
-        <v>376246</v>
-      </c>
-      <c r="WT2" t="n">
-        <v>393280</v>
-      </c>
-      <c r="WU2" t="n">
-        <v>333556</v>
-      </c>
-      <c r="WV2" t="n">
-        <v>40051</v>
-      </c>
-      <c r="WW2" t="n">
-        <v>827547</v>
-      </c>
-      <c r="WX2" t="n">
-        <v>891623</v>
-      </c>
-      <c r="WY2" t="n">
-        <v>41022</v>
-      </c>
-      <c r="WZ2" t="n">
-        <v>202278</v>
-      </c>
-      <c r="XA2" t="n">
-        <v>812493</v>
-      </c>
-      <c r="XB2" t="n">
-        <v>502433</v>
-      </c>
-      <c r="XC2" t="n">
-        <v>731272</v>
-      </c>
-      <c r="XD2" t="n">
-        <v>691211</v>
-      </c>
-      <c r="XE2" t="n">
-        <v>735831</v>
-      </c>
-      <c r="XF2" t="n">
-        <v>481080</v>
-      </c>
-      <c r="XG2" t="n">
-        <v>545902</v>
-      </c>
-      <c r="XH2" t="n">
-        <v>257629</v>
-      </c>
-      <c r="XI2" t="n">
-        <v>552729</v>
-      </c>
-      <c r="XJ2" t="n">
-        <v>435386</v>
-      </c>
-      <c r="XK2" t="n">
-        <v>904589</v>
-      </c>
-      <c r="XL2" t="n">
-        <v>232342</v>
-      </c>
-      <c r="XM2" t="n">
-        <v>575735</v>
-      </c>
-      <c r="XN2" t="n">
-        <v>1139917</v>
-      </c>
-      <c r="XO2" t="n">
-        <v>51196</v>
-      </c>
-      <c r="XP2" t="n">
-        <v>76314</v>
-      </c>
-      <c r="XQ2" t="n">
-        <v>958689</v>
-      </c>
-      <c r="XR2" t="n">
-        <v>314379</v>
-      </c>
-      <c r="XS2" t="n">
-        <v>196824</v>
-      </c>
-      <c r="XT2" t="n">
-        <v>485604</v>
-      </c>
-      <c r="XU2" t="n">
-        <v>508089</v>
-      </c>
-      <c r="XV2" t="n">
-        <v>677470</v>
-      </c>
-      <c r="XW2" t="n">
-        <v>362718</v>
-      </c>
-      <c r="XX2" t="n">
-        <v>118000</v>
-      </c>
-      <c r="XY2" t="n">
-        <v>478093</v>
-      </c>
-      <c r="XZ2" t="n">
-        <v>1069964</v>
-      </c>
-      <c r="YA2" t="n">
-        <v>442047</v>
-      </c>
-      <c r="YB2" t="n">
-        <v>1124824</v>
-      </c>
-      <c r="YC2" t="n">
-        <v>336217</v>
-      </c>
-      <c r="YD2" t="n">
-        <v>1200925</v>
-      </c>
-      <c r="YE2" t="n">
-        <v>67489</v>
-      </c>
-      <c r="YF2" t="n">
-        <v>830578</v>
-      </c>
-      <c r="YG2" t="n">
-        <v>123411</v>
-      </c>
-      <c r="YH2" t="n">
-        <v>625313</v>
-      </c>
-      <c r="YI2" t="n">
-        <v>75606</v>
-      </c>
-      <c r="YJ2" t="n">
-        <v>876462</v>
-      </c>
-      <c r="YK2" t="n">
-        <v>289405</v>
-      </c>
-      <c r="YL2" t="n">
-        <v>1019372</v>
-      </c>
-      <c r="YM2" t="n">
-        <v>932166</v>
-      </c>
-      <c r="YN2" t="n">
-        <v>103375</v>
-      </c>
-      <c r="YO2" t="n">
-        <v>1167629</v>
-      </c>
-      <c r="YP2" t="n">
-        <v>143428</v>
-      </c>
-      <c r="YQ2" t="n">
-        <v>111408</v>
-      </c>
-      <c r="YR2" t="n">
-        <v>819408</v>
-      </c>
-      <c r="YS2" t="n">
-        <v>1150262</v>
-      </c>
-      <c r="YT2" t="n">
-        <v>1047549</v>
-      </c>
-      <c r="YU2" t="n">
-        <v>431910</v>
-      </c>
-      <c r="YV2" t="n">
-        <v>590617</v>
-      </c>
-      <c r="YW2" t="n">
-        <v>1141713</v>
-      </c>
-      <c r="YX2" t="n">
-        <v>958651</v>
-      </c>
-      <c r="YY2" t="n">
-        <v>397336</v>
-      </c>
-      <c r="YZ2" t="n">
-        <v>442792</v>
-      </c>
-      <c r="ZA2" t="n">
-        <v>135040</v>
-      </c>
-      <c r="ZB2" t="n">
-        <v>63756</v>
-      </c>
-      <c r="ZC2" t="n">
-        <v>641525</v>
-      </c>
-      <c r="ZD2" t="n">
-        <v>557617</v>
-      </c>
-      <c r="ZE2" t="n">
-        <v>475297</v>
-      </c>
-      <c r="ZF2" t="n">
-        <v>50309</v>
-      </c>
-      <c r="ZG2" t="n">
-        <v>834094</v>
-      </c>
-      <c r="ZH2" t="n">
-        <v>123576</v>
-      </c>
-      <c r="ZI2" t="n">
-        <v>403568</v>
-      </c>
-      <c r="ZJ2" t="n">
-        <v>381415</v>
-      </c>
-      <c r="ZK2" t="n">
-        <v>585524</v>
-      </c>
-      <c r="ZL2" t="n">
-        <v>1085371</v>
-      </c>
-      <c r="ZM2" t="n">
-        <v>61382</v>
-      </c>
-      <c r="ZN2" t="n">
-        <v>216646</v>
-      </c>
-      <c r="ZO2" t="n">
-        <v>539835</v>
-      </c>
-      <c r="ZP2" t="n">
-        <v>223959</v>
-      </c>
-      <c r="ZQ2" t="n">
-        <v>545959</v>
-      </c>
-      <c r="ZR2" t="n">
-        <v>945187</v>
-      </c>
-      <c r="ZS2" t="n">
-        <v>383793</v>
-      </c>
-      <c r="ZT2" t="n">
-        <v>487235</v>
-      </c>
-      <c r="ZU2" t="n">
-        <v>740108</v>
-      </c>
-      <c r="ZV2" t="n">
-        <v>542082</v>
-      </c>
-      <c r="ZW2" t="n">
-        <v>333460</v>
-      </c>
-      <c r="ZX2" t="n">
-        <v>391325</v>
-      </c>
-      <c r="ZY2" t="n">
-        <v>153297</v>
-      </c>
-      <c r="ZZ2" t="n">
-        <v>208810</v>
-      </c>
-      <c r="AAA2" t="n">
-        <v>923494</v>
-      </c>
-      <c r="AAB2" t="n">
-        <v>555692</v>
-      </c>
-      <c r="AAC2" t="n">
-        <v>667931</v>
-      </c>
-      <c r="AAD2" t="n">
-        <v>1008835</v>
-      </c>
-      <c r="AAE2" t="n">
-        <v>767656</v>
-      </c>
-      <c r="AAF2" t="n">
-        <v>870595</v>
-      </c>
-      <c r="AAG2" t="n">
-        <v>1112719</v>
-      </c>
-      <c r="AAH2" t="n">
-        <v>385315</v>
-      </c>
-      <c r="AAI2" t="n">
-        <v>256252</v>
-      </c>
-      <c r="AAJ2" t="n">
-        <v>1095662</v>
-      </c>
-      <c r="AAK2" t="n">
-        <v>1049219</v>
-      </c>
-      <c r="AAL2" t="n">
-        <v>320810</v>
-      </c>
-      <c r="AAM2" t="n">
-        <v>202892</v>
-      </c>
-      <c r="AAN2" t="n">
-        <v>245755</v>
-      </c>
-      <c r="AAO2" t="n">
-        <v>146453</v>
-      </c>
-      <c r="AAP2" t="n">
-        <v>1115317</v>
-      </c>
-      <c r="AAQ2" t="n">
-        <v>606578</v>
-      </c>
-      <c r="AAR2" t="n">
-        <v>964914</v>
-      </c>
-      <c r="AAS2" t="n">
-        <v>1171225</v>
-      </c>
-      <c r="AAT2" t="n">
-        <v>810987</v>
-      </c>
-      <c r="AAU2" t="n">
-        <v>704857</v>
-      </c>
-      <c r="AAV2" t="n">
-        <v>458621</v>
-      </c>
-      <c r="AAW2" t="n">
-        <v>549035</v>
-      </c>
-      <c r="AAX2" t="n">
-        <v>129731</v>
-      </c>
-      <c r="AAY2" t="n">
-        <v>1054311</v>
-      </c>
-      <c r="AAZ2" t="n">
-        <v>1187215</v>
-      </c>
-      <c r="ABA2" t="n">
-        <v>6862</v>
-      </c>
-      <c r="ABB2" t="n">
-        <v>759162</v>
-      </c>
-      <c r="ABC2" t="n">
-        <v>412149</v>
-      </c>
-      <c r="ABD2" t="n">
-        <v>1188772</v>
-      </c>
-      <c r="ABE2" t="n">
-        <v>770696</v>
-      </c>
-      <c r="ABF2" t="n">
-        <v>783339</v>
-      </c>
-      <c r="ABG2" t="n">
-        <v>686460</v>
-      </c>
-      <c r="ABH2" t="n">
-        <v>848755</v>
-      </c>
-      <c r="ABI2" t="n">
-        <v>272875</v>
-      </c>
-      <c r="ABJ2" t="n">
-        <v>622916</v>
-      </c>
-      <c r="ABK2" t="n">
-        <v>1143399</v>
-      </c>
-      <c r="ABL2" t="n">
-        <v>750463</v>
-      </c>
-      <c r="ABM2" t="n">
-        <v>597642</v>
-      </c>
-      <c r="ABN2" t="n">
-        <v>778062</v>
-      </c>
-      <c r="ABO2" t="n">
-        <v>620242</v>
-      </c>
-      <c r="ABP2" t="n">
-        <v>605572</v>
-      </c>
-      <c r="ABQ2" t="n">
-        <v>741237</v>
-      </c>
-      <c r="ABR2" t="n">
-        <v>239660</v>
-      </c>
-      <c r="ABS2" t="n">
-        <v>784119</v>
-      </c>
-      <c r="ABT2" t="n">
-        <v>305750</v>
-      </c>
-      <c r="ABU2" t="n">
-        <v>1026585</v>
-      </c>
-      <c r="ABV2" t="n">
-        <v>845779</v>
-      </c>
-      <c r="ABW2" t="n">
-        <v>187679</v>
-      </c>
-      <c r="ABX2" t="n">
-        <v>454418</v>
-      </c>
-      <c r="ABY2" t="n">
-        <v>242296</v>
-      </c>
-      <c r="ABZ2" t="n">
-        <v>675088</v>
-      </c>
-      <c r="ACA2" t="n">
-        <v>244169</v>
-      </c>
-      <c r="ACB2" t="n">
-        <v>762196</v>
-      </c>
-      <c r="ACC2" t="n">
-        <v>210920</v>
-      </c>
-      <c r="ACD2" t="n">
-        <v>433773</v>
-      </c>
-      <c r="ACE2" t="n">
-        <v>544386</v>
-      </c>
-      <c r="ACF2" t="n">
-        <v>200733</v>
-      </c>
-      <c r="ACG2" t="n">
-        <v>801686</v>
-      </c>
-      <c r="ACH2" t="n">
-        <v>1020372</v>
-      </c>
-      <c r="ACI2" t="n">
-        <v>1185865</v>
-      </c>
-      <c r="ACJ2" t="n">
-        <v>495552</v>
-      </c>
-      <c r="ACK2" t="n">
-        <v>280279</v>
-      </c>
-      <c r="ACL2" t="n">
-        <v>696762</v>
-      </c>
-      <c r="ACM2" t="n">
-        <v>45503</v>
-      </c>
-      <c r="ACN2" t="n">
-        <v>712106</v>
-      </c>
-      <c r="ACO2" t="n">
-        <v>779408</v>
-      </c>
-      <c r="ACP2" t="n">
-        <v>292866</v>
-      </c>
-      <c r="ACQ2" t="n">
-        <v>798019</v>
-      </c>
-      <c r="ACR2" t="n">
-        <v>847262</v>
-      </c>
-      <c r="ACS2" t="n">
-        <v>793319</v>
-      </c>
-      <c r="ACT2" t="n">
-        <v>185923</v>
-      </c>
-      <c r="ACU2" t="n">
-        <v>1082521</v>
-      </c>
-      <c r="ACV2" t="n">
-        <v>616434</v>
-      </c>
-      <c r="ACW2" t="n">
-        <v>238803</v>
-      </c>
-      <c r="ACX2" t="n">
-        <v>1103864</v>
-      </c>
-      <c r="ACY2" t="n">
-        <v>308813</v>
-      </c>
-      <c r="ACZ2" t="n">
-        <v>147337</v>
-      </c>
-      <c r="ADA2" t="n">
-        <v>910365</v>
-      </c>
-      <c r="ADB2" t="n">
-        <v>1153271</v>
-      </c>
-      <c r="ADC2" t="n">
-        <v>600854</v>
-      </c>
-      <c r="ADD2" t="n">
-        <v>275420</v>
-      </c>
-      <c r="ADE2" t="n">
-        <v>979486</v>
-      </c>
-      <c r="ADF2" t="n">
-        <v>1110104</v>
-      </c>
-      <c r="ADG2" t="n">
-        <v>150149</v>
-      </c>
-      <c r="ADH2" t="n">
-        <v>444860</v>
-      </c>
-      <c r="ADI2" t="n">
-        <v>614672</v>
-      </c>
-      <c r="ADJ2" t="n">
-        <v>93851</v>
-      </c>
-      <c r="ADK2" t="n">
-        <v>662054</v>
-      </c>
-      <c r="ADL2" t="n">
-        <v>1090111</v>
-      </c>
-      <c r="ADM2" t="n">
-        <v>183113</v>
-      </c>
-      <c r="ADN2" t="n">
-        <v>533619</v>
-      </c>
-      <c r="ADO2" t="n">
-        <v>1065879</v>
-      </c>
-      <c r="ADP2" t="n">
-        <v>365429</v>
-      </c>
-      <c r="ADQ2" t="n">
-        <v>287616</v>
-      </c>
-      <c r="ADR2" t="n">
-        <v>794584</v>
-      </c>
-      <c r="ADS2" t="n">
-        <v>414698</v>
-      </c>
-      <c r="ADT2" t="n">
-        <v>536810</v>
-      </c>
-      <c r="ADU2" t="n">
-        <v>191623</v>
-      </c>
-      <c r="ADV2" t="n">
-        <v>890286</v>
-      </c>
-      <c r="ADW2" t="n">
-        <v>463174</v>
-      </c>
-      <c r="ADX2" t="n">
-        <v>1165634</v>
-      </c>
-      <c r="ADY2" t="n">
-        <v>689475</v>
-      </c>
-      <c r="ADZ2" t="n">
-        <v>368759</v>
-      </c>
-      <c r="AEA2" t="n">
-        <v>601860</v>
-      </c>
-      <c r="AEB2" t="n">
-        <v>738103</v>
-      </c>
-      <c r="AEC2" t="n">
-        <v>586246</v>
-      </c>
-      <c r="AED2" t="n">
-        <v>814444</v>
-      </c>
-      <c r="AEE2" t="n">
-        <v>478711</v>
-      </c>
-      <c r="AEF2" t="n">
-        <v>829401</v>
-      </c>
-      <c r="AEG2" t="n">
-        <v>854228</v>
-      </c>
-      <c r="AEH2" t="n">
-        <v>179478</v>
-      </c>
-      <c r="AEI2" t="n">
-        <v>509256</v>
-      </c>
-      <c r="AEJ2" t="n">
-        <v>884455</v>
-      </c>
-      <c r="AEK2" t="n">
-        <v>352539</v>
-      </c>
-      <c r="AEL2" t="n">
-        <v>356203</v>
-      </c>
-      <c r="AEM2" t="n">
-        <v>952441</v>
-      </c>
-      <c r="AEN2" t="n">
-        <v>905658</v>
-      </c>
-      <c r="AEO2" t="n">
-        <v>1167117</v>
-      </c>
-      <c r="AEP2" t="n">
-        <v>262568</v>
-      </c>
-      <c r="AEQ2" t="n">
-        <v>101718</v>
-      </c>
-      <c r="AER2" t="n">
-        <v>222581</v>
-      </c>
-      <c r="AES2" t="n">
-        <v>1027840</v>
-      </c>
-      <c r="AET2" t="n">
-        <v>1079071</v>
-      </c>
-      <c r="AEU2" t="n">
-        <v>377264</v>
-      </c>
-      <c r="AEV2" t="n">
-        <v>71872</v>
-      </c>
-      <c r="AEW2" t="n">
-        <v>460209</v>
-      </c>
-      <c r="AEX2" t="n">
-        <v>637189</v>
-      </c>
-      <c r="AEY2" t="n">
-        <v>363383</v>
-      </c>
-      <c r="AEZ2" t="n">
-        <v>30471</v>
-      </c>
-      <c r="AFA2" t="n">
-        <v>354095</v>
-      </c>
-      <c r="AFB2" t="n">
-        <v>350688</v>
-      </c>
-      <c r="AFC2" t="n">
-        <v>135483</v>
-      </c>
-      <c r="AFD2" t="n">
-        <v>987682</v>
-      </c>
-      <c r="AFE2" t="n">
-        <v>30229</v>
-      </c>
-      <c r="AFF2" t="n">
-        <v>765014</v>
-      </c>
-      <c r="AFG2" t="n">
-        <v>79306</v>
-      </c>
-      <c r="AFH2" t="n">
-        <v>1046592</v>
-      </c>
-      <c r="AFI2" t="n">
-        <v>886020</v>
-      </c>
-      <c r="AFJ2" t="n">
-        <v>573067</v>
-      </c>
-      <c r="AFK2" t="n">
-        <v>860630</v>
-      </c>
-      <c r="AFL2" t="n">
-        <v>449469</v>
-      </c>
-      <c r="AFM2" t="n">
-        <v>948970</v>
-      </c>
-      <c r="AFN2" t="n">
-        <v>363953</v>
-      </c>
-      <c r="AFO2" t="n">
-        <v>928265</v>
-      </c>
-      <c r="AFP2" t="n">
-        <v>277204</v>
-      </c>
-      <c r="AFQ2" t="n">
-        <v>214748</v>
-      </c>
-      <c r="AFR2" t="n">
-        <v>808948</v>
-      </c>
-      <c r="AFS2" t="n">
-        <v>1178012</v>
-      </c>
-      <c r="AFT2" t="n">
-        <v>484261</v>
-      </c>
-      <c r="AFU2" t="n">
-        <v>21770</v>
-      </c>
-      <c r="AFV2" t="n">
-        <v>1131098</v>
-      </c>
-      <c r="AFW2" t="n">
-        <v>879267</v>
-      </c>
-      <c r="AFX2" t="n">
-        <v>419453</v>
-      </c>
-      <c r="AFY2" t="n">
-        <v>670341</v>
-      </c>
-      <c r="AFZ2" t="n">
-        <v>263895</v>
-      </c>
-      <c r="AGA2" t="n">
-        <v>372393</v>
-      </c>
-      <c r="AGB2" t="n">
-        <v>934042</v>
-      </c>
-      <c r="AGC2" t="n">
-        <v>788669</v>
-      </c>
-      <c r="AGD2" t="n">
-        <v>534570</v>
-      </c>
-      <c r="AGE2" t="n">
-        <v>543125</v>
-      </c>
-      <c r="AGF2" t="n">
-        <v>891782</v>
-      </c>
-      <c r="AGG2" t="n">
-        <v>514206</v>
-      </c>
-      <c r="AGH2" t="n">
-        <v>223178</v>
-      </c>
-      <c r="AGI2" t="n">
-        <v>280043</v>
-      </c>
-      <c r="AGJ2" t="n">
-        <v>261012</v>
-      </c>
-      <c r="AGK2" t="n">
-        <v>1182556</v>
-      </c>
-      <c r="AGL2" t="n">
-        <v>1015855</v>
-      </c>
-      <c r="AGM2" t="n">
-        <v>865604</v>
-      </c>
-      <c r="AGN2" t="n">
-        <v>1076150</v>
-      </c>
-      <c r="AGO2" t="n">
-        <v>745680</v>
-      </c>
-      <c r="AGP2" t="n">
-        <v>26234</v>
-      </c>
-      <c r="AGQ2" t="n">
-        <v>546731</v>
-      </c>
-      <c r="AGR2" t="n">
-        <v>603620</v>
-      </c>
-      <c r="AGS2" t="n">
-        <v>458628</v>
-      </c>
-      <c r="AGT2" t="n">
-        <v>646154</v>
-      </c>
-      <c r="AGU2" t="n">
-        <v>333819</v>
-      </c>
-      <c r="AGV2" t="n">
-        <v>896955</v>
-      </c>
-      <c r="AGW2" t="n">
-        <v>532700</v>
-      </c>
-      <c r="AGX2" t="n">
-        <v>971107</v>
-      </c>
-      <c r="AGY2" t="n">
-        <v>310923</v>
-      </c>
-      <c r="AGZ2" t="n">
-        <v>490850</v>
-      </c>
-      <c r="AHA2" t="n">
-        <v>255783</v>
-      </c>
-      <c r="AHB2" t="n">
-        <v>228488</v>
-      </c>
-      <c r="AHC2" t="n">
-        <v>106369</v>
-      </c>
-      <c r="AHD2" t="n">
-        <v>1154699</v>
-      </c>
-      <c r="AHE2" t="n">
-        <v>72958</v>
-      </c>
-      <c r="AHF2" t="n">
-        <v>265336</v>
-      </c>
-      <c r="AHG2" t="n">
-        <v>822128</v>
-      </c>
-      <c r="AHH2" t="n">
-        <v>69706</v>
-      </c>
-      <c r="AHI2" t="n">
-        <v>453588</v>
-      </c>
-      <c r="AHJ2" t="n">
-        <v>54050</v>
-      </c>
-      <c r="AHK2" t="n">
-        <v>1071155</v>
-      </c>
-      <c r="AHL2" t="n">
-        <v>415153</v>
-      </c>
-      <c r="AHM2" t="n">
-        <v>89139</v>
-      </c>
-      <c r="AHN2" t="n">
-        <v>932293</v>
-      </c>
-      <c r="AHO2" t="n">
-        <v>1119013</v>
-      </c>
-      <c r="AHP2" t="n">
-        <v>952428</v>
-      </c>
-      <c r="AHQ2" t="n">
-        <v>881897</v>
-      </c>
-      <c r="AHR2" t="n">
-        <v>129459</v>
-      </c>
-      <c r="AHS2" t="n">
-        <v>477161</v>
-      </c>
-      <c r="AHT2" t="n">
-        <v>782052</v>
-      </c>
-      <c r="AHU2" t="n">
-        <v>791695</v>
-      </c>
       <c r="AHV2" t="n">
-        <v>441328</v>
+        <v>206619</v>
       </c>
       <c r="AHW2" t="n">
-        <v>451013</v>
+        <v>1059739</v>
       </c>
       <c r="AHX2" t="n">
-        <v>539012</v>
+        <v>5731</v>
       </c>
       <c r="AHY2" t="n">
-        <v>701517</v>
+        <v>346825</v>
       </c>
       <c r="AHZ2" t="n">
-        <v>51408</v>
+        <v>404606</v>
       </c>
       <c r="AIA2" t="n">
-        <v>467563</v>
+        <v>268868</v>
       </c>
       <c r="AIB2" t="n">
-        <v>1196672</v>
+        <v>282491</v>
       </c>
       <c r="AIC2" t="n">
-        <v>270446</v>
+        <v>757189</v>
       </c>
       <c r="AID2" t="n">
-        <v>1170752</v>
+        <v>1191666</v>
       </c>
       <c r="AIE2" t="n">
-        <v>905967</v>
+        <v>475371</v>
       </c>
       <c r="AIF2" t="n">
-        <v>1163673</v>
+        <v>230273</v>
       </c>
       <c r="AIG2" t="n">
-        <v>789124</v>
+        <v>233647</v>
       </c>
       <c r="AIH2" t="n">
-        <v>681221</v>
+        <v>662590</v>
       </c>
       <c r="AII2" t="n">
-        <v>1123910</v>
+        <v>565337</v>
       </c>
       <c r="AIJ2" t="n">
-        <v>57653</v>
+        <v>1178510</v>
       </c>
       <c r="AIK2" t="n">
-        <v>509865</v>
+        <v>309899</v>
       </c>
       <c r="AIL2" t="n">
-        <v>1047176</v>
+        <v>539498</v>
       </c>
       <c r="AIM2" t="n">
-        <v>709420</v>
+        <v>932859</v>
       </c>
       <c r="AIN2" t="n">
-        <v>607004</v>
+        <v>837418</v>
       </c>
       <c r="AIO2" t="n">
-        <v>659448</v>
+        <v>718685</v>
       </c>
       <c r="AIP2" t="n">
-        <v>323410</v>
+        <v>707166</v>
       </c>
       <c r="AIQ2" t="n">
-        <v>1133695</v>
+        <v>674455</v>
       </c>
       <c r="AIR2" t="n">
-        <v>553698</v>
+        <v>1192248</v>
       </c>
       <c r="AIS2" t="n">
-        <v>1097645</v>
+        <v>628600</v>
       </c>
       <c r="AIT2" t="n">
-        <v>647687</v>
+        <v>225888</v>
       </c>
       <c r="AIU2" t="n">
-        <v>664695</v>
+        <v>1125704</v>
       </c>
       <c r="AIV2" t="n">
-        <v>979970</v>
+        <v>821492</v>
       </c>
       <c r="AIW2" t="n">
-        <v>318290</v>
+        <v>89010</v>
       </c>
       <c r="AIX2" t="n">
-        <v>1081186</v>
+        <v>1110669</v>
       </c>
       <c r="AIY2" t="n">
-        <v>1057028</v>
+        <v>1054423</v>
       </c>
       <c r="AIZ2" t="n">
-        <v>1046545</v>
+        <v>1130687</v>
       </c>
       <c r="AJA2" t="n">
-        <v>899795</v>
+        <v>214086</v>
       </c>
       <c r="AJB2" t="n">
-        <v>699672</v>
+        <v>64884</v>
       </c>
       <c r="AJC2" t="n">
-        <v>541639</v>
+        <v>53060</v>
       </c>
       <c r="AJD2" t="n">
-        <v>1122278</v>
+        <v>457378</v>
       </c>
       <c r="AJE2" t="n">
-        <v>286073</v>
+        <v>145151</v>
       </c>
       <c r="AJF2" t="n">
-        <v>735817</v>
+        <v>1182927</v>
       </c>
       <c r="AJG2" t="n">
-        <v>957852</v>
+        <v>879921</v>
       </c>
       <c r="AJH2" t="n">
-        <v>130818</v>
+        <v>1070019</v>
       </c>
       <c r="AJI2" t="n">
-        <v>1092260</v>
+        <v>737358</v>
       </c>
       <c r="AJJ2" t="n">
-        <v>1084559</v>
+        <v>503175</v>
       </c>
       <c r="AJK2" t="n">
-        <v>496956</v>
+        <v>140930</v>
       </c>
       <c r="AJL2" t="n">
-        <v>346178</v>
+        <v>2686</v>
       </c>
       <c r="AJM2" t="n">
-        <v>197090</v>
+        <v>395849</v>
       </c>
       <c r="AJN2" t="n">
-        <v>2262</v>
+        <v>241831</v>
       </c>
       <c r="AJO2" t="n">
-        <v>471488</v>
+        <v>1032253</v>
       </c>
       <c r="AJP2" t="n">
-        <v>418890</v>
+        <v>981095</v>
       </c>
       <c r="AJQ2" t="n">
-        <v>116443</v>
+        <v>626763</v>
       </c>
       <c r="AJR2" t="n">
-        <v>432301</v>
+        <v>495389</v>
       </c>
       <c r="AJS2" t="n">
-        <v>62385</v>
+        <v>931362</v>
       </c>
       <c r="AJT2" t="n">
-        <v>864353</v>
+        <v>36499</v>
       </c>
       <c r="AJU2" t="n">
-        <v>174351</v>
+        <v>760432</v>
       </c>
       <c r="AJV2" t="n">
-        <v>1148822</v>
+        <v>606722</v>
       </c>
       <c r="AJW2" t="n">
-        <v>592963</v>
+        <v>731622</v>
       </c>
       <c r="AJX2" t="n">
-        <v>1004897</v>
+        <v>1072048</v>
       </c>
       <c r="AJY2" t="n">
-        <v>539302</v>
+        <v>1136064</v>
       </c>
       <c r="AJZ2" t="n">
-        <v>699620</v>
+        <v>531483</v>
       </c>
       <c r="AKA2" t="n">
-        <v>877224</v>
+        <v>446634</v>
       </c>
       <c r="AKB2" t="n">
-        <v>446775</v>
+        <v>929591</v>
       </c>
       <c r="AKC2" t="n">
-        <v>99345</v>
+        <v>733924</v>
       </c>
       <c r="AKD2" t="n">
-        <v>651399</v>
+        <v>120894</v>
       </c>
       <c r="AKE2" t="n">
-        <v>939434</v>
+        <v>85672</v>
       </c>
       <c r="AKF2" t="n">
-        <v>572544</v>
+        <v>831758</v>
       </c>
       <c r="AKG2" t="n">
-        <v>632275</v>
+        <v>1164339</v>
       </c>
       <c r="AKH2" t="n">
-        <v>216215</v>
+        <v>323021</v>
       </c>
       <c r="AKI2" t="n">
-        <v>629512</v>
+        <v>936881</v>
       </c>
       <c r="AKJ2" t="n">
-        <v>776456</v>
+        <v>568990</v>
       </c>
       <c r="AKK2" t="n">
-        <v>448133</v>
+        <v>182951</v>
       </c>
       <c r="AKL2" t="n">
-        <v>887146</v>
+        <v>1049611</v>
       </c>
       <c r="AKM2" t="n">
-        <v>903500</v>
+        <v>909376</v>
       </c>
       <c r="AKN2" t="n">
-        <v>576211</v>
+        <v>834616</v>
       </c>
       <c r="AKO2" t="n">
-        <v>557960</v>
+        <v>299517</v>
       </c>
       <c r="AKP2" t="n">
-        <v>460110</v>
+        <v>868862</v>
       </c>
       <c r="AKQ2" t="n">
-        <v>465171</v>
+        <v>478361</v>
       </c>
       <c r="AKR2" t="n">
-        <v>983763</v>
+        <v>429296</v>
       </c>
       <c r="AKS2" t="n">
-        <v>36035</v>
+        <v>1073884</v>
       </c>
       <c r="AKT2" t="n">
-        <v>1099464</v>
+        <v>698531</v>
       </c>
       <c r="AKU2" t="n">
-        <v>2747</v>
+        <v>27839</v>
       </c>
       <c r="AKV2" t="n">
-        <v>694159</v>
+        <v>1141702</v>
       </c>
       <c r="AKW2" t="n">
-        <v>5872</v>
+        <v>168750</v>
       </c>
       <c r="AKX2" t="n">
-        <v>992850</v>
+        <v>675334</v>
       </c>
       <c r="AKY2" t="n">
-        <v>324585</v>
+        <v>997993</v>
       </c>
       <c r="AKZ2" t="n">
-        <v>634718</v>
+        <v>697224</v>
       </c>
       <c r="ALA2" t="n">
-        <v>293011</v>
+        <v>1168812</v>
       </c>
       <c r="ALB2" t="n">
-        <v>1158956</v>
+        <v>328611</v>
       </c>
       <c r="ALC2" t="n">
-        <v>121066</v>
+        <v>1083227</v>
       </c>
       <c r="ALD2" t="n">
-        <v>52539</v>
+        <v>305839</v>
       </c>
       <c r="ALE2" t="n">
-        <v>262235</v>
+        <v>599073</v>
       </c>
       <c r="ALF2" t="n">
-        <v>851043</v>
+        <v>122924</v>
       </c>
       <c r="ALG2" t="n">
-        <v>285554</v>
+        <v>713830</v>
       </c>
       <c r="ALH2" t="n">
-        <v>401206</v>
+        <v>989931</v>
       </c>
       <c r="ALI2" t="n">
-        <v>842160</v>
+        <v>225663</v>
       </c>
       <c r="ALJ2" t="n">
-        <v>894488</v>
+        <v>320113</v>
       </c>
       <c r="ALK2" t="n">
-        <v>569066</v>
+        <v>823025</v>
       </c>
       <c r="ALL2" t="n">
-        <v>804834</v>
+        <v>1062607</v>
       </c>
     </row>
   </sheetData>
